--- a/research/traditional_assets/database/data/india/india_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/india/india_oil_gas_integrated.xlsx
@@ -650,10 +650,10 @@
         <v>0.1316113590198378</v>
       </c>
       <c r="X2">
-        <v>0.1446331033984183</v>
+        <v>0.1446145921985092</v>
       </c>
       <c r="Y2">
-        <v>-0.0130217443785805</v>
+        <v>-0.01300323317867144</v>
       </c>
       <c r="Z2">
         <v>1.515300911624154</v>
@@ -662,10 +662,10 @@
         <v>0.1032547757153735</v>
       </c>
       <c r="AB2">
-        <v>0.1101538204191113</v>
+        <v>0.110142600555919</v>
       </c>
       <c r="AC2">
-        <v>-0.006899044703737811</v>
+        <v>-0.006887824840545453</v>
       </c>
       <c r="AD2">
         <v>22855.5</v>
@@ -787,10 +787,10 @@
         <v>0.1316113590198378</v>
       </c>
       <c r="X3">
-        <v>0.1446331033984183</v>
+        <v>0.1446145921985092</v>
       </c>
       <c r="Y3">
-        <v>-0.0130217443785805</v>
+        <v>-0.01300323317867144</v>
       </c>
       <c r="Z3">
         <v>1.515300911624154</v>
@@ -799,10 +799,10 @@
         <v>0.1032547757153735</v>
       </c>
       <c r="AB3">
-        <v>0.1101538204191113</v>
+        <v>0.110142600555919</v>
       </c>
       <c r="AC3">
-        <v>-0.006899044703737811</v>
+        <v>-0.006887824840545453</v>
       </c>
       <c r="AD3">
         <v>22855.5</v>
@@ -1139,49 +1139,49 @@
         <v>6.92313341493268</v>
       </c>
       <c r="F2">
-        <v>3.05889746363137</v>
+        <v>3.01151839916519</v>
       </c>
       <c r="G2">
         <v>2.29765866114423</v>
       </c>
       <c r="H2">
-        <v>2.33331255717632</v>
+        <v>2.44997818503514</v>
       </c>
       <c r="I2">
         <v>0.393887849114353</v>
       </c>
       <c r="J2">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="K2">
         <v>35169.9</v>
       </c>
       <c r="L2">
-        <v>35308.8512318811</v>
+        <v>34985.9847439754</v>
       </c>
       <c r="M2">
         <v>53574.8</v>
       </c>
       <c r="N2">
-        <v>54068.4112318811</v>
+        <v>54906.0527439754</v>
       </c>
       <c r="O2">
         <v>22855.5</v>
       </c>
       <c r="P2">
-        <v>23210.16</v>
+        <v>24370.668</v>
       </c>
       <c r="Q2">
-        <v>0.110153820419111</v>
+        <v>0.110142600555919</v>
       </c>
       <c r="R2">
-        <v>0.109566309747916</v>
+        <v>0.10858254917244</v>
       </c>
       <c r="S2">
         <v>0.0570973161005042</v>
       </c>
       <c r="T2">
-        <v>0.0557673161005042</v>
+        <v>0.0539473161005042</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.144633103398418</v>
+        <v>0.144614592198509</v>
       </c>
       <c r="X2">
-        <v>0.145432305512857</v>
+        <v>0.148145993810739</v>
       </c>
       <c r="Y2">
         <v>1.36022005591736</v>
       </c>
       <c r="Z2">
-        <v>1.37121931332616</v>
+        <v>1.40883112834687</v>
       </c>
       <c r="AA2">
         <v>22855.5</v>
@@ -1236,7 +1236,7 @@
         <v>35169.9</v>
       </c>
       <c r="AK2">
-        <v>0.07265964280446037</v>
+        <v>0.07264603383006793</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1137311173951294</v>
+        <v>0.1137183940620466</v>
       </c>
       <c r="C2">
-        <v>55204.11606739512</v>
+        <v>55204.77350289707</v>
       </c>
       <c r="D2">
-        <v>50753.51606739512</v>
+        <v>50754.17350289707</v>
       </c>
       <c r="E2">
         <v>-22855.5</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1137311173951294</v>
+        <v>0.1137183940620466</v>
       </c>
       <c r="T2">
         <v>0.9349222590860211</v>
       </c>
       <c r="U2">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V2">
         <v>0.3</v>
       </c>
       <c r="W2">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1135835972039491</v>
+        <v>0.1135611120408655</v>
       </c>
       <c r="C3">
-        <v>54734.31900243813</v>
+        <v>54742.32629135557</v>
       </c>
       <c r="D3">
-        <v>50863.97300243814</v>
+        <v>50871.98029135558</v>
       </c>
       <c r="E3">
         <v>-22275.246</v>
@@ -1539,37 +1539,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M3">
-        <v>42.62986553797422</v>
+        <v>41.81750993797422</v>
       </c>
       <c r="N3">
-        <v>5613.570134462025</v>
+        <v>5614.382490062025</v>
       </c>
       <c r="O3">
-        <v>1684.071040338607</v>
+        <v>1684.314747018607</v>
       </c>
       <c r="P3">
-        <v>3929.499094123417</v>
+        <v>3930.067743043417</v>
       </c>
       <c r="Q3">
-        <v>8220.599094123418</v>
+        <v>8221.167743043417</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1142114384272162</v>
+        <v>0.1141986251311722</v>
       </c>
       <c r="T3">
         <v>0.941532820513902</v>
       </c>
       <c r="U3">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V3">
         <v>0.3</v>
       </c>
       <c r="W3">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>132.6816289148629</v>
+        <v>135.2591296896815</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1134360770127688</v>
+        <v>0.1134038300196844</v>
       </c>
       <c r="C4">
-        <v>54265.00376992598</v>
+        <v>54280.42724076273</v>
       </c>
       <c r="D4">
-        <v>50974.91176992599</v>
+        <v>50990.33524076273</v>
       </c>
       <c r="E4">
         <v>-21694.992</v>
@@ -1621,37 +1621,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M4">
-        <v>85.25973107594844</v>
+        <v>83.63501987594843</v>
       </c>
       <c r="N4">
-        <v>5570.940268924051</v>
+        <v>5572.564980124051</v>
       </c>
       <c r="O4">
-        <v>1671.282080677215</v>
+        <v>1671.769494037215</v>
       </c>
       <c r="P4">
-        <v>3899.658188246835</v>
+        <v>3900.795486086836</v>
       </c>
       <c r="Q4">
-        <v>8190.758188246836</v>
+        <v>8191.895486086836</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1147015619293456</v>
+        <v>0.1146886568343616</v>
       </c>
       <c r="T4">
         <v>0.9482782913586785</v>
       </c>
       <c r="U4">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V4">
         <v>0.3</v>
       </c>
       <c r="W4">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>66.34081445743146</v>
+        <v>67.62956484484074</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1132885568215884</v>
+        <v>0.1132465479985033</v>
       </c>
       <c r="C5">
-        <v>53796.17352950614</v>
+        <v>53819.08018597135</v>
       </c>
       <c r="D5">
-        <v>51086.33552950614</v>
+        <v>51109.24218597135</v>
       </c>
       <c r="E5">
         <v>-21114.738</v>
@@ -1703,37 +1703,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M5">
-        <v>127.8895966139226</v>
+        <v>125.4525298139227</v>
       </c>
       <c r="N5">
-        <v>5528.310403386076</v>
+        <v>5530.747470186076</v>
       </c>
       <c r="O5">
-        <v>1658.493121015823</v>
+        <v>1659.224241055823</v>
       </c>
       <c r="P5">
-        <v>3869.817282370253</v>
+        <v>3871.523229130254</v>
       </c>
       <c r="Q5">
-        <v>8160.917282370254</v>
+        <v>8162.623229130254</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1152017910706941</v>
+        <v>0.1151887922840085</v>
       </c>
       <c r="T5">
         <v>0.9551628440765432</v>
       </c>
       <c r="U5">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.22720963828765</v>
+        <v>45.08637656322716</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.113141036630408</v>
+        <v>0.1130892659773222</v>
       </c>
       <c r="C6">
-        <v>53327.83146851266</v>
+        <v>53358.28899768867</v>
       </c>
       <c r="D6">
-        <v>51198.24746851267</v>
+        <v>51228.70499768868</v>
       </c>
       <c r="E6">
         <v>-20534.484</v>
@@ -1785,37 +1785,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M6">
-        <v>170.5194621518969</v>
+        <v>167.2700397518969</v>
       </c>
       <c r="N6">
-        <v>5485.680537848102</v>
+        <v>5488.929960248102</v>
       </c>
       <c r="O6">
-        <v>1645.704161354431</v>
+        <v>1646.678988074431</v>
       </c>
       <c r="P6">
-        <v>3839.976376493672</v>
+        <v>3842.250972173671</v>
       </c>
       <c r="Q6">
-        <v>8131.076376493672</v>
+        <v>8133.350972173672</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1157124416524874</v>
+        <v>0.1156993472221896</v>
       </c>
       <c r="T6">
         <v>0.9621908249760299</v>
       </c>
       <c r="U6">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.17040722871573</v>
+        <v>33.81478242242037</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1129935164392277</v>
+        <v>0.1129319839561411</v>
       </c>
       <c r="C7">
-        <v>52859.98080227007</v>
+        <v>52898.05758289619</v>
       </c>
       <c r="D7">
-        <v>51310.65080227008</v>
+        <v>51348.72758289619</v>
       </c>
       <c r="E7">
         <v>-19954.23</v>
@@ -1867,37 +1867,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M7">
-        <v>213.1493276898711</v>
+        <v>209.0875496898711</v>
       </c>
       <c r="N7">
-        <v>5443.050672310128</v>
+        <v>5447.112450310128</v>
       </c>
       <c r="O7">
-        <v>1632.915201693038</v>
+        <v>1634.133735093038</v>
       </c>
       <c r="P7">
-        <v>3810.13547061709</v>
+        <v>3812.97871521709</v>
       </c>
       <c r="Q7">
-        <v>8101.23547061709</v>
+        <v>8104.078715217091</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1162338427728447</v>
+        <v>0.1162206506853852</v>
       </c>
       <c r="T7">
         <v>0.9693667633681375</v>
       </c>
       <c r="U7">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.53632578297259</v>
+        <v>27.0518259379363</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1128459962480474</v>
+        <v>0.11277470193496</v>
       </c>
       <c r="C8">
-        <v>52392.62477440154</v>
+        <v>52438.38988527584</v>
       </c>
       <c r="D8">
-        <v>51423.54877440154</v>
+        <v>51469.31388527584</v>
       </c>
       <c r="E8">
         <v>-19373.976</v>
@@ -1949,37 +1949,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M8">
-        <v>255.7791932278453</v>
+        <v>250.9050596278453</v>
       </c>
       <c r="N8">
-        <v>5400.420806772154</v>
+        <v>5405.294940372153</v>
       </c>
       <c r="O8">
-        <v>1620.126242031646</v>
+        <v>1621.588482111646</v>
       </c>
       <c r="P8">
-        <v>3780.294564740508</v>
+        <v>3783.706458260507</v>
       </c>
       <c r="Q8">
-        <v>8071.394564740508</v>
+        <v>8074.806458260507</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1167663375340608</v>
+        <v>0.1167530457116274</v>
       </c>
       <c r="T8">
         <v>0.9766953813005028</v>
       </c>
       <c r="U8">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.11360481914382</v>
+        <v>22.54318828161358</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.112698476056867</v>
+        <v>0.1126174199137789</v>
       </c>
       <c r="C9">
-        <v>51925.76665714067</v>
+        <v>51979.2898856417</v>
       </c>
       <c r="D9">
-        <v>51536.94465714067</v>
+        <v>51590.4678856417</v>
       </c>
       <c r="E9">
         <v>-18793.722</v>
@@ -2031,37 +2031,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M9">
-        <v>298.4090587658196</v>
+        <v>292.7225695658196</v>
       </c>
       <c r="N9">
-        <v>5357.79094123418</v>
+        <v>5363.477430434179</v>
       </c>
       <c r="O9">
-        <v>1607.337282370254</v>
+        <v>1609.043229130254</v>
       </c>
       <c r="P9">
-        <v>3750.453658863926</v>
+        <v>3754.434201303925</v>
       </c>
       <c r="Q9">
-        <v>8041.553658863926</v>
+        <v>8045.534201303926</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.117310283795518</v>
+        <v>0.1172968900932727</v>
       </c>
       <c r="T9">
         <v>0.9841816039195858</v>
       </c>
       <c r="U9">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.95451841640899</v>
+        <v>19.32273281281164</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1125509558656867</v>
+        <v>0.1124601378925978</v>
       </c>
       <c r="C10">
-        <v>51459.40975164776</v>
+        <v>51520.76160237822</v>
       </c>
       <c r="D10">
-        <v>51650.84175164776</v>
+        <v>51712.19360237823</v>
       </c>
       <c r="E10">
         <v>-18213.468</v>
@@ -2113,37 +2113,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M10">
-        <v>341.0389243037937</v>
+        <v>334.5400795037937</v>
       </c>
       <c r="N10">
-        <v>5315.161075696205</v>
+        <v>5321.659920496205</v>
       </c>
       <c r="O10">
-        <v>1594.548322708862</v>
+        <v>1596.497976148861</v>
       </c>
       <c r="P10">
-        <v>3720.612752987344</v>
+        <v>3725.161944347344</v>
       </c>
       <c r="Q10">
-        <v>8011.712752987344</v>
+        <v>8016.261944347344</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1178660549757025</v>
+        <v>0.1178525571788669</v>
       </c>
       <c r="T10">
         <v>0.9918305705086485</v>
       </c>
       <c r="U10">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.58520361435787</v>
+        <v>16.90739121121019</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1124034356745063</v>
+        <v>0.1123028558714167</v>
       </c>
       <c r="C11">
-        <v>50993.55738833008</v>
+        <v>51062.80909188443</v>
       </c>
       <c r="D11">
-        <v>51765.24338833008</v>
+        <v>51834.49509188443</v>
       </c>
       <c r="E11">
         <v>-17633.214</v>
@@ -2195,37 +2195,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M11">
-        <v>383.6687898417679</v>
+        <v>376.357589441768</v>
       </c>
       <c r="N11">
-        <v>5272.531210158231</v>
+        <v>5279.842410558231</v>
       </c>
       <c r="O11">
-        <v>1581.759363047469</v>
+        <v>1583.952723167469</v>
       </c>
       <c r="P11">
-        <v>3690.771847110762</v>
+        <v>3695.889687390762</v>
       </c>
       <c r="Q11">
-        <v>7981.871847110762</v>
+        <v>7986.989687390762</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1184340409070999</v>
+        <v>0.1184204367278806</v>
       </c>
       <c r="T11">
         <v>0.9996476462535149</v>
       </c>
       <c r="U11">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.74240321276255</v>
+        <v>15.02879218774239</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.112255915483326</v>
+        <v>0.1121455738502356</v>
       </c>
       <c r="C12">
-        <v>50528.21292716654</v>
+        <v>50605.43644902449</v>
       </c>
       <c r="D12">
-        <v>51880.15292716654</v>
+        <v>51957.37644902449</v>
       </c>
       <c r="E12">
         <v>-17052.96</v>
@@ -2277,37 +2277,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M12">
-        <v>426.2986553797422</v>
+        <v>418.1750993797422</v>
       </c>
       <c r="N12">
-        <v>5229.901344620257</v>
+        <v>5238.024900620257</v>
       </c>
       <c r="O12">
-        <v>1568.970403386077</v>
+        <v>1571.407470186077</v>
       </c>
       <c r="P12">
-        <v>3660.93094123418</v>
+        <v>3666.617430434179</v>
       </c>
       <c r="Q12">
-        <v>7952.03094123418</v>
+        <v>7957.71743043418</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.119014648748084</v>
+        <v>0.119000935822428</v>
       </c>
       <c r="T12">
         <v>1.007638434792712</v>
       </c>
       <c r="U12">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>13.26816289148629</v>
+        <v>13.52591296896815</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1121083952921456</v>
+        <v>0.1119882918290545</v>
       </c>
       <c r="C13">
-        <v>50063.37975803662</v>
+        <v>50148.64780758482</v>
       </c>
       <c r="D13">
-        <v>51995.57375803663</v>
+        <v>52080.84180758482</v>
       </c>
       <c r="E13">
         <v>-16472.706</v>
@@ -2359,37 +2359,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M13">
-        <v>468.9285209177164</v>
+        <v>459.9926093177164</v>
       </c>
       <c r="N13">
-        <v>5187.271479082283</v>
+        <v>5196.207390682282</v>
       </c>
       <c r="O13">
-        <v>1556.181443724685</v>
+        <v>1558.862217204685</v>
       </c>
       <c r="P13">
-        <v>3631.090035357598</v>
+        <v>3637.345173477598</v>
       </c>
       <c r="Q13">
-        <v>7922.190035357598</v>
+        <v>7928.445173477598</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1196083039562811</v>
+        <v>0.1195944798404484</v>
       </c>
       <c r="T13">
         <v>1.015808791613688</v>
       </c>
       <c r="U13">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.06196626498754</v>
+        <v>12.29628451724377</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1119608751009653</v>
+        <v>0.1118310098078734</v>
       </c>
       <c r="C14">
-        <v>49599.06130105373</v>
+        <v>49692.44734073756</v>
       </c>
       <c r="D14">
-        <v>52111.50930105374</v>
+        <v>52204.89534073756</v>
       </c>
       <c r="E14">
         <v>-15892.452</v>
@@ -2441,37 +2441,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M14">
-        <v>511.5583864556906</v>
+        <v>501.8101192556906</v>
       </c>
       <c r="N14">
-        <v>5144.641613544309</v>
+        <v>5154.389880744308</v>
       </c>
       <c r="O14">
-        <v>1543.392484063293</v>
+        <v>1546.316964223292</v>
       </c>
       <c r="P14">
-        <v>3601.249129481016</v>
+        <v>3608.072916521016</v>
       </c>
       <c r="Q14">
-        <v>7892.349129481016</v>
+        <v>7899.172916521016</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1202154513283009</v>
+        <v>0.120201513495242</v>
       </c>
       <c r="T14">
         <v>1.024164838362414</v>
       </c>
       <c r="U14">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.05680240957191</v>
+        <v>11.27159414080679</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1118133549097849</v>
+        <v>0.1116737277866923</v>
       </c>
       <c r="C15">
-        <v>49135.26100690301</v>
+        <v>49236.83926151082</v>
       </c>
       <c r="D15">
-        <v>52227.96300690301</v>
+        <v>52329.54126151082</v>
       </c>
       <c r="E15">
         <v>-15312.198</v>
@@ -2523,37 +2523,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M15">
-        <v>554.1882519936648</v>
+        <v>543.6276291936649</v>
       </c>
       <c r="N15">
-        <v>5102.011748006335</v>
+        <v>5112.572370806334</v>
       </c>
       <c r="O15">
-        <v>1530.6035244019</v>
+        <v>1533.7717112419</v>
       </c>
       <c r="P15">
-        <v>3571.408223604434</v>
+        <v>3578.800659564434</v>
       </c>
       <c r="Q15">
-        <v>7862.508223604435</v>
+        <v>7869.900659564434</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1208365561111717</v>
+        <v>0.1208225019466975</v>
       </c>
       <c r="T15">
         <v>1.032712978139846</v>
       </c>
       <c r="U15">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.20627914729715</v>
+        <v>10.4045484376678</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1116658347186046</v>
+        <v>0.1115164457655113</v>
       </c>
       <c r="C16">
-        <v>48671.98235718367</v>
+        <v>48781.82782326556</v>
       </c>
       <c r="D16">
-        <v>52344.93835718367</v>
+        <v>52454.78382326556</v>
       </c>
       <c r="E16">
         <v>-14731.944</v>
@@ -2605,37 +2605,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M16">
-        <v>596.8181175316391</v>
+        <v>585.4451391316392</v>
       </c>
       <c r="N16">
-        <v>5059.381882468359</v>
+        <v>5070.75486086836</v>
       </c>
       <c r="O16">
-        <v>1517.814564740508</v>
+        <v>1521.226458260508</v>
       </c>
       <c r="P16">
-        <v>3541.567317727851</v>
+        <v>3549.528402607852</v>
       </c>
       <c r="Q16">
-        <v>7832.667317727852</v>
+        <v>7840.628402607852</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1214721051913186</v>
+        <v>0.1214579319900473</v>
       </c>
       <c r="T16">
         <v>1.041459911865591</v>
       </c>
       <c r="U16">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.477259208204494</v>
+        <v>9.661366406405818</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1115183145274243</v>
+        <v>0.1113591637443302</v>
       </c>
       <c r="C17">
-        <v>48209.22886475609</v>
+        <v>48327.41732017951</v>
       </c>
       <c r="D17">
-        <v>52462.43886475608</v>
+        <v>52580.6273201795</v>
       </c>
       <c r="E17">
         <v>-14151.69</v>
@@ -2687,37 +2687,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M17">
-        <v>639.4479830696132</v>
+        <v>627.2626490696132</v>
       </c>
       <c r="N17">
-        <v>5016.752016930386</v>
+        <v>5028.937350930386</v>
       </c>
       <c r="O17">
-        <v>1505.025605079116</v>
+        <v>1508.681205279116</v>
       </c>
       <c r="P17">
-        <v>3511.72641185127</v>
+        <v>3520.25614565127</v>
       </c>
       <c r="Q17">
-        <v>7802.826411851271</v>
+        <v>7811.356145651271</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.122122608367469</v>
+        <v>0.1221083133285348</v>
       </c>
       <c r="T17">
         <v>1.050412655796647</v>
       </c>
       <c r="U17">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.05142731610050418</v>
+        <v>0.05044731610050417</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.84544192765753</v>
+        <v>9.017275312645433</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1114939943362439</v>
+        <v>0.111369881723149</v>
       </c>
       <c r="C18">
-        <v>47648.39667881793</v>
+        <v>47738.56855021667</v>
       </c>
       <c r="D18">
-        <v>52481.86067881793</v>
+        <v>52572.03255021667</v>
       </c>
       <c r="E18">
         <v>-13571.436</v>
@@ -2769,37 +2769,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M18">
-        <v>692.2903190075874</v>
+        <v>683.0062550075874</v>
       </c>
       <c r="N18">
-        <v>4963.909680992411</v>
+        <v>4973.193744992412</v>
       </c>
       <c r="O18">
-        <v>1489.172904297723</v>
+        <v>1491.958123497723</v>
       </c>
       <c r="P18">
-        <v>3474.736776694688</v>
+        <v>3481.235621494689</v>
       </c>
       <c r="Q18">
-        <v>7765.836776694689</v>
+        <v>7772.335621494689</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.12278859971448</v>
+        <v>0.1227741799369862</v>
       </c>
       <c r="T18">
         <v>1.059578560297491</v>
       </c>
       <c r="U18">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.05219731610050417</v>
+        <v>0.05149731610050417</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.17027169772976</v>
+        <v>8.281329722137269</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1113541741450636</v>
+        <v>0.1112230997019679</v>
       </c>
       <c r="C19">
-        <v>47180.08099379653</v>
+        <v>47276.26416175253</v>
       </c>
       <c r="D19">
-        <v>52593.79899379653</v>
+        <v>52689.98216175253</v>
       </c>
       <c r="E19">
         <v>-12991.182</v>
@@ -2851,37 +2851,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M19">
-        <v>735.5584639455617</v>
+        <v>725.6941459455617</v>
       </c>
       <c r="N19">
-        <v>4920.641536054437</v>
+        <v>4930.505854054437</v>
       </c>
       <c r="O19">
-        <v>1476.192460816331</v>
+        <v>1479.151756216331</v>
       </c>
       <c r="P19">
-        <v>3444.449075238106</v>
+        <v>3451.354097838106</v>
       </c>
       <c r="Q19">
-        <v>7735.549075238107</v>
+        <v>7742.454097838106</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1234706390457564</v>
+        <v>0.1234560915239545</v>
       </c>
       <c r="T19">
         <v>1.068965329967029</v>
       </c>
       <c r="U19">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.05219731610050417</v>
+        <v>0.05149731610050417</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.689667480216245</v>
+        <v>7.794192679658603</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1112143539538832</v>
+        <v>0.1110763176807869</v>
       </c>
       <c r="C20">
-        <v>46712.24383483722</v>
+        <v>46814.49022240053</v>
       </c>
       <c r="D20">
-        <v>52706.21583483722</v>
+        <v>52808.46222240054</v>
       </c>
       <c r="E20">
         <v>-12410.928</v>
@@ -2933,37 +2933,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M20">
-        <v>778.8266088835358</v>
+        <v>768.3820368835358</v>
       </c>
       <c r="N20">
-        <v>4877.373391116464</v>
+        <v>4887.817963116463</v>
       </c>
       <c r="O20">
-        <v>1463.212017334939</v>
+        <v>1466.345388934939</v>
       </c>
       <c r="P20">
-        <v>3414.161373781525</v>
+        <v>3421.472574181524</v>
       </c>
       <c r="Q20">
-        <v>7705.261373781525</v>
+        <v>7712.572574181524</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1241693134826737</v>
+        <v>0.1241546351008489</v>
       </c>
       <c r="T20">
         <v>1.078581045238263</v>
       </c>
       <c r="U20">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.05219731610050417</v>
+        <v>0.05149731610050417</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.262463731315345</v>
+        <v>7.361181975233126</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1110745337627028</v>
+        <v>0.1109295356596058</v>
       </c>
       <c r="C21">
-        <v>46244.88827699555</v>
+        <v>46353.25031857006</v>
       </c>
       <c r="D21">
-        <v>52819.11427699555</v>
+        <v>52927.47631857006</v>
       </c>
       <c r="E21">
         <v>-11830.674</v>
@@ -3015,37 +3015,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M21">
-        <v>822.09475382151</v>
+        <v>811.0699278215101</v>
       </c>
       <c r="N21">
-        <v>4834.105246178489</v>
+        <v>4845.130072178489</v>
       </c>
       <c r="O21">
-        <v>1450.231573853547</v>
+        <v>1453.539021653547</v>
       </c>
       <c r="P21">
-        <v>3383.873672324943</v>
+        <v>3391.591050524942</v>
       </c>
       <c r="Q21">
-        <v>7674.973672324943</v>
+        <v>7682.691050524943</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1248852391402556</v>
+        <v>0.1248704266672963</v>
       </c>
       <c r="T21">
         <v>1.088434185577923</v>
       </c>
       <c r="U21">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.05219731610050417</v>
+        <v>0.05149731610050417</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.88022879808822</v>
+        <v>6.973751344957698</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1112427135715225</v>
+        <v>0.1110207536384247</v>
       </c>
       <c r="C22">
-        <v>45528.89558193943</v>
+        <v>45698.9717612868</v>
       </c>
       <c r="D22">
-        <v>52683.37558193944</v>
+        <v>52853.4517612868</v>
       </c>
       <c r="E22">
         <v>-11250.42</v>
@@ -3097,37 +3097,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M22">
-        <v>890.8940747594844</v>
+        <v>873.4864547594844</v>
       </c>
       <c r="N22">
-        <v>4765.305925240515</v>
+        <v>4782.713545240515</v>
       </c>
       <c r="O22">
-        <v>1429.591777572154</v>
+        <v>1434.814063572154</v>
       </c>
       <c r="P22">
-        <v>3335.71414766836</v>
+        <v>3347.89948166836</v>
       </c>
       <c r="Q22">
-        <v>7626.81414766836</v>
+        <v>7638.999481668361</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1256190629392771</v>
+        <v>0.1256041130229048</v>
       </c>
       <c r="T22">
         <v>1.098533654426075</v>
       </c>
       <c r="U22">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.05373731610050417</v>
+        <v>0.05268731610050417</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.348902928248804</v>
+        <v>6.475429549228031</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1111182933803422</v>
+        <v>0.1108858716172436</v>
       </c>
       <c r="C23">
-        <v>45048.99441301791</v>
+        <v>45228.24968000926</v>
       </c>
       <c r="D23">
-        <v>52783.72841301791</v>
+        <v>52962.98368000926</v>
       </c>
       <c r="E23">
         <v>-10670.166</v>
@@ -3179,37 +3179,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M23">
-        <v>935.4387784974585</v>
+        <v>917.1607774974585</v>
       </c>
       <c r="N23">
-        <v>4720.76122150254</v>
+        <v>4739.039222502541</v>
       </c>
       <c r="O23">
-        <v>1416.228366450762</v>
+        <v>1421.711766750762</v>
       </c>
       <c r="P23">
-        <v>3304.532855051778</v>
+        <v>3317.327455751779</v>
       </c>
       <c r="Q23">
-        <v>7595.632855051778</v>
+        <v>7608.427455751779</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1263714645559953</v>
+        <v>0.12635637371663</v>
       </c>
       <c r="T23">
         <v>1.108888806029876</v>
       </c>
       <c r="U23">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.05373731610050417</v>
+        <v>0.05268731610050417</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.046574217379813</v>
+        <v>6.167075761169555</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1109938731891618</v>
+        <v>0.1107509895960625</v>
       </c>
       <c r="C24">
-        <v>44569.47628372318</v>
+        <v>44757.9825228729</v>
       </c>
       <c r="D24">
-        <v>52884.46428372319</v>
+        <v>53072.97052287291</v>
       </c>
       <c r="E24">
         <v>-10089.912</v>
@@ -3261,37 +3261,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M24">
-        <v>979.9834822354327</v>
+        <v>960.8351002354327</v>
       </c>
       <c r="N24">
-        <v>4676.216517764567</v>
+        <v>4695.364899764566</v>
       </c>
       <c r="O24">
-        <v>1402.86495532937</v>
+        <v>1408.60946992937</v>
       </c>
       <c r="P24">
-        <v>3273.351562435197</v>
+        <v>3286.755429835196</v>
       </c>
       <c r="Q24">
-        <v>7564.451562435197</v>
+        <v>7577.855429835196</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1271431585218601</v>
+        <v>0.1271279231460917</v>
       </c>
       <c r="T24">
         <v>1.119509474341466</v>
       </c>
       <c r="U24">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.05373731610050417</v>
+        <v>0.05268731610050417</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.771729934771641</v>
+        <v>5.886754135661847</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1111109529979815</v>
+        <v>0.1106161075748814</v>
       </c>
       <c r="C25">
-        <v>43894.4188444278</v>
+        <v>44288.1731299629</v>
       </c>
       <c r="D25">
-        <v>52789.6608444278</v>
+        <v>53183.41512996291</v>
       </c>
       <c r="E25">
         <v>-9509.657999999999</v>
@@ -3343,45 +3343,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M25">
-        <v>1044.546948973407</v>
+        <v>1004.509422973407</v>
       </c>
       <c r="N25">
-        <v>4611.653051026592</v>
+        <v>4651.690577026592</v>
       </c>
       <c r="O25">
-        <v>1383.495915307978</v>
+        <v>1395.507173107978</v>
       </c>
       <c r="P25">
-        <v>3228.157135718614</v>
+        <v>3256.183403918614</v>
       </c>
       <c r="Q25">
-        <v>7519.257135718615</v>
+        <v>7547.283403918615</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1279348964868383</v>
+        <v>0.1279195128204745</v>
       </c>
       <c r="T25">
         <v>1.130406004167644</v>
       </c>
       <c r="U25">
-        <v>0.07826759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.05478731610050417</v>
+        <v>0.05268731610050417</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>5.414979197975714</v>
+        <v>5.63080830367655</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1109970328068011</v>
+        <v>0.1106156255537003</v>
       </c>
       <c r="C26">
-        <v>43406.40536515154</v>
+        <v>43708.31464466104</v>
       </c>
       <c r="D26">
-        <v>52881.90136515154</v>
+        <v>53183.81064466104</v>
       </c>
       <c r="E26">
         <v>-8929.404</v>
@@ -3425,37 +3425,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M26">
-        <v>1089.962033711381</v>
+        <v>1059.324622511381</v>
       </c>
       <c r="N26">
-        <v>4566.237966288618</v>
+        <v>4596.875377488618</v>
       </c>
       <c r="O26">
-        <v>1369.871389886585</v>
+        <v>1379.062613246585</v>
       </c>
       <c r="P26">
-        <v>3196.366576402032</v>
+        <v>3217.812764242033</v>
       </c>
       <c r="Q26">
-        <v>7487.466576402033</v>
+        <v>7508.912764242034</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1287474696614212</v>
+        <v>0.128731933802078</v>
       </c>
       <c r="T26">
         <v>1.141589284778721</v>
       </c>
       <c r="U26">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.05478731610050417</v>
+        <v>0.05324731610050417</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.189355064726727</v>
+        <v>5.339439752274078</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1108831126156208</v>
+        <v>0.1104863435325192</v>
       </c>
       <c r="C27">
-        <v>42918.7147978361</v>
+        <v>43234.35372228411</v>
       </c>
       <c r="D27">
-        <v>52974.4647978361</v>
+        <v>53290.10372228411</v>
       </c>
       <c r="E27">
         <v>-8349.15</v>
@@ -3507,37 +3507,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M27">
-        <v>1135.377118449356</v>
+        <v>1103.463148449355</v>
       </c>
       <c r="N27">
-        <v>4520.822881550644</v>
+        <v>4552.736851550644</v>
       </c>
       <c r="O27">
-        <v>1356.246864465193</v>
+        <v>1365.821055465193</v>
       </c>
       <c r="P27">
-        <v>3164.576017085451</v>
+        <v>3186.915796085451</v>
       </c>
       <c r="Q27">
-        <v>7455.67601708545</v>
+        <v>7478.015796085451</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.129581711453993</v>
+        <v>0.1295660193431908</v>
       </c>
       <c r="T27">
         <v>1.153070786206093</v>
       </c>
       <c r="U27">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.05478731610050417</v>
+        <v>0.05324731610050417</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.981780862137657</v>
+        <v>5.125862162183115</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1107691924244404</v>
+        <v>0.1103570615113381</v>
       </c>
       <c r="C28">
-        <v>42431.34884111085</v>
+        <v>42760.81852510566</v>
       </c>
       <c r="D28">
-        <v>53067.35284111085</v>
+        <v>53396.82252510566</v>
       </c>
       <c r="E28">
         <v>-7768.895999999999</v>
@@ -3589,37 +3589,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M28">
-        <v>1180.79220318733</v>
+        <v>1147.601674387329</v>
       </c>
       <c r="N28">
-        <v>4475.407796812669</v>
+        <v>4508.598325612669</v>
       </c>
       <c r="O28">
-        <v>1342.622339043801</v>
+        <v>1352.579497683801</v>
       </c>
       <c r="P28">
-        <v>3132.785457768869</v>
+        <v>3156.018827928869</v>
       </c>
       <c r="Q28">
-        <v>7423.885457768869</v>
+        <v>7447.118827928869</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1304385003220397</v>
+        <v>0.1304226477367662</v>
       </c>
       <c r="T28">
         <v>1.164862598482853</v>
       </c>
       <c r="U28">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.05478731610050417</v>
+        <v>0.05324731610050417</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.790173905901593</v>
+        <v>4.928713617483764</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1106552722332601</v>
+        <v>0.110227779490157</v>
       </c>
       <c r="C29">
-        <v>41944.30920553984</v>
+        <v>42287.71161593078</v>
       </c>
       <c r="D29">
-        <v>53160.56720553985</v>
+        <v>53503.96961593079</v>
       </c>
       <c r="E29">
         <v>-7188.641999999998</v>
@@ -3671,37 +3671,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M29">
-        <v>1226.207287925304</v>
+        <v>1191.740200325304</v>
       </c>
       <c r="N29">
-        <v>4429.992712074695</v>
+        <v>4464.459799674695</v>
       </c>
       <c r="O29">
-        <v>1328.997813622409</v>
+        <v>1339.337939902409</v>
       </c>
       <c r="P29">
-        <v>3100.994898452287</v>
+        <v>3125.121859772286</v>
       </c>
       <c r="Q29">
-        <v>7392.094898452287</v>
+        <v>7416.221859772287</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1313187628577041</v>
+        <v>0.1313027454013984</v>
       </c>
       <c r="T29">
         <v>1.176977474109662</v>
       </c>
       <c r="U29">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.05478731610050417</v>
+        <v>0.05324731610050417</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.612760057534867</v>
+        <v>4.746168668688068</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1105413520420797</v>
+        <v>0.1100984974689759</v>
       </c>
       <c r="C30">
-        <v>41457.59761372706</v>
+        <v>41815.0355781763</v>
       </c>
       <c r="D30">
-        <v>53254.10961372706</v>
+        <v>53611.5475781763</v>
       </c>
       <c r="E30">
         <v>-6608.387999999997</v>
@@ -3753,37 +3753,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M30">
-        <v>1271.622372663278</v>
+        <v>1235.878726263278</v>
       </c>
       <c r="N30">
-        <v>4384.577627336721</v>
+        <v>4420.321273736721</v>
       </c>
       <c r="O30">
-        <v>1315.373288201016</v>
+        <v>1326.096382121016</v>
       </c>
       <c r="P30">
-        <v>3069.204339135705</v>
+        <v>3094.224891615705</v>
       </c>
       <c r="Q30">
-        <v>7360.304339135705</v>
+        <v>7385.324891615705</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1322234771304702</v>
+        <v>0.1322072902233815</v>
       </c>
       <c r="T30">
         <v>1.189428874059438</v>
       </c>
       <c r="U30">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.05478731610050417</v>
+        <v>0.05324731610050417</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.448018626908622</v>
+        <v>4.576662644806351</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1104274318508994</v>
+        <v>0.1099692154477948</v>
       </c>
       <c r="C31">
-        <v>40971.21580042219</v>
+        <v>41342.7930160782</v>
       </c>
       <c r="D31">
-        <v>53347.98180042219</v>
+        <v>53719.55901607819</v>
       </c>
       <c r="E31">
         <v>-6028.134000000002</v>
@@ -3835,37 +3835,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M31">
-        <v>1317.037457401252</v>
+        <v>1280.017252201252</v>
       </c>
       <c r="N31">
-        <v>4339.162542598747</v>
+        <v>4376.182747798747</v>
       </c>
       <c r="O31">
-        <v>1301.748762779624</v>
+        <v>1312.854824339624</v>
       </c>
       <c r="P31">
-        <v>3037.413779819123</v>
+        <v>3063.327923459123</v>
       </c>
       <c r="Q31">
-        <v>7328.513779819123</v>
+        <v>7354.427923459123</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1331536763123284</v>
+        <v>0.1331373151811952</v>
       </c>
       <c r="T31">
         <v>1.202231017669771</v>
       </c>
       <c r="U31">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.05478731610050417</v>
+        <v>0.05324731610050417</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.294638674256602</v>
+        <v>4.418846691537168</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.110607511659719</v>
+        <v>0.1098399334266137</v>
       </c>
       <c r="C32">
-        <v>40242.72444154971</v>
+        <v>40870.986554902</v>
       </c>
       <c r="D32">
-        <v>53199.74444154971</v>
+        <v>53828.006554902</v>
       </c>
       <c r="E32">
         <v>-5447.880000000001</v>
@@ -3917,45 +3917,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M32">
-        <v>1386.823210139226</v>
+        <v>1324.155778139226</v>
       </c>
       <c r="N32">
-        <v>4269.376789860773</v>
+        <v>4332.044221860773</v>
       </c>
       <c r="O32">
-        <v>1280.813036958232</v>
+        <v>1299.613266558232</v>
       </c>
       <c r="P32">
-        <v>2988.563752902541</v>
+        <v>3032.430955302541</v>
       </c>
       <c r="Q32">
-        <v>7279.663752902541</v>
+        <v>7323.530955302542</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1341104526136683</v>
+        <v>0.1340939122806606</v>
       </c>
       <c r="T32">
         <v>1.215398936811827</v>
       </c>
       <c r="U32">
-        <v>0.07966759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.05576731610050417</v>
+        <v>0.05324731610050417</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.078529951508498</v>
+        <v>4.271551801819262</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1105033914685387</v>
+        <v>0.1099276514054326</v>
       </c>
       <c r="C33">
-        <v>39748.07905396214</v>
+        <v>40217.10310122071</v>
       </c>
       <c r="D33">
-        <v>53285.35305396214</v>
+        <v>53754.37710122071</v>
       </c>
       <c r="E33">
         <v>-4867.626</v>
@@ -3999,37 +3999,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M33">
-        <v>1433.050650477201</v>
+        <v>1386.282178077201</v>
       </c>
       <c r="N33">
-        <v>4223.149349522799</v>
+        <v>4269.917821922798</v>
       </c>
       <c r="O33">
-        <v>1266.944804856839</v>
+        <v>1280.975346576839</v>
       </c>
       <c r="P33">
-        <v>2956.204544665959</v>
+        <v>2988.942475345959</v>
       </c>
       <c r="Q33">
-        <v>7247.30454466596</v>
+        <v>7280.042475345959</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1350949615614238</v>
+        <v>0.1350782368322845</v>
       </c>
       <c r="T33">
         <v>1.228948534769596</v>
       </c>
       <c r="U33">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.05576731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.946964469201773</v>
+        <v>4.080121702094774</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1103992712773583</v>
+        <v>0.1098053693842515</v>
       </c>
       <c r="C34">
-        <v>39253.70963187434</v>
+        <v>39739.54663960701</v>
       </c>
       <c r="D34">
-        <v>53371.23763187434</v>
+        <v>53857.07463960701</v>
       </c>
       <c r="E34">
         <v>-4287.371999999999</v>
@@ -4081,37 +4081,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M34">
-        <v>1479.278090815175</v>
+        <v>1431.000958015175</v>
       </c>
       <c r="N34">
-        <v>4176.921909184824</v>
+        <v>4225.199041984824</v>
       </c>
       <c r="O34">
-        <v>1253.076572755447</v>
+        <v>1267.559712595447</v>
       </c>
       <c r="P34">
-        <v>2923.845336429377</v>
+        <v>2957.639329389377</v>
       </c>
       <c r="Q34">
-        <v>7214.945336429378</v>
+        <v>7248.739329389377</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1361084266547015</v>
+        <v>0.1360915121060149</v>
       </c>
       <c r="T34">
         <v>1.242896650314357</v>
       </c>
       <c r="U34">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.05576731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.823621829539217</v>
+        <v>3.952617898904313</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.110295151086178</v>
+        <v>0.1096830873630704</v>
       </c>
       <c r="C35">
-        <v>38759.61751183234</v>
+        <v>39262.38333565308</v>
       </c>
       <c r="D35">
-        <v>53457.39951183235</v>
+        <v>53960.16533565309</v>
       </c>
       <c r="E35">
         <v>-3707.117999999999</v>
@@ -4163,37 +4163,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M35">
-        <v>1525.505531153149</v>
+        <v>1475.719737953149</v>
       </c>
       <c r="N35">
-        <v>4130.69446884685</v>
+        <v>4180.48026204685</v>
       </c>
       <c r="O35">
-        <v>1239.208340654055</v>
+        <v>1254.144078614055</v>
       </c>
       <c r="P35">
-        <v>2891.486128192795</v>
+        <v>2926.336183432795</v>
       </c>
       <c r="Q35">
-        <v>7182.586128192796</v>
+        <v>7217.436183432796</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1371521444373308</v>
+        <v>0.1371350344028418</v>
       </c>
       <c r="T35">
         <v>1.257261127517172</v>
       </c>
       <c r="U35">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.05576731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.707754501371362</v>
+        <v>3.832841598937515</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1101910308949976</v>
+        <v>0.1095608053418893</v>
       </c>
       <c r="C36">
-        <v>38265.80403902711</v>
+        <v>38785.61545138092</v>
       </c>
       <c r="D36">
-        <v>53543.84003902711</v>
+        <v>54063.65145138092</v>
       </c>
       <c r="E36">
         <v>-3126.863999999998</v>
@@ -4245,37 +4245,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M36">
-        <v>1571.732971491123</v>
+        <v>1520.438517891123</v>
       </c>
       <c r="N36">
-        <v>4084.467028508876</v>
+        <v>4135.761482108875</v>
       </c>
       <c r="O36">
-        <v>1225.340108552663</v>
+        <v>1240.728444632663</v>
       </c>
       <c r="P36">
-        <v>2859.126919956213</v>
+        <v>2895.033037476213</v>
       </c>
       <c r="Q36">
-        <v>7150.226919956213</v>
+        <v>7186.133037476213</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1382274900315549</v>
+        <v>0.1382101785874513</v>
       </c>
       <c r="T36">
         <v>1.27206089190795</v>
       </c>
       <c r="U36">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.05576731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.598702898389851</v>
+        <v>3.720110963674647</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1100869107038173</v>
+        <v>0.1094385233207082</v>
       </c>
       <c r="C37">
-        <v>37772.27056736419</v>
+        <v>38309.24526619837</v>
       </c>
       <c r="D37">
-        <v>53630.56056736419</v>
+        <v>54167.53526619838</v>
       </c>
       <c r="E37">
         <v>-2546.609999999997</v>
@@ -4327,37 +4327,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M37">
-        <v>1617.960411829098</v>
+        <v>1565.157297829098</v>
       </c>
       <c r="N37">
-        <v>4038.239588170901</v>
+        <v>4091.042702170901</v>
       </c>
       <c r="O37">
-        <v>1211.47187645127</v>
+        <v>1227.31281065127</v>
       </c>
       <c r="P37">
-        <v>2826.767711719631</v>
+        <v>2863.729891519631</v>
       </c>
       <c r="Q37">
-        <v>7117.867711719631</v>
+        <v>7154.829891519631</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1393359231825244</v>
+        <v>0.1393184041315873</v>
       </c>
       <c r="T37">
         <v>1.287316033664598</v>
       </c>
       <c r="U37">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.05576731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.495882815578712</v>
+        <v>3.613822078998228</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.109982790512637</v>
+        <v>0.1093162412995271</v>
       </c>
       <c r="C38">
-        <v>37279.01845953469</v>
+        <v>37833.27507706673</v>
       </c>
       <c r="D38">
-        <v>53717.56245953469</v>
+        <v>54271.81907706674</v>
       </c>
       <c r="E38">
         <v>-1966.356</v>
@@ -4409,37 +4409,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M38">
-        <v>1664.187852167072</v>
+        <v>1609.876077767072</v>
       </c>
       <c r="N38">
-        <v>3992.012147832927</v>
+        <v>4046.323922232928</v>
       </c>
       <c r="O38">
-        <v>1197.603644349878</v>
+        <v>1213.897176669878</v>
       </c>
       <c r="P38">
-        <v>2794.40850348305</v>
+        <v>2832.426745563049</v>
       </c>
       <c r="Q38">
-        <v>7085.50850348305</v>
+        <v>7123.526745563049</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1404789948694617</v>
+        <v>0.1404612617239775</v>
       </c>
       <c r="T38">
         <v>1.303047898601142</v>
       </c>
       <c r="U38">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.05576731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.398774959590415</v>
+        <v>3.51343813235939</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1098786703214566</v>
+        <v>0.109193959278346</v>
       </c>
       <c r="C39">
-        <v>36786.04908708658</v>
+        <v>37357.70719866991</v>
       </c>
       <c r="D39">
-        <v>53804.84708708659</v>
+        <v>54376.50519866991</v>
       </c>
       <c r="E39">
         <v>-1386.101999999999</v>
@@ -4491,37 +4491,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M39">
-        <v>1710.415292505046</v>
+        <v>1654.594857705046</v>
       </c>
       <c r="N39">
-        <v>3945.784707494953</v>
+        <v>4001.605142294953</v>
       </c>
       <c r="O39">
-        <v>1183.735412248486</v>
+        <v>1200.481542688486</v>
       </c>
       <c r="P39">
-        <v>2762.049295246467</v>
+        <v>2801.123599606467</v>
       </c>
       <c r="Q39">
-        <v>7053.149295246468</v>
+        <v>7092.223599606467</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1416583545464604</v>
+        <v>0.1416404005097769</v>
       </c>
       <c r="T39">
         <v>1.319279187821385</v>
       </c>
       <c r="U39">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.05576731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.306916176898782</v>
+        <v>3.418480344998325</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1097745501302763</v>
+        <v>0.1090716772571649</v>
       </c>
       <c r="C40">
-        <v>36293.36383049672</v>
+        <v>36882.54396358565</v>
       </c>
       <c r="D40">
-        <v>53892.41583049672</v>
+        <v>54481.59596358566</v>
       </c>
       <c r="E40">
         <v>-805.8479999999981</v>
@@ -4573,37 +4573,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M40">
-        <v>1756.64273284302</v>
+        <v>1699.31363764302</v>
       </c>
       <c r="N40">
-        <v>3899.557267156979</v>
+        <v>3956.886362356979</v>
       </c>
       <c r="O40">
-        <v>1169.867180147094</v>
+        <v>1187.065908707094</v>
       </c>
       <c r="P40">
-        <v>2729.690087009885</v>
+        <v>2769.820453649885</v>
       </c>
       <c r="Q40">
-        <v>7020.790087009886</v>
+        <v>7060.920453649886</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1428757580840075</v>
+        <v>0.1428575760306021</v>
       </c>
       <c r="T40">
         <v>1.336034067016475</v>
       </c>
       <c r="U40">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.05576731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.219892066980393</v>
+        <v>3.328520335919421</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1096704299390959</v>
+        <v>0.1089493952359838</v>
       </c>
       <c r="C41">
-        <v>35800.96407924363</v>
+        <v>36407.78772245893</v>
       </c>
       <c r="D41">
-        <v>53980.27007924364</v>
+        <v>54587.09372245894</v>
       </c>
       <c r="E41">
         <v>-225.5939999999973</v>
@@ -4655,37 +4655,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M41">
-        <v>1802.870173180994</v>
+        <v>1744.032417580994</v>
       </c>
       <c r="N41">
-        <v>3853.329826819005</v>
+        <v>3912.167582419004</v>
       </c>
       <c r="O41">
-        <v>1155.998948045701</v>
+        <v>1173.650274725701</v>
       </c>
       <c r="P41">
-        <v>2697.330878773303</v>
+        <v>2738.517307693303</v>
       </c>
       <c r="Q41">
-        <v>6988.430878773303</v>
+        <v>7029.617307693304</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1441330764916382</v>
+        <v>0.1441146589455527</v>
       </c>
       <c r="T41">
         <v>1.353338286513044</v>
       </c>
       <c r="U41">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.05576731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.137330731929614</v>
+        <v>3.243173660639436</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1095663097479156</v>
+        <v>0.1088271132148027</v>
       </c>
       <c r="C42">
-        <v>35308.85123188108</v>
+        <v>35933.44084417709</v>
       </c>
       <c r="D42">
-        <v>54068.41123188108</v>
+        <v>54693.0008441771</v>
       </c>
       <c r="E42">
         <v>354.6600000000035</v>
@@ -4737,37 +4737,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M42">
-        <v>1849.097613518969</v>
+        <v>1788.751197518969</v>
       </c>
       <c r="N42">
-        <v>3807.10238648103</v>
+        <v>3867.44880248103</v>
       </c>
       <c r="O42">
-        <v>1142.130715944309</v>
+        <v>1160.234640744309</v>
       </c>
       <c r="P42">
-        <v>2664.971670536721</v>
+        <v>2707.214161736722</v>
       </c>
       <c r="Q42">
-        <v>6956.071670536721</v>
+        <v>6998.314161736722</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1454323055128565</v>
+        <v>0.145413644624335</v>
       </c>
       <c r="T42">
         <v>1.371219313326164</v>
       </c>
       <c r="U42">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.05576731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.058897463631373</v>
+        <v>3.16209431912345</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1102083895567352</v>
+        <v>0.1087048311936216</v>
       </c>
       <c r="C43">
-        <v>34189.59547472073</v>
+        <v>35459.50571604719</v>
       </c>
       <c r="D43">
-        <v>53529.40947472073</v>
+        <v>54799.3197160472</v>
       </c>
       <c r="E43">
         <v>934.9140000000007</v>
@@ -4819,45 +4819,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M43">
-        <v>1957.180130256943</v>
+        <v>1833.469977456943</v>
       </c>
       <c r="N43">
-        <v>3699.019869743056</v>
+        <v>3822.730022543056</v>
       </c>
       <c r="O43">
-        <v>1109.705960922917</v>
+        <v>1146.819006762917</v>
       </c>
       <c r="P43">
-        <v>2589.313908820139</v>
+        <v>2675.91101578014</v>
       </c>
       <c r="Q43">
-        <v>6880.413908820139</v>
+        <v>6967.01101578014</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1467755761958111</v>
+        <v>0.1467566637159574</v>
       </c>
       <c r="T43">
         <v>1.389706476641425</v>
       </c>
       <c r="U43">
-        <v>0.08226759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.05758731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.889974158514189</v>
+        <v>3.084970067437513</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1101224693655549</v>
+        <v>0.1085825491724405</v>
       </c>
       <c r="C44">
-        <v>33680.84459239023</v>
+        <v>34985.98474397542</v>
       </c>
       <c r="D44">
-        <v>53600.91259239023</v>
+        <v>54906.05274397543</v>
       </c>
       <c r="E44">
         <v>1515.168000000001</v>
@@ -4901,45 +4901,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M44">
-        <v>2004.916230994917</v>
+        <v>1878.188757394917</v>
       </c>
       <c r="N44">
-        <v>3651.283769005082</v>
+        <v>3778.011242605082</v>
       </c>
       <c r="O44">
-        <v>1095.385130701525</v>
+        <v>1133.403372781524</v>
       </c>
       <c r="P44">
-        <v>2555.898638303557</v>
+        <v>2644.607869823557</v>
       </c>
       <c r="Q44">
-        <v>6846.998638303558</v>
+        <v>6935.707869823558</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1481651665574882</v>
+        <v>0.1481459938107392</v>
       </c>
       <c r="T44">
         <v>1.408831128346866</v>
       </c>
       <c r="U44">
-        <v>0.08226759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.05758731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.821165249978137</v>
+        <v>3.01151839916519</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1100365491743745</v>
+        <v>0.1092127671512594</v>
       </c>
       <c r="C45">
-        <v>33172.28498937407</v>
+        <v>33860.05543063208</v>
       </c>
       <c r="D45">
-        <v>53672.60698937407</v>
+        <v>54360.37743063208</v>
       </c>
       <c r="E45">
         <v>2095.421999999999</v>
@@ -4983,37 +4983,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M45">
-        <v>2052.652331732891</v>
+        <v>1985.284842332891</v>
       </c>
       <c r="N45">
-        <v>3603.547668267108</v>
+        <v>3670.915157667108</v>
       </c>
       <c r="O45">
-        <v>1081.064300480132</v>
+        <v>1101.274547300132</v>
       </c>
       <c r="P45">
-        <v>2522.483367786976</v>
+        <v>2569.640610366976</v>
       </c>
       <c r="Q45">
-        <v>6813.583367786976</v>
+        <v>6860.740610366976</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1496035144757153</v>
+        <v>0.1495840723298993</v>
       </c>
       <c r="T45">
         <v>1.428626820463025</v>
       </c>
       <c r="U45">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.05758731610050417</v>
+        <v>0.05569731610050417</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.755556755792599</v>
+        <v>2.849062199736259</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1099506289831942</v>
+        <v>0.1091079851300783</v>
       </c>
       <c r="C46">
-        <v>32663.91743424248</v>
+        <v>33369.77412850969</v>
       </c>
       <c r="D46">
-        <v>53744.49343424248</v>
+        <v>54450.35012850969</v>
       </c>
       <c r="E46">
         <v>2675.675999999999</v>
@@ -5065,37 +5065,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M46">
-        <v>2100.388432470866</v>
+        <v>2031.454257270865</v>
       </c>
       <c r="N46">
-        <v>3555.811567529133</v>
+        <v>3624.745742729134</v>
       </c>
       <c r="O46">
-        <v>1066.74347025874</v>
+        <v>1087.42372281874</v>
       </c>
       <c r="P46">
-        <v>2489.068097270393</v>
+        <v>2537.322019910393</v>
       </c>
       <c r="Q46">
-        <v>6780.168097270393</v>
+        <v>6828.422019910394</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1510932319624506</v>
+        <v>0.1510735107961723</v>
       </c>
       <c r="T46">
         <v>1.449129501583333</v>
       </c>
       <c r="U46">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.05758731610050417</v>
+        <v>0.05569731610050417</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.692930465888221</v>
+        <v>2.784310786105889</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1098647087920138</v>
+        <v>0.1090032031088972</v>
       </c>
       <c r="C47">
-        <v>32155.74269968882</v>
+        <v>32879.79115054401</v>
       </c>
       <c r="D47">
-        <v>53816.57269968882</v>
+        <v>54540.62115054402</v>
       </c>
       <c r="E47">
         <v>3255.93</v>
@@ -5147,37 +5147,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M47">
-        <v>2148.12453320884</v>
+        <v>2077.62367220884</v>
       </c>
       <c r="N47">
-        <v>3508.075466791159</v>
+        <v>3578.576327791159</v>
       </c>
       <c r="O47">
-        <v>1052.422640037348</v>
+        <v>1073.572898337348</v>
       </c>
       <c r="P47">
-        <v>2455.652826753811</v>
+        <v>2505.003429453812</v>
       </c>
       <c r="Q47">
-        <v>6746.752826753812</v>
+        <v>6796.103429453812</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1526371209941581</v>
+        <v>0.1526171106612188</v>
       </c>
       <c r="T47">
         <v>1.470377734744379</v>
       </c>
       <c r="U47">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.05758731610050417</v>
+        <v>0.05569731610050417</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.633087566646261</v>
+        <v>2.722437213081314</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1097787886008335</v>
+        <v>0.1088984210877161</v>
       </c>
       <c r="C48">
-        <v>31647.76156255713</v>
+        <v>32390.10798293746</v>
       </c>
       <c r="D48">
-        <v>53888.84556255713</v>
+        <v>54631.19198293746</v>
       </c>
       <c r="E48">
         <v>3836.184000000001</v>
@@ -5229,37 +5229,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M48">
-        <v>2195.860633946814</v>
+        <v>2123.793087146814</v>
       </c>
       <c r="N48">
-        <v>3460.339366053185</v>
+        <v>3532.406912853185</v>
       </c>
       <c r="O48">
-        <v>1038.101809815955</v>
+        <v>1059.722073855955</v>
       </c>
       <c r="P48">
-        <v>2422.237556237229</v>
+        <v>2472.68483899723</v>
       </c>
       <c r="Q48">
-        <v>6713.337556237229</v>
+        <v>6763.78483899723</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.154238191101114</v>
+        <v>0.1542178808916374</v>
       </c>
       <c r="T48">
         <v>1.492412939503982</v>
       </c>
       <c r="U48">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.05758731610050417</v>
+        <v>0.05569731610050417</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.575846532588733</v>
+        <v>2.663253795405633</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1096928684096532</v>
+        <v>0.108793639066535</v>
       </c>
       <c r="C49">
-        <v>31139.97480387011</v>
+        <v>31900.72612178087</v>
       </c>
       <c r="D49">
-        <v>53961.31280387012</v>
+        <v>54722.06412178087</v>
       </c>
       <c r="E49">
         <v>4416.438000000002</v>
@@ -5311,37 +5311,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M49">
-        <v>2243.596734684788</v>
+        <v>2169.962502084788</v>
       </c>
       <c r="N49">
-        <v>3412.603265315211</v>
+        <v>3486.237497915211</v>
       </c>
       <c r="O49">
-        <v>1023.780979594563</v>
+        <v>1045.871249374563</v>
       </c>
       <c r="P49">
-        <v>2388.822285720647</v>
+        <v>2440.366248540648</v>
       </c>
       <c r="Q49">
-        <v>6679.922285720648</v>
+        <v>6731.466248540648</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1558996789479551</v>
+        <v>0.1558790575458454</v>
       </c>
       <c r="T49">
         <v>1.515279661424325</v>
       </c>
       <c r="U49">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.05758731610050417</v>
+        <v>0.05569731610050417</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.521041287214505</v>
+        <v>2.606588821035301</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1105141482184728</v>
+        <v>0.1086888570453539</v>
       </c>
       <c r="C50">
-        <v>29874.90399204089</v>
+        <v>31411.64707313587</v>
       </c>
       <c r="D50">
-        <v>53276.49599204089</v>
+        <v>54813.23907313587</v>
       </c>
       <c r="E50">
         <v>4996.691999999999</v>
@@ -5393,45 +5393,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M50">
-        <v>2366.533753822762</v>
+        <v>2216.131917022762</v>
       </c>
       <c r="N50">
-        <v>3289.666246177237</v>
+        <v>3440.068082977237</v>
       </c>
       <c r="O50">
-        <v>986.8998738531709</v>
+        <v>1032.020424893171</v>
       </c>
       <c r="P50">
-        <v>2302.766372324066</v>
+        <v>2408.047658084066</v>
       </c>
       <c r="Q50">
-        <v>6593.866372324066</v>
+        <v>6699.147658084066</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1576250701735208</v>
+        <v>0.1576041256098306</v>
       </c>
       <c r="T50">
         <v>1.539025872649296</v>
       </c>
       <c r="U50">
-        <v>0.08496759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.05947731610050417</v>
+        <v>0.05569731610050417</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.390077889598363</v>
+        <v>2.552284887263732</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1104471280272925</v>
+        <v>0.1085840750241728</v>
       </c>
       <c r="C51">
-        <v>29349.88215866239</v>
+        <v>30922.87235311815</v>
       </c>
       <c r="D51">
-        <v>53331.72815866239</v>
+        <v>54904.71835311815</v>
       </c>
       <c r="E51">
         <v>5576.946</v>
@@ -5475,45 +5475,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M51">
-        <v>2415.836540360736</v>
+        <v>2262.301331960736</v>
       </c>
       <c r="N51">
-        <v>3240.363459639263</v>
+        <v>3393.898668039263</v>
       </c>
       <c r="O51">
-        <v>972.1090378917787</v>
+        <v>1018.169600411779</v>
       </c>
       <c r="P51">
-        <v>2268.254421747484</v>
+        <v>2375.729067627484</v>
       </c>
       <c r="Q51">
-        <v>6559.354421747485</v>
+        <v>6666.829067627485</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.159418123800089</v>
+        <v>0.1593968434018152</v>
       </c>
       <c r="T51">
         <v>1.563703307843874</v>
       </c>
       <c r="U51">
-        <v>0.08496759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.05947731610050417</v>
+        <v>0.05569731610050417</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.341300789810641</v>
+        <v>2.500197440584881</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1103801078361121</v>
+        <v>0.1097042930029917</v>
       </c>
       <c r="C52">
-        <v>28824.97496338193</v>
+        <v>29380.15949893333</v>
       </c>
       <c r="D52">
-        <v>53387.07496338193</v>
+        <v>53942.25949893333</v>
       </c>
       <c r="E52">
         <v>6157.200000000001</v>
@@ -5557,37 +5557,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M52">
-        <v>2465.139326898711</v>
+        <v>2410.015196898711</v>
       </c>
       <c r="N52">
-        <v>3191.060673101288</v>
+        <v>3246.184803101288</v>
       </c>
       <c r="O52">
-        <v>957.3182019303864</v>
+        <v>973.8554409303864</v>
       </c>
       <c r="P52">
-        <v>2233.742471170902</v>
+        <v>2272.329362170902</v>
       </c>
       <c r="Q52">
-        <v>6524.842471170902</v>
+        <v>6563.429362170902</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1612828995717201</v>
+        <v>0.1612612699054793</v>
       </c>
       <c r="T52">
         <v>1.589367840446236</v>
       </c>
       <c r="U52">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.05947731610050417</v>
+        <v>0.05814731610050417</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.294474774014428</v>
+        <v>2.346956154997939</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1119909876449318</v>
+        <v>0.1096240109818106</v>
       </c>
       <c r="C53">
-        <v>26945.44799329447</v>
+        <v>28867.75760589168</v>
       </c>
       <c r="D53">
-        <v>52087.80199329447</v>
+        <v>54010.11160589168</v>
       </c>
       <c r="E53">
         <v>6737.454000000002</v>
@@ -5639,45 +5639,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M53">
-        <v>2653.528997236685</v>
+        <v>2458.215500836685</v>
       </c>
       <c r="N53">
-        <v>3002.671002763314</v>
+        <v>3197.984499163314</v>
       </c>
       <c r="O53">
-        <v>900.8013008289942</v>
+        <v>959.3953497489941</v>
       </c>
       <c r="P53">
-        <v>2101.86970193432</v>
+        <v>2238.58914941432</v>
       </c>
       <c r="Q53">
-        <v>6392.96970193432</v>
+        <v>6529.68914941432</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1632237886401523</v>
+        <v>0.1632017954501092</v>
       </c>
       <c r="T53">
         <v>1.616079904991551</v>
       </c>
       <c r="U53">
-        <v>0.08966759442929167</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.06276731610050416</v>
+        <v>0.05814731610050417</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.131576480185525</v>
+        <v>2.300937406860724</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1119568674537514</v>
+        <v>0.1095437289606295</v>
       </c>
       <c r="C54">
-        <v>26392.05810930507</v>
+        <v>28355.5266254834</v>
       </c>
       <c r="D54">
-        <v>52114.66610930507</v>
+        <v>54078.13462548341</v>
       </c>
       <c r="E54">
         <v>7317.708000000002</v>
@@ -5721,45 +5721,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M54">
-        <v>2705.558977574659</v>
+        <v>2506.415804774659</v>
       </c>
       <c r="N54">
-        <v>2950.64102242534</v>
+        <v>3149.78419522534</v>
       </c>
       <c r="O54">
-        <v>885.1923067276018</v>
+        <v>944.9352585676019</v>
       </c>
       <c r="P54">
-        <v>2065.448715697737</v>
+        <v>2204.848936657738</v>
       </c>
       <c r="Q54">
-        <v>6356.548715697738</v>
+        <v>6495.948936657738</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1652455480864359</v>
+        <v>0.1652231762257653</v>
       </c>
       <c r="T54">
         <v>1.643904972226254</v>
       </c>
       <c r="U54">
-        <v>0.08966759442929167</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V54">
         <v>0.3</v>
       </c>
       <c r="W54">
-        <v>0.06276731610050416</v>
+        <v>0.05814731610050417</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.090584624797342</v>
+        <v>2.256688610574941</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1119227472625711</v>
+        <v>0.1105022469394484</v>
       </c>
       <c r="C55">
-        <v>25838.69594977697</v>
+        <v>26974.14334865899</v>
       </c>
       <c r="D55">
-        <v>52141.55794977698</v>
+        <v>53277.005348659</v>
       </c>
       <c r="E55">
         <v>7897.962000000003</v>
@@ -5803,37 +5803,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M55">
-        <v>2757.588957912633</v>
+        <v>2640.725802312634</v>
       </c>
       <c r="N55">
-        <v>2898.611042087366</v>
+        <v>3015.474197687365</v>
       </c>
       <c r="O55">
-        <v>869.5833126262097</v>
+        <v>904.6422593062096</v>
       </c>
       <c r="P55">
-        <v>2029.027729461156</v>
+        <v>2110.831938381156</v>
       </c>
       <c r="Q55">
-        <v>6320.127729461156</v>
+        <v>6401.931938381156</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1673533398495827</v>
+        <v>0.1673305732046409</v>
       </c>
       <c r="T55">
         <v>1.6729140848752</v>
       </c>
       <c r="U55">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.06276731610050416</v>
+        <v>0.06010731610050417</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.051139631876637</v>
+        <v>2.141911134827608</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1118886270713907</v>
+        <v>0.1104415649182673</v>
       </c>
       <c r="C56">
-        <v>25285.3615576509</v>
+        <v>26443.90293312467</v>
       </c>
       <c r="D56">
-        <v>52168.47755765091</v>
+        <v>53327.01893312467</v>
       </c>
       <c r="E56">
         <v>8478.216000000004</v>
@@ -5885,37 +5885,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M56">
-        <v>2809.618938250608</v>
+        <v>2690.550817450608</v>
       </c>
       <c r="N56">
-        <v>2846.581061749391</v>
+        <v>2965.649182549391</v>
       </c>
       <c r="O56">
-        <v>853.9743185248174</v>
+        <v>889.6947547648174</v>
       </c>
       <c r="P56">
-        <v>1992.606743224574</v>
+        <v>2075.954427784574</v>
       </c>
       <c r="Q56">
-        <v>6283.706743224574</v>
+        <v>6367.054427784575</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1695527747328663</v>
+        <v>0.1695295961391197</v>
       </c>
       <c r="T56">
         <v>1.703184463291491</v>
       </c>
       <c r="U56">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V56">
         <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.06276731610050416</v>
+        <v>0.06010731610050417</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.013155564619662</v>
+        <v>2.102246113812282</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1154350068802104</v>
+        <v>0.1103808828970862</v>
       </c>
       <c r="C57">
-        <v>22048.26520556242</v>
+        <v>25913.75650594278</v>
       </c>
       <c r="D57">
-        <v>49511.63520556243</v>
+        <v>53377.12650594279</v>
       </c>
       <c r="E57">
         <v>9058.470000000005</v>
@@ -5967,45 +5967,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M57">
-        <v>3158.448839588582</v>
+        <v>2740.375832588582</v>
       </c>
       <c r="N57">
-        <v>2497.751160411417</v>
+        <v>2915.824167411417</v>
       </c>
       <c r="O57">
-        <v>749.325348123425</v>
+        <v>874.7472502234251</v>
       </c>
       <c r="P57">
-        <v>1748.425812287991</v>
+        <v>2041.076917187992</v>
       </c>
       <c r="Q57">
-        <v>6039.525812287991</v>
+        <v>6332.176917187992</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1718499622776291</v>
+        <v>0.1718263534262421</v>
       </c>
       <c r="T57">
         <v>1.734800191859617</v>
       </c>
       <c r="U57">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.06927731610050417</v>
+        <v>0.06010731610050417</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.790815772952894</v>
+        <v>2.064023457197513</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.11546598668903</v>
+        <v>0.1103202008759051</v>
       </c>
       <c r="C58">
-        <v>21445.9938472228</v>
+        <v>25383.70433230488</v>
       </c>
       <c r="D58">
-        <v>49489.61784722281</v>
+        <v>53427.32833230489</v>
       </c>
       <c r="E58">
         <v>9638.724000000006</v>
@@ -6049,45 +6049,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M58">
-        <v>3215.875182126556</v>
+        <v>2790.200847726556</v>
       </c>
       <c r="N58">
-        <v>2440.324817873442</v>
+        <v>2865.999152273443</v>
       </c>
       <c r="O58">
-        <v>732.0974453620328</v>
+        <v>859.7997456820327</v>
       </c>
       <c r="P58">
-        <v>1708.22737251141</v>
+        <v>2006.19940659141</v>
       </c>
       <c r="Q58">
-        <v>5999.32737251141</v>
+        <v>6297.29940659141</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.174251567438063</v>
+        <v>0.17422750877187</v>
       </c>
       <c r="T58">
         <v>1.767852998999022</v>
       </c>
       <c r="U58">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V58">
         <v>0.3</v>
       </c>
       <c r="W58">
-        <v>0.06927731610050417</v>
+        <v>0.06010731610050417</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.75883691986445</v>
+        <v>2.027165895461843</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1173722664978497</v>
+        <v>0.113371718854724</v>
       </c>
       <c r="C59">
-        <v>19547.61672684912</v>
+        <v>22390.68866618825</v>
       </c>
       <c r="D59">
-        <v>48171.49472684912</v>
+        <v>51014.56666618826</v>
       </c>
       <c r="E59">
         <v>10218.978</v>
@@ -6131,45 +6131,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M59">
-        <v>3428.751571264531</v>
+        <v>3098.00679126453</v>
       </c>
       <c r="N59">
-        <v>2227.448428735468</v>
+        <v>2558.193208735468</v>
       </c>
       <c r="O59">
-        <v>668.2345286206404</v>
+        <v>767.4579626206405</v>
       </c>
       <c r="P59">
-        <v>1559.213900114828</v>
+        <v>1790.735246114828</v>
       </c>
       <c r="Q59">
-        <v>5850.313900114828</v>
+        <v>6081.835246114828</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1767648751640984</v>
+        <v>0.1767403457614806</v>
       </c>
       <c r="T59">
         <v>1.802443146005376</v>
       </c>
       <c r="U59">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V59">
         <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.07256731610050418</v>
+        <v>0.06556731610050417</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.649638325331917</v>
+        <v>1.825754551587434</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1174361463066693</v>
+        <v>0.1133656368335429</v>
       </c>
       <c r="C60">
-        <v>18924.40695616131</v>
+        <v>21815.02681819849</v>
       </c>
       <c r="D60">
-        <v>48128.5389561613</v>
+        <v>51019.15881819849</v>
       </c>
       <c r="E60">
         <v>10799.232</v>
@@ -6213,45 +6213,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M60">
-        <v>3488.905107602504</v>
+        <v>3152.357787602504</v>
       </c>
       <c r="N60">
-        <v>2167.294892397495</v>
+        <v>2503.842212397495</v>
       </c>
       <c r="O60">
-        <v>650.1884677192484</v>
+        <v>751.1526637192484</v>
       </c>
       <c r="P60">
-        <v>1517.106424678246</v>
+        <v>1752.689548678246</v>
       </c>
       <c r="Q60">
-        <v>5808.206424678247</v>
+        <v>6043.789548678247</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1793978642104212</v>
+        <v>0.1793728416553584</v>
       </c>
       <c r="T60">
         <v>1.838680442869175</v>
       </c>
       <c r="U60">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V60">
         <v>0.3</v>
       </c>
       <c r="W60">
-        <v>0.07256731610050418</v>
+        <v>0.06556731610050417</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.621196285239987</v>
+        <v>1.794276024835927</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.117500026115489</v>
+        <v>0.1133595548123618</v>
       </c>
       <c r="C61">
-        <v>18301.27372676833</v>
+        <v>21239.36579702193</v>
       </c>
       <c r="D61">
-        <v>48085.65972676832</v>
+        <v>51023.75179702193</v>
       </c>
       <c r="E61">
         <v>11379.486</v>
@@ -6295,45 +6295,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M61">
-        <v>3549.058643940479</v>
+        <v>3206.708783940478</v>
       </c>
       <c r="N61">
-        <v>2107.14135605952</v>
+        <v>2449.49121605952</v>
       </c>
       <c r="O61">
-        <v>632.142406817856</v>
+        <v>734.8473648178561</v>
       </c>
       <c r="P61">
-        <v>1474.998949241664</v>
+        <v>1714.643851241664</v>
       </c>
       <c r="Q61">
-        <v>5766.098949241665</v>
+        <v>6005.743851241665</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1821592917468086</v>
+        <v>0.1821337519830838</v>
       </c>
       <c r="T61">
         <v>1.87668541275072</v>
       </c>
       <c r="U61">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.07256731610050418</v>
+        <v>0.06556731610050417</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.593718382100326</v>
+        <v>1.763864566787861</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1175639059243087</v>
+        <v>0.1149914727911807</v>
       </c>
       <c r="C62">
-        <v>17678.21683427314</v>
+        <v>19455.68925743166</v>
       </c>
       <c r="D62">
-        <v>48042.85683427314</v>
+        <v>49820.32925743166</v>
       </c>
       <c r="E62">
         <v>11959.74</v>
@@ -6377,37 +6377,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M62">
-        <v>3609.212180278453</v>
+        <v>3396.839216278453</v>
       </c>
       <c r="N62">
-        <v>2046.987819721546</v>
+        <v>2259.360783721546</v>
       </c>
       <c r="O62">
-        <v>614.0963459164639</v>
+        <v>677.8082351164638</v>
       </c>
       <c r="P62">
-        <v>1432.891473805082</v>
+        <v>1581.552548605082</v>
       </c>
       <c r="Q62">
-        <v>5723.991473805083</v>
+        <v>5872.652548605083</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1850587906600154</v>
+        <v>0.1850327078271956</v>
       </c>
       <c r="T62">
         <v>1.916590631126343</v>
       </c>
       <c r="U62">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V62">
         <v>0.3</v>
       </c>
       <c r="W62">
-        <v>0.07256731610050418</v>
+        <v>0.06829731610050417</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.567156409065321</v>
+        <v>1.665136216307842</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1176277857331283</v>
+        <v>0.1150126907699996</v>
       </c>
       <c r="C63">
-        <v>17055.23607500581</v>
+        <v>18860.1622391575</v>
       </c>
       <c r="D63">
-        <v>48000.13007500581</v>
+        <v>49805.0562391575</v>
       </c>
       <c r="E63">
         <v>12539.994</v>
@@ -6459,37 +6459,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M63">
-        <v>3669.365716616427</v>
+        <v>3453.453203216427</v>
       </c>
       <c r="N63">
-        <v>1986.834283383572</v>
+        <v>2202.746796783572</v>
       </c>
       <c r="O63">
-        <v>596.0502850150715</v>
+        <v>660.8240390350716</v>
       </c>
       <c r="P63">
-        <v>1390.7839983685</v>
+        <v>1541.9227577485</v>
       </c>
       <c r="Q63">
-        <v>5681.883998368501</v>
+        <v>5833.0227577485</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1881069818251814</v>
+        <v>0.1880803280735694</v>
       </c>
       <c r="T63">
         <v>1.958542270957126</v>
       </c>
       <c r="U63">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V63">
         <v>0.3</v>
       </c>
       <c r="W63">
-        <v>0.07256731610050418</v>
+        <v>0.06829731610050417</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.541465320392119</v>
+        <v>1.637838901286402</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.117691665541948</v>
+        <v>0.1150339087488185</v>
       </c>
       <c r="C64">
-        <v>16432.33124602036</v>
+        <v>18264.64458226661</v>
       </c>
       <c r="D64">
-        <v>47957.47924602036</v>
+        <v>49789.79258226661</v>
       </c>
       <c r="E64">
         <v>13120.248</v>
@@ -6541,37 +6541,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M64">
-        <v>3729.519252954402</v>
+        <v>3510.067190154401</v>
       </c>
       <c r="N64">
-        <v>1926.680747045597</v>
+        <v>2146.132809845598</v>
       </c>
       <c r="O64">
-        <v>578.0042241136792</v>
+        <v>643.8398429536793</v>
       </c>
       <c r="P64">
-        <v>1348.676522931918</v>
+        <v>1502.292966891919</v>
       </c>
       <c r="Q64">
-        <v>5639.776522931918</v>
+        <v>5793.392966891919</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1913156041043036</v>
+        <v>0.191288349385542</v>
       </c>
       <c r="T64">
         <v>2.002701891831634</v>
       </c>
       <c r="U64">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V64">
         <v>0.3</v>
       </c>
       <c r="W64">
-        <v>0.07256731610050418</v>
+        <v>0.06829731610050417</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.516602976514827</v>
+        <v>1.611422144814041</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1249438453507676</v>
+        <v>0.1150551267276374</v>
       </c>
       <c r="C65">
-        <v>11457.59450224622</v>
+        <v>17669.13627815477</v>
       </c>
       <c r="D65">
-        <v>43562.99650224622</v>
+        <v>49774.53827815477</v>
       </c>
       <c r="E65">
         <v>13700.502</v>
@@ -6623,45 +6623,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M65">
-        <v>4385.535621892376</v>
+        <v>3566.681177092375</v>
       </c>
       <c r="N65">
-        <v>1270.664378107623</v>
+        <v>2089.518822907623</v>
       </c>
       <c r="O65">
-        <v>381.1993134322868</v>
+        <v>626.855646872287</v>
       </c>
       <c r="P65">
-        <v>889.465064675336</v>
+        <v>1462.663176035336</v>
       </c>
       <c r="Q65">
-        <v>5180.565064675337</v>
+        <v>5753.763176035337</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1946976654255405</v>
+        <v>0.1946697772549184</v>
       </c>
       <c r="T65">
         <v>2.0492485192399</v>
       </c>
       <c r="U65">
-        <v>0.1199675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.08397731610050418</v>
+        <v>0.06829731610050417</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.289739837424767</v>
+        <v>1.585844015531278</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1251218251595873</v>
+        <v>0.1150763447064563</v>
       </c>
       <c r="C66">
-        <v>10779.59522503555</v>
+        <v>17073.63731822823</v>
       </c>
       <c r="D66">
-        <v>43465.25122503555</v>
+        <v>49759.29331822824</v>
       </c>
       <c r="E66">
         <v>14280.756</v>
@@ -6705,45 +6705,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M66">
-        <v>4455.147298430351</v>
+        <v>3623.29516403035</v>
       </c>
       <c r="N66">
-        <v>1201.052701569648</v>
+        <v>2032.904835969649</v>
       </c>
       <c r="O66">
-        <v>360.3158104708944</v>
+        <v>609.8714507908946</v>
       </c>
       <c r="P66">
-        <v>840.7368910987536</v>
+        <v>1423.033385178754</v>
       </c>
       <c r="Q66">
-        <v>5131.836891098754</v>
+        <v>5714.133385178755</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1982676190424016</v>
+        <v>0.1982390622281491</v>
       </c>
       <c r="T66">
         <v>2.098381070393069</v>
       </c>
       <c r="U66">
-        <v>0.1199675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.08397731610050418</v>
+        <v>0.06829731610050417</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.269587652465005</v>
+        <v>1.561065202788602</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1252998049684069</v>
+        <v>0.1150975626852753</v>
       </c>
       <c r="C67">
-        <v>10102.03360137025</v>
+        <v>16478.14769390381</v>
       </c>
       <c r="D67">
-        <v>43367.94360137025</v>
+        <v>49744.05769390381</v>
       </c>
       <c r="E67">
         <v>14861.01</v>
@@ -6787,45 +6787,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M67">
-        <v>4524.758974968325</v>
+        <v>3679.909150968324</v>
       </c>
       <c r="N67">
-        <v>1131.441025031674</v>
+        <v>1976.290849031675</v>
       </c>
       <c r="O67">
-        <v>339.4323075095022</v>
+        <v>592.8872547095025</v>
       </c>
       <c r="P67">
-        <v>792.008717522172</v>
+        <v>1383.403594322172</v>
       </c>
       <c r="Q67">
-        <v>5083.108717522173</v>
+        <v>5674.503594322173</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2020415700087977</v>
+        <v>0.2020123063427073</v>
       </c>
       <c r="T67">
         <v>2.150321195897849</v>
       </c>
       <c r="U67">
-        <v>0.1199675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V67">
         <v>0.3</v>
       </c>
       <c r="W67">
-        <v>0.08397731610050418</v>
+        <v>0.06829731610050417</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.250055534734774</v>
+        <v>1.537048815053393</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1420081583213691</v>
+        <v>0.1151187806640941</v>
       </c>
       <c r="C68">
-        <v>1990.121803051436</v>
+        <v>15882.66739660886</v>
       </c>
       <c r="D68">
-        <v>35836.28580305144</v>
+        <v>49728.83139660887</v>
       </c>
       <c r="E68">
         <v>15441.264</v>
@@ -6869,45 +6869,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M68">
-        <v>5846.674834306298</v>
+        <v>3736.523137906298</v>
       </c>
       <c r="N68">
-        <v>-190.4748343062993</v>
+        <v>1919.6768620937</v>
       </c>
       <c r="O68">
-        <v>-57.14245029188978</v>
+        <v>575.9030586281101</v>
       </c>
       <c r="P68">
-        <v>-133.3323840144095</v>
+        <v>1343.77380346559</v>
       </c>
       <c r="Q68">
-        <v>4157.767615985591</v>
+        <v>5634.873803465591</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2073263126530631</v>
+        <v>0.2060075059934159</v>
       </c>
       <c r="T68">
-        <v>2.223054042362391</v>
+        <v>2.205316622902909</v>
       </c>
       <c r="U68">
-        <v>0.1526675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V68">
-        <v>0.2902265044813853</v>
+        <v>0.3</v>
       </c>
       <c r="W68">
-        <v>0.1083594121504965</v>
+        <v>0.06829731610050417</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.9674216816046177</v>
+        <v>1.513760196643493</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1430768342656621</v>
+        <v>0.121799798642913</v>
       </c>
       <c r="C69">
-        <v>1016.173077481551</v>
+        <v>10930.83317456864</v>
       </c>
       <c r="D69">
-        <v>35442.59107748156</v>
+        <v>45357.25117456865</v>
       </c>
       <c r="E69">
         <v>16021.518</v>
@@ -6951,45 +6951,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M69">
-        <v>5935.260816644272</v>
+        <v>4345.190780444273</v>
       </c>
       <c r="N69">
-        <v>-279.0608166442735</v>
+        <v>1311.009219555726</v>
       </c>
       <c r="O69">
-        <v>-83.71824499328204</v>
+        <v>393.3027658667179</v>
       </c>
       <c r="P69">
-        <v>-195.3425716509914</v>
+        <v>917.7064536890084</v>
       </c>
       <c r="Q69">
-        <v>4095.757428349009</v>
+        <v>5208.806453689009</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2122210494001256</v>
+        <v>0.2102448389562886</v>
       </c>
       <c r="T69">
-        <v>2.290419316373373</v>
+        <v>2.263645106090094</v>
       </c>
       <c r="U69">
-        <v>0.1526675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V69">
-        <v>0.2858947656085288</v>
+        <v>0.3</v>
       </c>
       <c r="W69">
-        <v>0.1090207283039114</v>
+        <v>0.07823731610050418</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.9529825520284294</v>
+        <v>1.301714996141477</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.144145510209955</v>
+        <v>0.121920416621732</v>
       </c>
       <c r="C70">
-        <v>50.7805550715857</v>
+        <v>10278.70752430371</v>
       </c>
       <c r="D70">
-        <v>35057.45255507159</v>
+        <v>45285.37952430372</v>
       </c>
       <c r="E70">
         <v>16601.772</v>
@@ -7033,45 +7033,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M70">
-        <v>6023.846798982247</v>
+        <v>4410.044374182247</v>
       </c>
       <c r="N70">
-        <v>-367.6467989822486</v>
+        <v>1246.155625817752</v>
       </c>
       <c r="O70">
-        <v>-110.2940396946746</v>
+        <v>373.8466877453255</v>
       </c>
       <c r="P70">
-        <v>-257.352759287574</v>
+        <v>872.3089380724261</v>
       </c>
       <c r="Q70">
-        <v>4033.747240712426</v>
+        <v>5163.408938072426</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2174217071938795</v>
+        <v>0.214747005229341</v>
       </c>
       <c r="T70">
-        <v>2.361994920010041</v>
+        <v>2.325619119476478</v>
       </c>
       <c r="U70">
-        <v>0.1526675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V70">
-        <v>0.281690430820168</v>
+        <v>0.3</v>
       </c>
       <c r="W70">
-        <v>0.1096625939822258</v>
+        <v>0.07823731610050418</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.9389681027338935</v>
+        <v>1.282572128551161</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1452141861542479</v>
+        <v>0.1220410346005509</v>
       </c>
       <c r="C71">
-        <v>-906.3316948733991</v>
+        <v>9626.809284730014</v>
       </c>
       <c r="D71">
-        <v>34680.59430512661</v>
+        <v>45213.73528473002</v>
       </c>
       <c r="E71">
         <v>17182.02600000001</v>
@@ -7115,45 +7115,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M71">
-        <v>6112.432781320222</v>
+        <v>4474.897967920221</v>
       </c>
       <c r="N71">
-        <v>-456.2327813202228</v>
+        <v>1181.302032079778</v>
       </c>
       <c r="O71">
-        <v>-136.8698343960668</v>
+        <v>354.3906096239333</v>
       </c>
       <c r="P71">
-        <v>-319.3629469241559</v>
+        <v>826.9114224558444</v>
       </c>
       <c r="Q71">
-        <v>3971.737053075844</v>
+        <v>5118.011422455845</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2229578912969079</v>
+        <v>0.2195396338425903</v>
       </c>
       <c r="T71">
-        <v>2.438188304526494</v>
+        <v>2.391591456307145</v>
       </c>
       <c r="U71">
-        <v>0.1526675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V71">
-        <v>0.2776079608082816</v>
+        <v>0.3</v>
       </c>
       <c r="W71">
-        <v>0.1102858548582702</v>
+        <v>0.07823731610050418</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.9253598693609386</v>
+        <v>1.263984126688101</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1462828620985408</v>
+        <v>0.1365225711411666</v>
       </c>
       <c r="C72">
-        <v>-1855.427864509504</v>
+        <v>1829.339641175182</v>
       </c>
       <c r="D72">
-        <v>34311.7521354905</v>
+        <v>37996.51964117519</v>
       </c>
       <c r="E72">
         <v>17762.28000000001</v>
@@ -7197,37 +7197,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M72">
-        <v>6201.018763658196</v>
+        <v>5701.420069658197</v>
       </c>
       <c r="N72">
-        <v>-544.818763658197</v>
+        <v>-45.22006965819764</v>
       </c>
       <c r="O72">
-        <v>-163.4456290974591</v>
+        <v>-13.56602089745929</v>
       </c>
       <c r="P72">
-        <v>-381.3731345607379</v>
+        <v>-31.65404876073835</v>
       </c>
       <c r="Q72">
-        <v>3909.726865439262</v>
+        <v>4259.445951239262</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2288631543401382</v>
+        <v>0.2250288511488905</v>
       </c>
       <c r="T72">
-        <v>2.51946124801071</v>
+        <v>2.467152598697113</v>
       </c>
       <c r="U72">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V72">
-        <v>0.2736421327967347</v>
+        <v>0.2976205891283726</v>
       </c>
       <c r="W72">
-        <v>0.1108913082807134</v>
+        <v>0.09859130828071344</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9121404426557823</v>
+        <v>0.9920686304279087</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1473515380428337</v>
+        <v>0.1374682470854594</v>
       </c>
       <c r="C73">
-        <v>-2796.761025105501</v>
+        <v>857.1026401474373</v>
       </c>
       <c r="D73">
-        <v>33950.6729748945</v>
+        <v>37604.53664014744</v>
       </c>
       <c r="E73">
         <v>18342.534</v>
@@ -7279,37 +7279,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M73">
-        <v>6289.604745996169</v>
+        <v>5782.86892779617</v>
       </c>
       <c r="N73">
-        <v>-633.4047459961703</v>
+        <v>-126.6689277961714</v>
       </c>
       <c r="O73">
-        <v>-190.0214237988511</v>
+        <v>-38.00067833885141</v>
       </c>
       <c r="P73">
-        <v>-443.3833221973192</v>
+        <v>-88.66824945731997</v>
       </c>
       <c r="Q73">
-        <v>3847.716677802681</v>
+        <v>4202.431750542681</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2351756769035911</v>
+        <v>0.2312091563609211</v>
       </c>
       <c r="T73">
-        <v>2.606339222080044</v>
+        <v>2.552226826238392</v>
       </c>
       <c r="U73">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V73">
-        <v>0.2697880182503019</v>
+        <v>0.2934287498448744</v>
       </c>
       <c r="W73">
-        <v>0.1114797066771722</v>
+        <v>0.09917970667717227</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8992933941676728</v>
+        <v>0.9780958328162481</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1484202139871267</v>
+        <v>0.1384139230297524</v>
       </c>
       <c r="C74">
-        <v>-3730.573706101597</v>
+        <v>-107.1293248659276</v>
       </c>
       <c r="D74">
-        <v>33597.1142938984</v>
+        <v>37220.55867513407</v>
       </c>
       <c r="E74">
         <v>18922.788</v>
@@ -7361,37 +7361,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M74">
-        <v>6378.190728334143</v>
+        <v>5864.317785934144</v>
       </c>
       <c r="N74">
-        <v>-721.9907283341445</v>
+        <v>-208.1177859341451</v>
       </c>
       <c r="O74">
-        <v>-216.5972185002433</v>
+        <v>-62.43533578024353</v>
       </c>
       <c r="P74">
-        <v>-505.3935098339011</v>
+        <v>-145.6824501539016</v>
       </c>
       <c r="Q74">
-        <v>3785.706490166099</v>
+        <v>4145.417549846099</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2419390939358623</v>
+        <v>0.2378309119452397</v>
       </c>
       <c r="T74">
-        <v>2.699422765725761</v>
+        <v>2.643377784318334</v>
       </c>
       <c r="U74">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V74">
-        <v>0.2660409624412699</v>
+        <v>0.2893533505414734</v>
       </c>
       <c r="W74">
-        <v>0.1120517606737295</v>
+        <v>0.0997517606737295</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8868032081375663</v>
+        <v>0.964511168471578</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1494888899314196</v>
+        <v>0.1393595989740453</v>
       </c>
       <c r="C75">
-        <v>-4657.098438359375</v>
+        <v>-1063.598992292864</v>
       </c>
       <c r="D75">
-        <v>33250.84356164063</v>
+        <v>36844.34300770714</v>
       </c>
       <c r="E75">
         <v>19503.042</v>
@@ -7443,37 +7443,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M75">
-        <v>6466.776710672118</v>
+        <v>5945.766644072119</v>
       </c>
       <c r="N75">
-        <v>-810.5767106721187</v>
+        <v>-289.5666440721197</v>
       </c>
       <c r="O75">
-        <v>-243.1730132016356</v>
+        <v>-86.86999322163592</v>
       </c>
       <c r="P75">
-        <v>-567.4036974704831</v>
+        <v>-202.6966508504838</v>
       </c>
       <c r="Q75">
-        <v>3723.696302529517</v>
+        <v>4088.403349149517</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2492035048223757</v>
+        <v>0.2449431679432116</v>
       </c>
       <c r="T75">
-        <v>2.799401386678566</v>
+        <v>2.741280665219013</v>
       </c>
       <c r="U75">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V75">
-        <v>0.2623965656954991</v>
+        <v>0.285389606013508</v>
       </c>
       <c r="W75">
-        <v>0.1126081419580522</v>
+        <v>0.1003081419580523</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8746552189849969</v>
+        <v>0.9512986867116934</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1505575658757125</v>
+        <v>0.1403052749183382</v>
       </c>
       <c r="C76">
-        <v>-5576.558264160361</v>
+        <v>-2012.539384621487</v>
       </c>
       <c r="D76">
-        <v>32911.63773583964</v>
+        <v>36475.65661537852</v>
       </c>
       <c r="E76">
         <v>20083.296</v>
@@ -7525,37 +7525,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M76">
-        <v>6555.362693010092</v>
+        <v>6027.215502210093</v>
       </c>
       <c r="N76">
-        <v>-899.1626930100929</v>
+        <v>-371.0155022100944</v>
       </c>
       <c r="O76">
-        <v>-269.7488079030279</v>
+        <v>-111.3046506630283</v>
       </c>
       <c r="P76">
-        <v>-629.413885107065</v>
+        <v>-259.7108515470661</v>
       </c>
       <c r="Q76">
-        <v>3661.686114892936</v>
+        <v>4031.389148452934</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2570267165463132</v>
+        <v>0.252602520556412</v>
       </c>
       <c r="T76">
-        <v>2.907070670781588</v>
+        <v>2.846714536958206</v>
       </c>
       <c r="U76">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V76">
-        <v>0.2588506661590734</v>
+        <v>0.2815329897160281</v>
       </c>
       <c r="W76">
-        <v>0.1131494859103663</v>
+        <v>0.1008494859103663</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.862835553863578</v>
+        <v>0.9384432990534272</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1516262418200054</v>
+        <v>0.1412509508626311</v>
       </c>
       <c r="C77">
-        <v>-6489.167216303489</v>
+        <v>-2954.174289701135</v>
       </c>
       <c r="D77">
-        <v>32579.28278369652</v>
+        <v>36114.27571029887</v>
       </c>
       <c r="E77">
         <v>20663.55</v>
@@ -7607,37 +7607,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M77">
-        <v>6643.948675348066</v>
+        <v>6108.664360348067</v>
       </c>
       <c r="N77">
-        <v>-987.7486753480671</v>
+        <v>-452.4643603480681</v>
       </c>
       <c r="O77">
-        <v>-296.3246026044201</v>
+        <v>-135.7393081044204</v>
       </c>
       <c r="P77">
-        <v>-691.424072743647</v>
+        <v>-316.7250522436477</v>
       </c>
       <c r="Q77">
-        <v>3599.675927256353</v>
+        <v>3974.374947756352</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2654757852081657</v>
+        <v>0.2608746213786685</v>
       </c>
       <c r="T77">
-        <v>3.023353497612852</v>
+        <v>2.960583118436534</v>
       </c>
       <c r="U77">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V77">
-        <v>0.2553993239436191</v>
+        <v>0.2777792165198145</v>
       </c>
       <c r="W77">
-        <v>0.113676394023952</v>
+        <v>0.101376394023952</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8513310798120637</v>
+        <v>0.9259307217327148</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1526949177642983</v>
+        <v>0.142196626806924</v>
       </c>
       <c r="C78">
-        <v>-7395.130768464085</v>
+        <v>-3888.718713713562</v>
       </c>
       <c r="D78">
-        <v>32253.57323153592</v>
+        <v>35759.98528628644</v>
       </c>
       <c r="E78">
         <v>21243.804</v>
@@ -7689,37 +7689,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M78">
-        <v>6732.534657686041</v>
+        <v>6190.113218486042</v>
       </c>
       <c r="N78">
-        <v>-1076.334657686042</v>
+        <v>-533.9132184860428</v>
       </c>
       <c r="O78">
-        <v>-322.9003973058126</v>
+        <v>-160.1739655458128</v>
       </c>
       <c r="P78">
-        <v>-753.4342603802295</v>
+        <v>-373.7392529402299</v>
       </c>
       <c r="Q78">
-        <v>3537.665739619771</v>
+        <v>3917.36074705977</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2746289429251726</v>
+        <v>0.269836063936113</v>
       </c>
       <c r="T78">
-        <v>3.149326560013388</v>
+        <v>3.083940748371391</v>
       </c>
       <c r="U78">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V78">
-        <v>0.2520388065233083</v>
+        <v>0.2741242268287643</v>
       </c>
       <c r="W78">
-        <v>0.1141894361345485</v>
+        <v>0.1018894361345486</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8401293550776943</v>
+        <v>0.9137474227625475</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1537635937085912</v>
+        <v>0.1431423027512169</v>
       </c>
       <c r="C79">
-        <v>-8294.646258805602</v>
+        <v>-4816.379307740201</v>
       </c>
       <c r="D79">
-        <v>31934.3117411944</v>
+        <v>35412.57869225981</v>
       </c>
       <c r="E79">
         <v>21824.058</v>
@@ -7771,37 +7771,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M79">
-        <v>6821.120640024015</v>
+        <v>6271.562076624016</v>
       </c>
       <c r="N79">
-        <v>-1164.920640024016</v>
+        <v>-615.3620766240174</v>
       </c>
       <c r="O79">
-        <v>-349.4761920072049</v>
+        <v>-184.6086229872052</v>
       </c>
       <c r="P79">
-        <v>-815.4444480168115</v>
+        <v>-430.7534536368122</v>
       </c>
       <c r="Q79">
-        <v>3475.655551983189</v>
+        <v>3860.346546363188</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2845780274001801</v>
+        <v>0.279576762368118</v>
       </c>
       <c r="T79">
-        <v>3.2862538017531</v>
+        <v>3.218025128735364</v>
       </c>
       <c r="U79">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V79">
-        <v>0.2487655752697588</v>
+        <v>0.2705641719348842</v>
       </c>
       <c r="W79">
-        <v>0.1146891524760387</v>
+        <v>0.1023891524760387</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8292185842325295</v>
+        <v>0.9018805731162807</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1548322696528842</v>
+        <v>0.1440879786955099</v>
       </c>
       <c r="C80">
-        <v>-9187.903288679372</v>
+        <v>-5737.354769704507</v>
       </c>
       <c r="D80">
-        <v>31621.30871132063</v>
+        <v>35071.8572302955</v>
       </c>
       <c r="E80">
         <v>22404.31200000001</v>
@@ -7853,37 +7853,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M80">
-        <v>6909.70662236199</v>
+        <v>6353.01093476199</v>
       </c>
       <c r="N80">
-        <v>-1253.506622361991</v>
+        <v>-696.8109347619911</v>
       </c>
       <c r="O80">
-        <v>-376.0519867085972</v>
+        <v>-209.0432804285973</v>
       </c>
       <c r="P80">
-        <v>-877.4546356533934</v>
+        <v>-487.7676543333938</v>
       </c>
       <c r="Q80">
-        <v>3413.645364346607</v>
+        <v>3803.332345666607</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2954315741001883</v>
+        <v>0.2902029788393961</v>
       </c>
       <c r="T80">
-        <v>3.435628974560059</v>
+        <v>3.364298998223335</v>
       </c>
       <c r="U80">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V80">
-        <v>0.2455762730227106</v>
+        <v>0.2670954004998216</v>
       </c>
       <c r="W80">
-        <v>0.1151760555780035</v>
+        <v>0.1028760555780035</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8185875767423688</v>
+        <v>0.890318001666072</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1559009455971771</v>
+        <v>0.1450336546398028</v>
       </c>
       <c r="C81">
-        <v>-10075.08409810465</v>
+        <v>-6651.836223331542</v>
       </c>
       <c r="D81">
-        <v>31314.38190189535</v>
+        <v>34737.62977666847</v>
       </c>
       <c r="E81">
         <v>22984.56600000001</v>
@@ -7935,37 +7935,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M81">
-        <v>6998.292604699964</v>
+        <v>6434.459792899965</v>
       </c>
       <c r="N81">
-        <v>-1342.092604699965</v>
+        <v>-778.2597928999658</v>
       </c>
       <c r="O81">
-        <v>-402.6277814099894</v>
+        <v>-233.4779378699897</v>
       </c>
       <c r="P81">
-        <v>-939.4648232899754</v>
+        <v>-544.781855029976</v>
       </c>
       <c r="Q81">
-        <v>3351.635176710025</v>
+        <v>3746.318144970024</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3073187919144831</v>
+        <v>0.3018412159269864</v>
       </c>
       <c r="T81">
-        <v>3.599230354301015</v>
+        <v>3.524503712424447</v>
       </c>
       <c r="U81">
-        <v>0.1526675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V81">
-        <v>0.2424677126047016</v>
+        <v>0.2637144460631149</v>
       </c>
       <c r="W81">
-        <v>0.115650632019159</v>
+        <v>0.1033506320191591</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8082257086823388</v>
+        <v>0.8790481535437166</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1854250496935912</v>
+        <v>0.1459793305840957</v>
       </c>
       <c r="C82">
-        <v>-17276.85102157587</v>
+        <v>-7560.00757564378</v>
       </c>
       <c r="D82">
-        <v>24692.86897842414</v>
+        <v>34409.71242435623</v>
       </c>
       <c r="E82">
         <v>23564.82000000001</v>
@@ -8017,45 +8017,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M82">
-        <v>8604.823051037938</v>
+        <v>6515.908651037939</v>
       </c>
       <c r="N82">
-        <v>-2948.623051037939</v>
+        <v>-859.7086510379404</v>
       </c>
       <c r="O82">
-        <v>-884.5869153113817</v>
+        <v>-257.9125953113821</v>
       </c>
       <c r="P82">
-        <v>-2064.036135726557</v>
+        <v>-601.7960557265583</v>
       </c>
       <c r="Q82">
-        <v>2227.063864273443</v>
+        <v>3689.303944273442</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3318718722708132</v>
+        <v>0.3146432767233357</v>
       </c>
       <c r="T82">
-        <v>3.937149444027435</v>
+        <v>3.700728898045669</v>
       </c>
       <c r="U82">
-        <v>0.1853675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V82">
-        <v>0.1971987093674541</v>
+        <v>0.260418015487326</v>
       </c>
       <c r="W82">
-        <v>0.1488133440492857</v>
+        <v>0.1038133440492857</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.6573290312248469</v>
+        <v>0.8680600516244201</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2314574827454869</v>
+        <v>0.1469250065283886</v>
       </c>
       <c r="C83">
-        <v>-23979.52368900323</v>
+        <v>-8462.045854397962</v>
       </c>
       <c r="D83">
-        <v>18570.45031099678</v>
+        <v>34087.92814560205</v>
       </c>
       <c r="E83">
         <v>24145.07400000001</v>
@@ -8099,45 +8099,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M83">
-        <v>11165.81330197592</v>
+        <v>6597.357509175913</v>
       </c>
       <c r="N83">
-        <v>-5509.613301975916</v>
+        <v>-941.1575091759141</v>
       </c>
       <c r="O83">
-        <v>-1652.883990592775</v>
+        <v>-282.3472527527742</v>
       </c>
       <c r="P83">
-        <v>-3856.729311383142</v>
+        <v>-658.8102564231399</v>
       </c>
       <c r="Q83">
-        <v>434.3706886168588</v>
+        <v>3632.28974357686</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3593217450619232</v>
+        <v>0.3287929228666691</v>
       </c>
       <c r="T83">
-        <v>4.314936503413103</v>
+        <v>3.895504103205967</v>
       </c>
       <c r="U83">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V83">
-        <v>0.1519692255377153</v>
+        <v>0.2572029782590874</v>
       </c>
       <c r="W83">
-        <v>0.2014646310910142</v>
+        <v>0.1042646310910142</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5065640851257177</v>
+        <v>0.8573432608636249</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2333751586897798</v>
+        <v>0.1478706824726815</v>
       </c>
       <c r="C84">
-        <v>-24749.63281739462</v>
+        <v>-9358.12152676416</v>
       </c>
       <c r="D84">
-        <v>18380.59518260538</v>
+        <v>33772.10647323584</v>
       </c>
       <c r="E84">
         <v>24725.328</v>
@@ -8181,45 +8181,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M84">
-        <v>11303.66284891389</v>
+        <v>6678.806367313887</v>
       </c>
       <c r="N84">
-        <v>-5647.462848913889</v>
+        <v>-1022.606367313888</v>
       </c>
       <c r="O84">
-        <v>-1694.238854674167</v>
+        <v>-306.7819101941664</v>
       </c>
       <c r="P84">
-        <v>-3953.223994239722</v>
+        <v>-715.8244571197215</v>
       </c>
       <c r="Q84">
-        <v>337.8760057602785</v>
+        <v>3575.275542880279</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3767396197875856</v>
+        <v>0.3445147519148175</v>
       </c>
       <c r="T84">
-        <v>4.554655198047164</v>
+        <v>4.111920997828522</v>
       </c>
       <c r="U84">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V84">
-        <v>0.1501159422994505</v>
+        <v>0.254066356573001</v>
       </c>
       <c r="W84">
-        <v>0.2019049111317249</v>
+        <v>0.1047049111317249</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.5003864743315017</v>
+        <v>0.8468878552433368</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2352928346340727</v>
+        <v>0.1488163584169744</v>
       </c>
       <c r="C85">
-        <v>-25515.89926103945</v>
+        <v>-10248.39880045207</v>
       </c>
       <c r="D85">
-        <v>18194.58273896055</v>
+        <v>33462.08319954793</v>
       </c>
       <c r="E85">
         <v>25305.582</v>
@@ -8263,45 +8263,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M85">
-        <v>11441.51239585186</v>
+        <v>6760.255225451861</v>
       </c>
       <c r="N85">
-        <v>-5785.312395851863</v>
+        <v>-1104.055225451862</v>
       </c>
       <c r="O85">
-        <v>-1735.593718755559</v>
+        <v>-331.2165676355588</v>
       </c>
       <c r="P85">
-        <v>-4049.718677096304</v>
+        <v>-772.8386578163038</v>
       </c>
       <c r="Q85">
-        <v>241.3813229036964</v>
+        <v>3518.261342183697</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3962066562456789</v>
+        <v>0.3620862079098067</v>
       </c>
       <c r="T85">
-        <v>4.822576092049938</v>
+        <v>4.35379870358314</v>
       </c>
       <c r="U85">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V85">
-        <v>0.1483073164886138</v>
+        <v>0.2510053161323624</v>
       </c>
       <c r="W85">
-        <v>0.2023345820148281</v>
+        <v>0.1051345820148281</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.4943577216287126</v>
+        <v>0.8366843871078748</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2372105105783656</v>
+        <v>0.1497620343612674</v>
       </c>
       <c r="C86">
-        <v>-26278.43851554049</v>
+        <v>-11133.03590840259</v>
       </c>
       <c r="D86">
-        <v>18012.29748445952</v>
+        <v>33157.70009159741</v>
       </c>
       <c r="E86">
         <v>25885.836</v>
@@ -8345,45 +8345,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M86">
-        <v>11579.36194278984</v>
+        <v>6841.704083589835</v>
       </c>
       <c r="N86">
-        <v>-5923.161942789837</v>
+        <v>-1185.504083589836</v>
       </c>
       <c r="O86">
-        <v>-1776.948582836951</v>
+        <v>-355.6512250769509</v>
       </c>
       <c r="P86">
-        <v>-4146.213359952886</v>
+        <v>-829.8528585128854</v>
       </c>
       <c r="Q86">
-        <v>144.8866400471143</v>
+        <v>3461.247141487115</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4181070722610337</v>
+        <v>0.3818540959041695</v>
       </c>
       <c r="T86">
-        <v>5.123987097803058</v>
+        <v>4.625911122557085</v>
       </c>
       <c r="U86">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V86">
-        <v>0.1465417531970827</v>
+        <v>0.2480171576069772</v>
       </c>
       <c r="W86">
-        <v>0.2027540226388098</v>
+        <v>0.1055540226388098</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.4884725106569422</v>
+        <v>0.826723858689924</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2391281865226585</v>
+        <v>0.1507077103055603</v>
       </c>
       <c r="C87">
-        <v>-27037.36149396877</v>
+        <v>-12012.18537808134</v>
       </c>
       <c r="D87">
-        <v>17833.62850603123</v>
+        <v>32858.80462191866</v>
       </c>
       <c r="E87">
         <v>26466.09</v>
@@ -8427,45 +8427,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M87">
-        <v>11717.21148972781</v>
+        <v>6923.152941727809</v>
       </c>
       <c r="N87">
-        <v>-6061.011489727809</v>
+        <v>-1266.95294172781</v>
       </c>
       <c r="O87">
-        <v>-1818.303446918343</v>
+        <v>-380.085882518343</v>
       </c>
       <c r="P87">
-        <v>-4242.708042809467</v>
+        <v>-886.867059209467</v>
       </c>
       <c r="Q87">
-        <v>48.3919571905335</v>
+        <v>3404.232940790534</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4429275437451026</v>
+        <v>0.4042577022977808</v>
       </c>
       <c r="T87">
-        <v>5.465586237656595</v>
+        <v>4.934305197394224</v>
       </c>
       <c r="U87">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V87">
-        <v>0.1448177325712346</v>
+        <v>0.2450993086939539</v>
       </c>
       <c r="W87">
-        <v>0.203163594071639</v>
+        <v>0.105963594071639</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.4827257752374489</v>
+        <v>0.8169976956465133</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2410458624669515</v>
+        <v>0.1516533862498532</v>
       </c>
       <c r="C88">
-        <v>-27792.77475190828</v>
+        <v>-12885.99428633739</v>
       </c>
       <c r="D88">
-        <v>17658.46924809171</v>
+        <v>32565.2497136626</v>
       </c>
       <c r="E88">
         <v>27046.344</v>
@@ -8509,45 +8509,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M88">
-        <v>11855.06103666578</v>
+        <v>7004.601799865783</v>
       </c>
       <c r="N88">
-        <v>-6198.861036665785</v>
+        <v>-1348.401799865784</v>
       </c>
       <c r="O88">
-        <v>-1859.658310999735</v>
+        <v>-404.5205399597351</v>
       </c>
       <c r="P88">
-        <v>-4339.202725666049</v>
+        <v>-943.8812599060486</v>
       </c>
       <c r="Q88">
-        <v>-48.10272566604908</v>
+        <v>3347.218740093952</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4712937968697528</v>
+        <v>0.4298618238904794</v>
       </c>
       <c r="T88">
-        <v>5.855985254632066</v>
+        <v>5.286755568636669</v>
       </c>
       <c r="U88">
-        <v>0.2375675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V88">
-        <v>0.1431338054483133</v>
+        <v>0.2422493167323964</v>
       </c>
       <c r="W88">
-        <v>0.2035636405874257</v>
+        <v>0.1063636405874257</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.477112684827711</v>
+        <v>0.8074977224413212</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2429635384112444</v>
+        <v>0.1795001994436337</v>
       </c>
       <c r="C89">
-        <v>-28544.78069936761</v>
+        <v>-20248.8741100744</v>
       </c>
       <c r="D89">
-        <v>17486.71730063239</v>
+        <v>25782.6238899256</v>
       </c>
       <c r="E89">
         <v>27626.598</v>
@@ -8591,45 +8591,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M89">
-        <v>11992.91058360376</v>
+        <v>8509.645821603757</v>
       </c>
       <c r="N89">
-        <v>-6336.710583603759</v>
+        <v>-2853.445821603758</v>
       </c>
       <c r="O89">
-        <v>-1901.013175081128</v>
+        <v>-856.0337464811274</v>
       </c>
       <c r="P89">
-        <v>-4435.697408522631</v>
+        <v>-1997.412075122631</v>
       </c>
       <c r="Q89">
-        <v>-144.5974085226308</v>
+        <v>2293.687924877369</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5040240889366568</v>
+        <v>0.4776137891858058</v>
       </c>
       <c r="T89">
-        <v>6.306445658834533</v>
+        <v>5.944079345004512</v>
       </c>
       <c r="U89">
-        <v>0.2375675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V89">
-        <v>0.141488589293735</v>
+        <v>0.1994043037246177</v>
       </c>
       <c r="W89">
-        <v>0.2039544906315851</v>
+        <v>0.134954490631585</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.4716286309791167</v>
+        <v>0.6646810124153923</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2448812143555373</v>
+        <v>0.1807278753879267</v>
       </c>
       <c r="C90">
-        <v>-29293.47780044386</v>
+        <v>-21063.71793845057</v>
       </c>
       <c r="D90">
-        <v>17318.27419955614</v>
+        <v>25548.03406154944</v>
       </c>
       <c r="E90">
         <v>28206.852</v>
@@ -8673,45 +8673,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M90">
-        <v>12130.76013054173</v>
+        <v>8607.457842541731</v>
       </c>
       <c r="N90">
-        <v>-6474.560130541733</v>
+        <v>-2951.257842541732</v>
       </c>
       <c r="O90">
-        <v>-1942.36803916252</v>
+        <v>-885.3773527625196</v>
       </c>
       <c r="P90">
-        <v>-4532.192091379213</v>
+        <v>-2065.880489779212</v>
       </c>
       <c r="Q90">
-        <v>-241.0920913792124</v>
+        <v>2225.219510220788</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5422094296813783</v>
+        <v>0.5135982716179565</v>
       </c>
       <c r="T90">
-        <v>6.831982797070745</v>
+        <v>6.439419290421557</v>
       </c>
       <c r="U90">
-        <v>0.2375675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V90">
-        <v>0.1398807644153971</v>
+        <v>0.197138345727747</v>
       </c>
       <c r="W90">
-        <v>0.2043364577201953</v>
+        <v>0.1353364577201953</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.4662692147179903</v>
+        <v>0.6571278190924903</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2467988902998302</v>
+        <v>0.2328742805236711</v>
       </c>
       <c r="C91">
-        <v>-30038.96076155711</v>
+        <v>-28765.41124515838</v>
       </c>
       <c r="D91">
-        <v>17153.04523844289</v>
+        <v>18426.59475484162</v>
       </c>
       <c r="E91">
         <v>28787.106</v>
@@ -8755,37 +8755,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M91">
-        <v>12268.60967747971</v>
+        <v>11493.97058747971</v>
       </c>
       <c r="N91">
-        <v>-6612.409677479707</v>
+        <v>-5837.770587479707</v>
       </c>
       <c r="O91">
-        <v>-1983.722903243912</v>
+        <v>-1751.331176243912</v>
       </c>
       <c r="P91">
-        <v>-4628.686774235795</v>
+        <v>-4086.439411235795</v>
       </c>
       <c r="Q91">
-        <v>-337.586774235795</v>
+        <v>204.6605887642054</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5873375596524126</v>
+        <v>0.5821138344146026</v>
       </c>
       <c r="T91">
-        <v>7.453072142258994</v>
+        <v>7.382561801916629</v>
       </c>
       <c r="U91">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V91">
-        <v>0.1383090704332016</v>
+        <v>0.1476304456397667</v>
       </c>
       <c r="W91">
-        <v>0.2047098412787245</v>
+        <v>0.1897098412787245</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4610302347773387</v>
+        <v>0.4921014854658889</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2487165662441231</v>
+        <v>0.234641956467964</v>
       </c>
       <c r="C92">
-        <v>-30781.32070901118</v>
+        <v>-29518.14941600995</v>
       </c>
       <c r="D92">
-        <v>16990.93929098882</v>
+        <v>18254.11058399004</v>
       </c>
       <c r="E92">
         <v>29367.36</v>
@@ -8837,37 +8837,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M92">
-        <v>12406.45922441768</v>
+        <v>11623.11632441768</v>
       </c>
       <c r="N92">
-        <v>-6750.259224417681</v>
+        <v>-5966.916324417682</v>
       </c>
       <c r="O92">
-        <v>-2025.077767325304</v>
+        <v>-1790.074897325304</v>
       </c>
       <c r="P92">
-        <v>-4725.181457092377</v>
+        <v>-4176.841427092377</v>
       </c>
       <c r="Q92">
-        <v>-434.0814570923767</v>
+        <v>114.2585729076236</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.641491315617654</v>
+        <v>0.635745217856063</v>
       </c>
       <c r="T92">
-        <v>8.198379356484894</v>
+        <v>8.120817982108292</v>
       </c>
       <c r="U92">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V92">
-        <v>0.1367723029839438</v>
+        <v>0.1459901073548804</v>
       </c>
       <c r="W92">
-        <v>0.2050749274248419</v>
+        <v>0.1900749274248419</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4559076766131461</v>
+        <v>0.4866336911829345</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.250634242188416</v>
+        <v>0.236409632412257</v>
       </c>
       <c r="C93">
-        <v>-31520.64535658045</v>
+        <v>-30267.68841884756</v>
       </c>
       <c r="D93">
-        <v>16831.86864341956</v>
+        <v>18084.82558115244</v>
       </c>
       <c r="E93">
         <v>29947.614</v>
@@ -8919,37 +8919,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M93">
-        <v>12544.30877135566</v>
+        <v>11752.26206135565</v>
       </c>
       <c r="N93">
-        <v>-6888.108771355657</v>
+        <v>-6096.062061355655</v>
       </c>
       <c r="O93">
-        <v>-2066.432631406697</v>
+        <v>-1828.818618406696</v>
       </c>
       <c r="P93">
-        <v>-4821.676139948961</v>
+        <v>-4267.243442948959</v>
       </c>
       <c r="Q93">
-        <v>-530.5761399489602</v>
+        <v>23.85655705104182</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7076792395751712</v>
+        <v>0.7012946865067368</v>
       </c>
       <c r="T93">
-        <v>9.109310396094328</v>
+        <v>9.023131091231438</v>
       </c>
       <c r="U93">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V93">
-        <v>0.1352693106434609</v>
+        <v>0.1443858204608707</v>
       </c>
       <c r="W93">
-        <v>0.2054319896996161</v>
+        <v>0.1904319896996161</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4508977021448697</v>
+        <v>0.4812860682029023</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.252551918132709</v>
+        <v>0.2381773083565499</v>
       </c>
       <c r="C94">
-        <v>-32257.01916377017</v>
+        <v>-31014.11644118749</v>
       </c>
       <c r="D94">
-        <v>16675.74883622983</v>
+        <v>17918.65155881251</v>
       </c>
       <c r="E94">
         <v>30527.868</v>
@@ -9001,37 +9001,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M94">
-        <v>12682.15831829363</v>
+        <v>11881.40779829363</v>
       </c>
       <c r="N94">
-        <v>-7025.958318293631</v>
+        <v>-6225.20779829363</v>
       </c>
       <c r="O94">
-        <v>-2107.787495488089</v>
+        <v>-1867.562339488089</v>
       </c>
       <c r="P94">
-        <v>-4918.170822805541</v>
+        <v>-4357.645458805541</v>
       </c>
       <c r="Q94">
-        <v>-627.070822805541</v>
+        <v>-66.54545880554087</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7904141445220679</v>
+        <v>0.7832315223200791</v>
       </c>
       <c r="T94">
-        <v>10.24797419560612</v>
+        <v>10.15102247763537</v>
       </c>
       <c r="U94">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V94">
-        <v>0.1337989920495102</v>
+        <v>0.1428164093689047</v>
       </c>
       <c r="W94">
-        <v>0.2057812897510256</v>
+        <v>0.1907812897510256</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4459966401650342</v>
+        <v>0.476054697896349</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2544695940770019</v>
+        <v>0.2399449843008428</v>
       </c>
       <c r="C95">
-        <v>-32990.52348535036</v>
+        <v>-31757.5184587824</v>
       </c>
       <c r="D95">
-        <v>16522.49851464964</v>
+        <v>17755.5035412176</v>
       </c>
       <c r="E95">
         <v>31108.122</v>
@@ -9083,37 +9083,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M95">
-        <v>12820.0078652316</v>
+        <v>12010.5535352316</v>
       </c>
       <c r="N95">
-        <v>-7163.807865231605</v>
+        <v>-6354.353535231605</v>
       </c>
       <c r="O95">
-        <v>-2149.142359569481</v>
+        <v>-1906.306060569481</v>
       </c>
       <c r="P95">
-        <v>-5014.665505662124</v>
+        <v>-4448.047474662124</v>
       </c>
       <c r="Q95">
-        <v>-723.5655056621235</v>
+        <v>-156.9474746621236</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8967875937395061</v>
+        <v>0.888578882651519</v>
       </c>
       <c r="T95">
-        <v>11.71197050926414</v>
+        <v>11.601168545869</v>
       </c>
       <c r="U95">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V95">
-        <v>0.1323602932102682</v>
+        <v>0.14128074905311</v>
       </c>
       <c r="W95">
-        <v>0.2061230779733726</v>
+        <v>0.1911230779733726</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4412009773675607</v>
+        <v>0.4709358301770334</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2563872700212948</v>
+        <v>0.2417126602451357</v>
       </c>
       <c r="C96">
-        <v>-33721.23671271941</v>
+        <v>-32497.97638051644</v>
       </c>
       <c r="D96">
-        <v>16372.0392872806</v>
+        <v>17595.29961948356</v>
       </c>
       <c r="E96">
         <v>31688.376</v>
@@ -9165,37 +9165,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M96">
-        <v>12957.85741216958</v>
+        <v>12139.69927216958</v>
       </c>
       <c r="N96">
-        <v>-7301.657412169579</v>
+        <v>-6483.499272169578</v>
       </c>
       <c r="O96">
-        <v>-2190.497223650874</v>
+        <v>-1945.049781650873</v>
       </c>
       <c r="P96">
-        <v>-5111.160188518706</v>
+        <v>-4538.449490518705</v>
       </c>
       <c r="Q96">
-        <v>-820.0601885187052</v>
+        <v>-247.3494905187044</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.038618859362758</v>
+        <v>1.029042029760106</v>
       </c>
       <c r="T96">
-        <v>13.6639655941415</v>
+        <v>13.53469663684717</v>
       </c>
       <c r="U96">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V96">
-        <v>0.130952204984627</v>
+        <v>0.1397777623610557</v>
       </c>
       <c r="W96">
-        <v>0.2064575941058824</v>
+        <v>0.1914575941058823</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4365073499487568</v>
+        <v>0.4659258745368523</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2583049459655877</v>
+        <v>0.2434803361894286</v>
       </c>
       <c r="C97">
-        <v>-34449.23440761355</v>
+        <v>-33235.56918552628</v>
       </c>
       <c r="D97">
-        <v>16224.29559238645</v>
+        <v>17437.96081447372</v>
       </c>
       <c r="E97">
         <v>32268.63</v>
@@ -9247,37 +9247,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M97">
-        <v>13095.70695910755</v>
+        <v>12268.84500910755</v>
       </c>
       <c r="N97">
-        <v>-7439.506959107553</v>
+        <v>-6612.645009107553</v>
       </c>
       <c r="O97">
-        <v>-2231.852087732266</v>
+        <v>-1983.793502732266</v>
       </c>
       <c r="P97">
-        <v>-5207.654871375287</v>
+        <v>-4628.851506375287</v>
       </c>
       <c r="Q97">
-        <v>-916.5548713752869</v>
+        <v>-337.7515063752871</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.23718263123531</v>
+        <v>1.225690435712128</v>
       </c>
       <c r="T97">
-        <v>16.39675871296981</v>
+        <v>16.24163596421661</v>
       </c>
       <c r="U97">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V97">
-        <v>0.129573760721631</v>
+        <v>0.1383064174940972</v>
       </c>
       <c r="W97">
-        <v>0.2067850677934972</v>
+        <v>0.1917850677934972</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.43191253573877</v>
+        <v>0.4610213916469906</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2602226219098807</v>
+        <v>0.2452480121337215</v>
       </c>
       <c r="C98">
-        <v>-35174.58942864151</v>
+        <v>-33970.3730530306</v>
       </c>
       <c r="D98">
-        <v>16079.19457135848</v>
+        <v>17283.4109469694</v>
       </c>
       <c r="E98">
         <v>32848.884</v>
@@ -9329,37 +9329,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M98">
-        <v>13233.55650604553</v>
+        <v>12397.99074604553</v>
       </c>
       <c r="N98">
-        <v>-7577.356506045528</v>
+        <v>-6741.790746045526</v>
       </c>
       <c r="O98">
-        <v>-2273.206951813658</v>
+        <v>-2022.537223813658</v>
       </c>
       <c r="P98">
-        <v>-5304.14955423187</v>
+        <v>-4719.253522231868</v>
       </c>
       <c r="Q98">
-        <v>-1013.049554231869</v>
+        <v>-428.153522231868</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.535028289044134</v>
+        <v>1.520663044640156</v>
       </c>
       <c r="T98">
-        <v>20.49594839121222</v>
+        <v>20.30204495527071</v>
       </c>
       <c r="U98">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V98">
-        <v>0.1282240340474473</v>
+        <v>0.1368657256452004</v>
       </c>
       <c r="W98">
-        <v>0.20710571911262</v>
+        <v>0.19210571911262</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4274134468248244</v>
+        <v>0.4562190854840011</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2621402978541736</v>
+        <v>0.2470156880780144</v>
       </c>
       <c r="C99">
-        <v>-35897.3720510893</v>
+        <v>-34702.46148531623</v>
       </c>
       <c r="D99">
-        <v>15936.6659489107</v>
+        <v>17131.57651468377</v>
       </c>
       <c r="E99">
         <v>33429.138</v>
@@ -9411,37 +9411,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M99">
-        <v>13371.4060529835</v>
+        <v>12527.1364829835</v>
       </c>
       <c r="N99">
-        <v>-7715.206052983502</v>
+        <v>-6870.936482983501</v>
       </c>
       <c r="O99">
-        <v>-2314.561815895051</v>
+        <v>-2061.28094489505</v>
       </c>
       <c r="P99">
-        <v>-5400.644237088451</v>
+        <v>-4809.655538088451</v>
       </c>
       <c r="Q99">
-        <v>-1109.54423708845</v>
+        <v>-518.5555380884507</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.031437718725511</v>
+        <v>2.012284059520208</v>
       </c>
       <c r="T99">
-        <v>27.32793118828295</v>
+        <v>27.06939327369428</v>
       </c>
       <c r="U99">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V99">
-        <v>0.1269021367892262</v>
+        <v>0.1354547387828787</v>
       </c>
       <c r="W99">
-        <v>0.2074197590643383</v>
+        <v>0.1924197590643383</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.423007122630754</v>
+        <v>0.451515795942929</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2640579737984665</v>
+        <v>0.2487833640223074</v>
       </c>
       <c r="C100">
-        <v>-36617.6500804092</v>
+        <v>-35431.90542429809</v>
       </c>
       <c r="D100">
-        <v>15796.6419195908</v>
+        <v>16982.38657570192</v>
       </c>
       <c r="E100">
         <v>34009.392</v>
@@ -9493,37 +9493,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M100">
-        <v>13509.25559992147</v>
+        <v>12656.28221992147</v>
       </c>
       <c r="N100">
-        <v>-7853.055599921476</v>
+        <v>-7000.082219921474</v>
       </c>
       <c r="O100">
-        <v>-2355.916679976443</v>
+        <v>-2100.024665976442</v>
       </c>
       <c r="P100">
-        <v>-5497.138919945033</v>
+        <v>-4900.057553945033</v>
       </c>
       <c r="Q100">
-        <v>-1206.038919945033</v>
+        <v>-608.9575539450325</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>3.024256578088267</v>
+        <v>2.995526089280312</v>
       </c>
       <c r="T100">
-        <v>40.99189678242443</v>
+        <v>40.60408991054143</v>
       </c>
       <c r="U100">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V100">
-        <v>0.1256072170260708</v>
+        <v>0.1340725475708085</v>
       </c>
       <c r="W100">
-        <v>0.2077273900374501</v>
+        <v>0.1927273900374501</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4186907234202362</v>
+        <v>0.446908491902695</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2659756497427594</v>
+        <v>0.2505510399666003</v>
       </c>
       <c r="C101">
-        <v>-37335.48895977801</v>
+        <v>-36158.77336204144</v>
       </c>
       <c r="D101">
-        <v>15659.05704022199</v>
+        <v>16835.77263795856</v>
       </c>
       <c r="E101">
         <v>34589.646</v>
@@ -9575,37 +9575,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M101">
-        <v>13647.10514685945</v>
+        <v>12785.42795685945</v>
       </c>
       <c r="N101">
-        <v>-7990.90514685945</v>
+        <v>-7129.227956859449</v>
       </c>
       <c r="O101">
-        <v>-2397.271544057835</v>
+        <v>-2138.768387057835</v>
       </c>
       <c r="P101">
-        <v>-5593.633602801615</v>
+        <v>-4990.459569801615</v>
       </c>
       <c r="Q101">
-        <v>-1302.533602801615</v>
+        <v>-699.3595698016143</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>6.002713156176534</v>
+        <v>5.945252178560624</v>
       </c>
       <c r="T101">
-        <v>81.98379356484885</v>
+        <v>81.20817982108285</v>
       </c>
       <c r="U101">
-        <v>0.2375675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V101">
-        <v>0.1243384572581307</v>
+        <v>0.1327182794135276</v>
       </c>
       <c r="W101">
-        <v>0.2080288062434283</v>
+        <v>0.1930288062434283</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.4144615241937691</v>
+        <v>0.4423942647117587</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/india/india_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/india/india_oil_gas_integrated.xlsx
@@ -1175,7 +1175,7 @@
         <v>0.110142600555919</v>
       </c>
       <c r="R2">
-        <v>0.10858254917244</v>
+        <v>0.108582549172441</v>
       </c>
       <c r="S2">
         <v>0.0570973161005042</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1137183940620466</v>
+        <v>0.1135611120408655</v>
       </c>
       <c r="C2">
-        <v>55204.77350289707</v>
+        <v>54742.32629135557</v>
       </c>
       <c r="D2">
-        <v>50754.17350289707</v>
+        <v>50871.98029135558</v>
       </c>
       <c r="E2">
-        <v>-22855.5</v>
+        <v>-22275.246</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>580.254</v>
       </c>
       <c r="G2">
         <v>4450.6</v>
@@ -1457,28 +1457,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>41.81750993797422</v>
       </c>
       <c r="N2">
-        <v>5656.199999999999</v>
+        <v>5614.382490062025</v>
       </c>
       <c r="O2">
-        <v>1696.86</v>
+        <v>1684.314747018607</v>
       </c>
       <c r="P2">
-        <v>3959.339999999999</v>
+        <v>3930.067743043417</v>
       </c>
       <c r="Q2">
-        <v>8250.439999999999</v>
+        <v>8221.167743043417</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1137183940620466</v>
+        <v>0.1141986251311722</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.941532820513902</v>
       </c>
       <c r="U2">
         <v>0.07206759442929168</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>135.2591296896815</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1135611120408655</v>
+        <v>0.1134038300196844</v>
       </c>
       <c r="C3">
-        <v>54742.32629135557</v>
+        <v>54280.42724076273</v>
       </c>
       <c r="D3">
-        <v>50871.98029135558</v>
+        <v>50990.33524076273</v>
       </c>
       <c r="E3">
-        <v>-22275.246</v>
+        <v>-21694.992</v>
       </c>
       <c r="F3">
-        <v>580.254</v>
+        <v>1160.508</v>
       </c>
       <c r="G3">
         <v>4450.6</v>
@@ -1539,28 +1539,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M3">
-        <v>41.81750993797422</v>
+        <v>83.63501987594843</v>
       </c>
       <c r="N3">
-        <v>5614.382490062025</v>
+        <v>5572.564980124051</v>
       </c>
       <c r="O3">
-        <v>1684.314747018607</v>
+        <v>1671.769494037215</v>
       </c>
       <c r="P3">
-        <v>3930.067743043417</v>
+        <v>3900.795486086836</v>
       </c>
       <c r="Q3">
-        <v>8221.167743043417</v>
+        <v>8191.895486086836</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1141986251311722</v>
+        <v>0.1146886568343616</v>
       </c>
       <c r="T3">
-        <v>0.941532820513902</v>
+        <v>0.9482782913586785</v>
       </c>
       <c r="U3">
         <v>0.07206759442929168</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>135.2591296896815</v>
+        <v>67.62956484484074</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1134038300196844</v>
+        <v>0.1132465479985033</v>
       </c>
       <c r="C4">
-        <v>54280.42724076273</v>
+        <v>53819.08018597135</v>
       </c>
       <c r="D4">
-        <v>50990.33524076273</v>
+        <v>51109.24218597135</v>
       </c>
       <c r="E4">
-        <v>-21694.992</v>
+        <v>-21114.738</v>
       </c>
       <c r="F4">
-        <v>1160.508</v>
+        <v>1740.762</v>
       </c>
       <c r="G4">
         <v>4450.6</v>
@@ -1621,28 +1621,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M4">
-        <v>83.63501987594843</v>
+        <v>125.4525298139227</v>
       </c>
       <c r="N4">
-        <v>5572.564980124051</v>
+        <v>5530.747470186076</v>
       </c>
       <c r="O4">
-        <v>1671.769494037215</v>
+        <v>1659.224241055823</v>
       </c>
       <c r="P4">
-        <v>3900.795486086836</v>
+        <v>3871.523229130254</v>
       </c>
       <c r="Q4">
-        <v>8191.895486086836</v>
+        <v>8162.623229130254</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1146886568343616</v>
+        <v>0.1151887922840085</v>
       </c>
       <c r="T4">
-        <v>0.9482782913586785</v>
+        <v>0.9551628440765432</v>
       </c>
       <c r="U4">
         <v>0.07206759442929168</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.62956484484074</v>
+        <v>45.08637656322716</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1132465479985033</v>
+        <v>0.1130892659773222</v>
       </c>
       <c r="C5">
-        <v>53819.08018597135</v>
+        <v>53358.28899768867</v>
       </c>
       <c r="D5">
-        <v>51109.24218597135</v>
+        <v>51228.70499768868</v>
       </c>
       <c r="E5">
-        <v>-21114.738</v>
+        <v>-20534.484</v>
       </c>
       <c r="F5">
-        <v>1740.762</v>
+        <v>2321.016</v>
       </c>
       <c r="G5">
         <v>4450.6</v>
@@ -1703,28 +1703,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M5">
-        <v>125.4525298139227</v>
+        <v>167.2700397518969</v>
       </c>
       <c r="N5">
-        <v>5530.747470186076</v>
+        <v>5488.929960248102</v>
       </c>
       <c r="O5">
-        <v>1659.224241055823</v>
+        <v>1646.678988074431</v>
       </c>
       <c r="P5">
-        <v>3871.523229130254</v>
+        <v>3842.250972173671</v>
       </c>
       <c r="Q5">
-        <v>8162.623229130254</v>
+        <v>8133.350972173672</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1151887922840085</v>
+        <v>0.1156993472221896</v>
       </c>
       <c r="T5">
-        <v>0.9551628440765432</v>
+        <v>0.9621908249760299</v>
       </c>
       <c r="U5">
         <v>0.07206759442929168</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.08637656322716</v>
+        <v>33.81478242242037</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1130892659773222</v>
+        <v>0.1129319839561411</v>
       </c>
       <c r="C6">
-        <v>53358.28899768867</v>
+        <v>52898.05758289619</v>
       </c>
       <c r="D6">
-        <v>51228.70499768868</v>
+        <v>51348.72758289619</v>
       </c>
       <c r="E6">
-        <v>-20534.484</v>
+        <v>-19954.23</v>
       </c>
       <c r="F6">
-        <v>2321.016</v>
+        <v>2901.27</v>
       </c>
       <c r="G6">
         <v>4450.6</v>
@@ -1785,28 +1785,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M6">
-        <v>167.2700397518969</v>
+        <v>209.0875496898711</v>
       </c>
       <c r="N6">
-        <v>5488.929960248102</v>
+        <v>5447.112450310128</v>
       </c>
       <c r="O6">
-        <v>1646.678988074431</v>
+        <v>1634.133735093038</v>
       </c>
       <c r="P6">
-        <v>3842.250972173671</v>
+        <v>3812.97871521709</v>
       </c>
       <c r="Q6">
-        <v>8133.350972173672</v>
+        <v>8104.078715217091</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1156993472221896</v>
+        <v>0.1162206506853852</v>
       </c>
       <c r="T6">
-        <v>0.9621908249760299</v>
+        <v>0.9693667633681375</v>
       </c>
       <c r="U6">
         <v>0.07206759442929168</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.81478242242037</v>
+        <v>27.0518259379363</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1129319839561411</v>
+        <v>0.11277470193496</v>
       </c>
       <c r="C7">
-        <v>52898.05758289619</v>
+        <v>52438.38988527584</v>
       </c>
       <c r="D7">
-        <v>51348.72758289619</v>
+        <v>51469.31388527584</v>
       </c>
       <c r="E7">
-        <v>-19954.23</v>
+        <v>-19373.976</v>
       </c>
       <c r="F7">
-        <v>2901.27</v>
+        <v>3481.524</v>
       </c>
       <c r="G7">
         <v>4450.6</v>
@@ -1867,28 +1867,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M7">
-        <v>209.0875496898711</v>
+        <v>250.9050596278453</v>
       </c>
       <c r="N7">
-        <v>5447.112450310128</v>
+        <v>5405.294940372153</v>
       </c>
       <c r="O7">
-        <v>1634.133735093038</v>
+        <v>1621.588482111646</v>
       </c>
       <c r="P7">
-        <v>3812.97871521709</v>
+        <v>3783.706458260507</v>
       </c>
       <c r="Q7">
-        <v>8104.078715217091</v>
+        <v>8074.806458260507</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1162206506853852</v>
+        <v>0.1167530457116274</v>
       </c>
       <c r="T7">
-        <v>0.9693667633681375</v>
+        <v>0.9766953813005028</v>
       </c>
       <c r="U7">
         <v>0.07206759442929168</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.0518259379363</v>
+        <v>22.54318828161358</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.11277470193496</v>
+        <v>0.112617419913779</v>
       </c>
       <c r="C8">
-        <v>52438.38988527584</v>
+        <v>51979.28988564169</v>
       </c>
       <c r="D8">
-        <v>51469.31388527584</v>
+        <v>51590.46788564169</v>
       </c>
       <c r="E8">
-        <v>-19373.976</v>
+        <v>-18793.722</v>
       </c>
       <c r="F8">
-        <v>3481.524</v>
+        <v>4061.778</v>
       </c>
       <c r="G8">
         <v>4450.6</v>
@@ -1949,28 +1949,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M8">
-        <v>250.9050596278453</v>
+        <v>292.7225695658195</v>
       </c>
       <c r="N8">
-        <v>5405.294940372153</v>
+        <v>5363.477430434179</v>
       </c>
       <c r="O8">
-        <v>1621.588482111646</v>
+        <v>1609.043229130254</v>
       </c>
       <c r="P8">
-        <v>3783.706458260507</v>
+        <v>3754.434201303925</v>
       </c>
       <c r="Q8">
-        <v>8074.806458260507</v>
+        <v>8045.534201303926</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1167530457116274</v>
+        <v>0.1172968900932727</v>
       </c>
       <c r="T8">
-        <v>0.9766953813005028</v>
+        <v>0.9841816039195858</v>
       </c>
       <c r="U8">
         <v>0.07206759442929168</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.54318828161358</v>
+        <v>19.32273281281164</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1126174199137789</v>
+        <v>0.1124601378925978</v>
       </c>
       <c r="C9">
-        <v>51979.2898856417</v>
+        <v>51520.76160237822</v>
       </c>
       <c r="D9">
-        <v>51590.4678856417</v>
+        <v>51712.19360237823</v>
       </c>
       <c r="E9">
-        <v>-18793.722</v>
+        <v>-18213.468</v>
       </c>
       <c r="F9">
-        <v>4061.778000000001</v>
+        <v>4642.032</v>
       </c>
       <c r="G9">
         <v>4450.6</v>
@@ -2031,28 +2031,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M9">
-        <v>292.7225695658196</v>
+        <v>334.5400795037937</v>
       </c>
       <c r="N9">
-        <v>5363.477430434179</v>
+        <v>5321.659920496205</v>
       </c>
       <c r="O9">
-        <v>1609.043229130254</v>
+        <v>1596.497976148861</v>
       </c>
       <c r="P9">
-        <v>3754.434201303925</v>
+        <v>3725.161944347344</v>
       </c>
       <c r="Q9">
-        <v>8045.534201303926</v>
+        <v>8016.261944347344</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1172968900932727</v>
+        <v>0.1178525571788669</v>
       </c>
       <c r="T9">
-        <v>0.9841816039195858</v>
+        <v>0.9918305705086485</v>
       </c>
       <c r="U9">
         <v>0.07206759442929168</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.32273281281164</v>
+        <v>16.90739121121019</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1124601378925978</v>
+        <v>0.1123028558714167</v>
       </c>
       <c r="C10">
-        <v>51520.76160237822</v>
+        <v>51062.80909188443</v>
       </c>
       <c r="D10">
-        <v>51712.19360237823</v>
+        <v>51834.49509188443</v>
       </c>
       <c r="E10">
-        <v>-18213.468</v>
+        <v>-17633.214</v>
       </c>
       <c r="F10">
-        <v>4642.032</v>
+        <v>5222.286</v>
       </c>
       <c r="G10">
         <v>4450.6</v>
@@ -2113,28 +2113,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M10">
-        <v>334.5400795037937</v>
+        <v>376.357589441768</v>
       </c>
       <c r="N10">
-        <v>5321.659920496205</v>
+        <v>5279.842410558231</v>
       </c>
       <c r="O10">
-        <v>1596.497976148861</v>
+        <v>1583.952723167469</v>
       </c>
       <c r="P10">
-        <v>3725.161944347344</v>
+        <v>3695.889687390762</v>
       </c>
       <c r="Q10">
-        <v>8016.261944347344</v>
+        <v>7986.989687390762</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1178525571788669</v>
+        <v>0.1184204367278806</v>
       </c>
       <c r="T10">
-        <v>0.9918305705086485</v>
+        <v>0.9996476462535149</v>
       </c>
       <c r="U10">
         <v>0.07206759442929168</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.90739121121019</v>
+        <v>15.02879218774239</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1123028558714167</v>
+        <v>0.1121455738502356</v>
       </c>
       <c r="C11">
-        <v>51062.80909188443</v>
+        <v>50605.4364490245</v>
       </c>
       <c r="D11">
-        <v>51834.49509188443</v>
+        <v>51957.3764490245</v>
       </c>
       <c r="E11">
-        <v>-17633.214</v>
+        <v>-17052.96</v>
       </c>
       <c r="F11">
-        <v>5222.286</v>
+        <v>5802.54</v>
       </c>
       <c r="G11">
         <v>4450.6</v>
@@ -2195,28 +2195,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M11">
-        <v>376.357589441768</v>
+        <v>418.1750993797422</v>
       </c>
       <c r="N11">
-        <v>5279.842410558231</v>
+        <v>5238.024900620257</v>
       </c>
       <c r="O11">
-        <v>1583.952723167469</v>
+        <v>1571.407470186077</v>
       </c>
       <c r="P11">
-        <v>3695.889687390762</v>
+        <v>3666.617430434179</v>
       </c>
       <c r="Q11">
-        <v>7986.989687390762</v>
+        <v>7957.71743043418</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1184204367278806</v>
+        <v>0.119000935822428</v>
       </c>
       <c r="T11">
-        <v>0.9996476462535149</v>
+        <v>1.007638434792712</v>
       </c>
       <c r="U11">
         <v>0.07206759442929168</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.02879218774239</v>
+        <v>13.52591296896815</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1121455738502356</v>
+        <v>0.1119882918290545</v>
       </c>
       <c r="C12">
-        <v>50605.43644902449</v>
+        <v>50148.64780758482</v>
       </c>
       <c r="D12">
-        <v>51957.37644902449</v>
+        <v>52080.84180758482</v>
       </c>
       <c r="E12">
-        <v>-17052.96</v>
+        <v>-16472.706</v>
       </c>
       <c r="F12">
-        <v>5802.540000000001</v>
+        <v>6382.794</v>
       </c>
       <c r="G12">
         <v>4450.6</v>
@@ -2277,28 +2277,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M12">
-        <v>418.1750993797422</v>
+        <v>459.9926093177164</v>
       </c>
       <c r="N12">
-        <v>5238.024900620257</v>
+        <v>5196.207390682282</v>
       </c>
       <c r="O12">
-        <v>1571.407470186077</v>
+        <v>1558.862217204685</v>
       </c>
       <c r="P12">
-        <v>3666.617430434179</v>
+        <v>3637.345173477598</v>
       </c>
       <c r="Q12">
-        <v>7957.71743043418</v>
+        <v>7928.445173477598</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.119000935822428</v>
+        <v>0.1195944798404484</v>
       </c>
       <c r="T12">
-        <v>1.007638434792712</v>
+        <v>1.015808791613688</v>
       </c>
       <c r="U12">
         <v>0.07206759442929168</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>13.52591296896815</v>
+        <v>12.29628451724377</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1119882918290545</v>
+        <v>0.1118310098078734</v>
       </c>
       <c r="C13">
-        <v>50148.64780758482</v>
+        <v>49692.44734073756</v>
       </c>
       <c r="D13">
-        <v>52080.84180758482</v>
+        <v>52204.89534073756</v>
       </c>
       <c r="E13">
-        <v>-16472.706</v>
+        <v>-15892.452</v>
       </c>
       <c r="F13">
-        <v>6382.794</v>
+        <v>6963.048</v>
       </c>
       <c r="G13">
         <v>4450.6</v>
@@ -2359,28 +2359,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M13">
-        <v>459.9926093177164</v>
+        <v>501.8101192556906</v>
       </c>
       <c r="N13">
-        <v>5196.207390682282</v>
+        <v>5154.389880744308</v>
       </c>
       <c r="O13">
-        <v>1558.862217204685</v>
+        <v>1546.316964223292</v>
       </c>
       <c r="P13">
-        <v>3637.345173477598</v>
+        <v>3608.072916521016</v>
       </c>
       <c r="Q13">
-        <v>7928.445173477598</v>
+        <v>7899.172916521016</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1195944798404484</v>
+        <v>0.120201513495242</v>
       </c>
       <c r="T13">
-        <v>1.015808791613688</v>
+        <v>1.024164838362414</v>
       </c>
       <c r="U13">
         <v>0.07206759442929168</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.29628451724377</v>
+        <v>11.27159414080679</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1118310098078734</v>
+        <v>0.1116737277866923</v>
       </c>
       <c r="C14">
-        <v>49692.44734073756</v>
+        <v>49236.83926151082</v>
       </c>
       <c r="D14">
-        <v>52204.89534073756</v>
+        <v>52329.54126151082</v>
       </c>
       <c r="E14">
-        <v>-15892.452</v>
+        <v>-15312.198</v>
       </c>
       <c r="F14">
-        <v>6963.048</v>
+        <v>7543.302000000001</v>
       </c>
       <c r="G14">
         <v>4450.6</v>
@@ -2441,28 +2441,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M14">
-        <v>501.8101192556906</v>
+        <v>543.6276291936649</v>
       </c>
       <c r="N14">
-        <v>5154.389880744308</v>
+        <v>5112.572370806334</v>
       </c>
       <c r="O14">
-        <v>1546.316964223292</v>
+        <v>1533.7717112419</v>
       </c>
       <c r="P14">
-        <v>3608.072916521016</v>
+        <v>3578.800659564434</v>
       </c>
       <c r="Q14">
-        <v>7899.172916521016</v>
+        <v>7869.900659564434</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.120201513495242</v>
+        <v>0.1208225019466975</v>
       </c>
       <c r="T14">
-        <v>1.024164838362414</v>
+        <v>1.032712978139846</v>
       </c>
       <c r="U14">
         <v>0.07206759442929168</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.27159414080679</v>
+        <v>10.4045484376678</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1116737277866923</v>
+        <v>0.1115164457655113</v>
       </c>
       <c r="C15">
-        <v>49236.83926151082</v>
+        <v>48781.82782326556</v>
       </c>
       <c r="D15">
-        <v>52329.54126151082</v>
+        <v>52454.78382326556</v>
       </c>
       <c r="E15">
-        <v>-15312.198</v>
+        <v>-14731.944</v>
       </c>
       <c r="F15">
-        <v>7543.302000000001</v>
+        <v>8123.556000000001</v>
       </c>
       <c r="G15">
         <v>4450.6</v>
@@ -2523,28 +2523,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M15">
-        <v>543.6276291936649</v>
+        <v>585.4451391316392</v>
       </c>
       <c r="N15">
-        <v>5112.572370806334</v>
+        <v>5070.75486086836</v>
       </c>
       <c r="O15">
-        <v>1533.7717112419</v>
+        <v>1521.226458260508</v>
       </c>
       <c r="P15">
-        <v>3578.800659564434</v>
+        <v>3549.528402607852</v>
       </c>
       <c r="Q15">
-        <v>7869.900659564434</v>
+        <v>7840.628402607852</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1208225019466975</v>
+        <v>0.1214579319900473</v>
       </c>
       <c r="T15">
-        <v>1.032712978139846</v>
+        <v>1.041459911865591</v>
       </c>
       <c r="U15">
         <v>0.07206759442929168</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.4045484376678</v>
+        <v>9.661366406405818</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1115164457655113</v>
+        <v>0.1113591637443302</v>
       </c>
       <c r="C16">
-        <v>48781.82782326556</v>
+        <v>48327.41732017951</v>
       </c>
       <c r="D16">
-        <v>52454.78382326556</v>
+        <v>52580.6273201795</v>
       </c>
       <c r="E16">
-        <v>-14731.944</v>
+        <v>-14151.69</v>
       </c>
       <c r="F16">
-        <v>8123.556000000001</v>
+        <v>8703.810000000001</v>
       </c>
       <c r="G16">
         <v>4450.6</v>
@@ -2605,28 +2605,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M16">
-        <v>585.4451391316392</v>
+        <v>627.2626490696133</v>
       </c>
       <c r="N16">
-        <v>5070.75486086836</v>
+        <v>5028.937350930386</v>
       </c>
       <c r="O16">
-        <v>1521.226458260508</v>
+        <v>1508.681205279116</v>
       </c>
       <c r="P16">
-        <v>3549.528402607852</v>
+        <v>3520.25614565127</v>
       </c>
       <c r="Q16">
-        <v>7840.628402607852</v>
+        <v>7811.356145651271</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1214579319900473</v>
+        <v>0.1221083133285348</v>
       </c>
       <c r="T16">
-        <v>1.041459911865591</v>
+        <v>1.050412655796647</v>
       </c>
       <c r="U16">
         <v>0.07206759442929168</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.661366406405818</v>
+        <v>9.017275312645433</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1113591637443302</v>
+        <v>0.111369881723149</v>
       </c>
       <c r="C17">
-        <v>48327.41732017951</v>
+        <v>47738.56855021667</v>
       </c>
       <c r="D17">
-        <v>52580.6273201795</v>
+        <v>52572.03255021667</v>
       </c>
       <c r="E17">
-        <v>-14151.69</v>
+        <v>-13571.436</v>
       </c>
       <c r="F17">
-        <v>8703.809999999999</v>
+        <v>9284.064</v>
       </c>
       <c r="G17">
         <v>4450.6</v>
@@ -2687,45 +2687,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M17">
-        <v>627.2626490696132</v>
+        <v>683.0062550075874</v>
       </c>
       <c r="N17">
-        <v>5028.937350930386</v>
+        <v>4973.193744992412</v>
       </c>
       <c r="O17">
-        <v>1508.681205279116</v>
+        <v>1491.958123497723</v>
       </c>
       <c r="P17">
-        <v>3520.25614565127</v>
+        <v>3481.235621494689</v>
       </c>
       <c r="Q17">
-        <v>7811.356145651271</v>
+        <v>7772.335621494689</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1221083133285348</v>
+        <v>0.1227741799369862</v>
       </c>
       <c r="T17">
-        <v>1.050412655796647</v>
+        <v>1.059578560297491</v>
       </c>
       <c r="U17">
-        <v>0.07206759442929168</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.05044731610050417</v>
+        <v>0.05149731610050417</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.017275312645433</v>
+        <v>8.281329722137269</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.111369881723149</v>
+        <v>0.1112230997019679</v>
       </c>
       <c r="C18">
-        <v>47738.56855021667</v>
+        <v>47276.26416175253</v>
       </c>
       <c r="D18">
-        <v>52572.03255021667</v>
+        <v>52689.98216175253</v>
       </c>
       <c r="E18">
-        <v>-13571.436</v>
+        <v>-12991.182</v>
       </c>
       <c r="F18">
-        <v>9284.064</v>
+        <v>9864.318000000001</v>
       </c>
       <c r="G18">
         <v>4450.6</v>
@@ -2769,28 +2769,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M18">
-        <v>683.0062550075874</v>
+        <v>725.6941459455617</v>
       </c>
       <c r="N18">
-        <v>4973.193744992412</v>
+        <v>4930.505854054437</v>
       </c>
       <c r="O18">
-        <v>1491.958123497723</v>
+        <v>1479.151756216331</v>
       </c>
       <c r="P18">
-        <v>3481.235621494689</v>
+        <v>3451.354097838106</v>
       </c>
       <c r="Q18">
-        <v>7772.335621494689</v>
+        <v>7742.454097838106</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1227741799369862</v>
+        <v>0.1234560915239545</v>
       </c>
       <c r="T18">
-        <v>1.059578560297491</v>
+        <v>1.068965329967029</v>
       </c>
       <c r="U18">
         <v>0.07356759442929167</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.281329722137269</v>
+        <v>7.794192679658603</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1112230997019679</v>
+        <v>0.1110763176807868</v>
       </c>
       <c r="C19">
-        <v>47276.26416175253</v>
+        <v>46814.49022240054</v>
       </c>
       <c r="D19">
-        <v>52689.98216175253</v>
+        <v>52808.46222240054</v>
       </c>
       <c r="E19">
-        <v>-12991.182</v>
+        <v>-12410.928</v>
       </c>
       <c r="F19">
-        <v>9864.318000000001</v>
+        <v>10444.572</v>
       </c>
       <c r="G19">
         <v>4450.6</v>
@@ -2851,28 +2851,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M19">
-        <v>725.6941459455617</v>
+        <v>768.3820368835359</v>
       </c>
       <c r="N19">
-        <v>4930.505854054437</v>
+        <v>4887.817963116463</v>
       </c>
       <c r="O19">
-        <v>1479.151756216331</v>
+        <v>1466.345388934939</v>
       </c>
       <c r="P19">
-        <v>3451.354097838106</v>
+        <v>3421.472574181524</v>
       </c>
       <c r="Q19">
-        <v>7742.454097838106</v>
+        <v>7712.572574181524</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1234560915239545</v>
+        <v>0.1241546351008489</v>
       </c>
       <c r="T19">
-        <v>1.068965329967029</v>
+        <v>1.078581045238263</v>
       </c>
       <c r="U19">
         <v>0.07356759442929167</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.794192679658603</v>
+        <v>7.361181975233126</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1110763176807869</v>
+        <v>0.1109295356596058</v>
       </c>
       <c r="C20">
-        <v>46814.49022240053</v>
+        <v>46353.25031857006</v>
       </c>
       <c r="D20">
-        <v>52808.46222240054</v>
+        <v>52927.47631857006</v>
       </c>
       <c r="E20">
-        <v>-12410.928</v>
+        <v>-11830.674</v>
       </c>
       <c r="F20">
-        <v>10444.572</v>
+        <v>11024.826</v>
       </c>
       <c r="G20">
         <v>4450.6</v>
@@ -2933,28 +2933,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M20">
-        <v>768.3820368835358</v>
+        <v>811.0699278215101</v>
       </c>
       <c r="N20">
-        <v>4887.817963116463</v>
+        <v>4845.130072178489</v>
       </c>
       <c r="O20">
-        <v>1466.345388934939</v>
+        <v>1453.539021653547</v>
       </c>
       <c r="P20">
-        <v>3421.472574181524</v>
+        <v>3391.591050524942</v>
       </c>
       <c r="Q20">
-        <v>7712.572574181524</v>
+        <v>7682.691050524943</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1241546351008489</v>
+        <v>0.1248704266672963</v>
       </c>
       <c r="T20">
-        <v>1.078581045238263</v>
+        <v>1.088434185577923</v>
       </c>
       <c r="U20">
         <v>0.07356759442929167</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.361181975233126</v>
+        <v>6.973751344957698</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1109295356596058</v>
+        <v>0.1110207536384247</v>
       </c>
       <c r="C21">
-        <v>46353.25031857006</v>
+        <v>45698.9717612868</v>
       </c>
       <c r="D21">
-        <v>52927.47631857006</v>
+        <v>52853.4517612868</v>
       </c>
       <c r="E21">
-        <v>-11830.674</v>
+        <v>-11250.42</v>
       </c>
       <c r="F21">
-        <v>11024.826</v>
+        <v>11605.08</v>
       </c>
       <c r="G21">
         <v>4450.6</v>
@@ -3015,45 +3015,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M21">
-        <v>811.0699278215101</v>
+        <v>873.4864547594844</v>
       </c>
       <c r="N21">
-        <v>4845.130072178489</v>
+        <v>4782.713545240515</v>
       </c>
       <c r="O21">
-        <v>1453.539021653547</v>
+        <v>1434.814063572154</v>
       </c>
       <c r="P21">
-        <v>3391.591050524942</v>
+        <v>3347.89948166836</v>
       </c>
       <c r="Q21">
-        <v>7682.691050524943</v>
+        <v>7638.999481668361</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1248704266672963</v>
+        <v>0.1256041130229048</v>
       </c>
       <c r="T21">
-        <v>1.088434185577923</v>
+        <v>1.098533654426075</v>
       </c>
       <c r="U21">
-        <v>0.07356759442929167</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.05149731610050417</v>
+        <v>0.05268731610050417</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.973751344957698</v>
+        <v>6.475429549228031</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1110207536384247</v>
+        <v>0.1108858716172436</v>
       </c>
       <c r="C22">
-        <v>45698.9717612868</v>
+        <v>45228.24968000923</v>
       </c>
       <c r="D22">
-        <v>52853.4517612868</v>
+        <v>52962.98368000924</v>
       </c>
       <c r="E22">
-        <v>-11250.42</v>
+        <v>-10670.166</v>
       </c>
       <c r="F22">
-        <v>11605.08</v>
+        <v>12185.334</v>
       </c>
       <c r="G22">
         <v>4450.6</v>
@@ -3097,28 +3097,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M22">
-        <v>873.4864547594844</v>
+        <v>917.1607774974585</v>
       </c>
       <c r="N22">
-        <v>4782.713545240515</v>
+        <v>4739.039222502541</v>
       </c>
       <c r="O22">
-        <v>1434.814063572154</v>
+        <v>1421.711766750762</v>
       </c>
       <c r="P22">
-        <v>3347.89948166836</v>
+        <v>3317.327455751779</v>
       </c>
       <c r="Q22">
-        <v>7638.999481668361</v>
+        <v>7608.427455751779</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1256041130229048</v>
+        <v>0.12635637371663</v>
       </c>
       <c r="T22">
-        <v>1.098533654426075</v>
+        <v>1.108888806029876</v>
       </c>
       <c r="U22">
         <v>0.07526759442929168</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.475429549228031</v>
+        <v>6.167075761169555</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1108858716172436</v>
+        <v>0.1107509895960625</v>
       </c>
       <c r="C23">
-        <v>45228.24968000926</v>
+        <v>44757.9825228729</v>
       </c>
       <c r="D23">
-        <v>52962.98368000926</v>
+        <v>53072.97052287291</v>
       </c>
       <c r="E23">
-        <v>-10670.166</v>
+        <v>-10089.912</v>
       </c>
       <c r="F23">
-        <v>12185.334</v>
+        <v>12765.588</v>
       </c>
       <c r="G23">
         <v>4450.6</v>
@@ -3179,28 +3179,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M23">
-        <v>917.1607774974585</v>
+        <v>960.8351002354327</v>
       </c>
       <c r="N23">
-        <v>4739.039222502541</v>
+        <v>4695.364899764566</v>
       </c>
       <c r="O23">
-        <v>1421.711766750762</v>
+        <v>1408.60946992937</v>
       </c>
       <c r="P23">
-        <v>3317.327455751779</v>
+        <v>3286.755429835196</v>
       </c>
       <c r="Q23">
-        <v>7608.427455751779</v>
+        <v>7577.855429835196</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.12635637371663</v>
+        <v>0.1271279231460917</v>
       </c>
       <c r="T23">
-        <v>1.108888806029876</v>
+        <v>1.119509474341466</v>
       </c>
       <c r="U23">
         <v>0.07526759442929168</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.167075761169555</v>
+        <v>5.886754135661847</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1107509895960625</v>
+        <v>0.1106161075748814</v>
       </c>
       <c r="C24">
-        <v>44757.9825228729</v>
+        <v>44288.1731299629</v>
       </c>
       <c r="D24">
-        <v>53072.97052287291</v>
+        <v>53183.41512996291</v>
       </c>
       <c r="E24">
-        <v>-10089.912</v>
+        <v>-9509.657999999999</v>
       </c>
       <c r="F24">
-        <v>12765.588</v>
+        <v>13345.842</v>
       </c>
       <c r="G24">
         <v>4450.6</v>
@@ -3261,28 +3261,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M24">
-        <v>960.8351002354327</v>
+        <v>1004.509422973407</v>
       </c>
       <c r="N24">
-        <v>4695.364899764566</v>
+        <v>4651.690577026592</v>
       </c>
       <c r="O24">
-        <v>1408.60946992937</v>
+        <v>1395.507173107978</v>
       </c>
       <c r="P24">
-        <v>3286.755429835196</v>
+        <v>3256.183403918614</v>
       </c>
       <c r="Q24">
-        <v>7577.855429835196</v>
+        <v>7547.283403918615</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1271279231460917</v>
+        <v>0.1279195128204745</v>
       </c>
       <c r="T24">
-        <v>1.119509474341466</v>
+        <v>1.130406004167644</v>
       </c>
       <c r="U24">
         <v>0.07526759442929168</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.886754135661847</v>
+        <v>5.63080830367655</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1106161075748814</v>
+        <v>0.1106156255537003</v>
       </c>
       <c r="C25">
-        <v>44288.1731299629</v>
+        <v>43708.31464466103</v>
       </c>
       <c r="D25">
-        <v>53183.41512996291</v>
+        <v>53183.81064466104</v>
       </c>
       <c r="E25">
-        <v>-9509.657999999999</v>
+        <v>-8929.403999999999</v>
       </c>
       <c r="F25">
-        <v>13345.842</v>
+        <v>13926.096</v>
       </c>
       <c r="G25">
         <v>4450.6</v>
@@ -3343,45 +3343,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M25">
-        <v>1004.509422973407</v>
+        <v>1059.324622511381</v>
       </c>
       <c r="N25">
-        <v>4651.690577026592</v>
+        <v>4596.875377488617</v>
       </c>
       <c r="O25">
-        <v>1395.507173107978</v>
+        <v>1379.062613246585</v>
       </c>
       <c r="P25">
-        <v>3256.183403918614</v>
+        <v>3217.812764242032</v>
       </c>
       <c r="Q25">
-        <v>7547.283403918615</v>
+        <v>7508.912764242033</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1279195128204745</v>
+        <v>0.128731933802078</v>
       </c>
       <c r="T25">
-        <v>1.130406004167644</v>
+        <v>1.141589284778721</v>
       </c>
       <c r="U25">
-        <v>0.07526759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.05268731610050417</v>
+        <v>0.05324731610050417</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>5.63080830367655</v>
+        <v>5.339439752274076</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1106156255537003</v>
+        <v>0.1104863435325192</v>
       </c>
       <c r="C26">
-        <v>43708.31464466104</v>
+        <v>43234.35372228411</v>
       </c>
       <c r="D26">
-        <v>53183.81064466104</v>
+        <v>53290.10372228411</v>
       </c>
       <c r="E26">
-        <v>-8929.404</v>
+        <v>-8349.15</v>
       </c>
       <c r="F26">
-        <v>13926.096</v>
+        <v>14506.35</v>
       </c>
       <c r="G26">
         <v>4450.6</v>
@@ -3425,28 +3425,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M26">
-        <v>1059.324622511381</v>
+        <v>1103.463148449355</v>
       </c>
       <c r="N26">
-        <v>4596.875377488618</v>
+        <v>4552.736851550644</v>
       </c>
       <c r="O26">
-        <v>1379.062613246585</v>
+        <v>1365.821055465193</v>
       </c>
       <c r="P26">
-        <v>3217.812764242033</v>
+        <v>3186.915796085451</v>
       </c>
       <c r="Q26">
-        <v>7508.912764242034</v>
+        <v>7478.015796085451</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.128731933802078</v>
+        <v>0.1295660193431908</v>
       </c>
       <c r="T26">
-        <v>1.141589284778721</v>
+        <v>1.153070786206093</v>
       </c>
       <c r="U26">
         <v>0.07606759442929167</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.339439752274078</v>
+        <v>5.125862162183115</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1104863435325192</v>
+        <v>0.1103570615113381</v>
       </c>
       <c r="C27">
-        <v>43234.35372228411</v>
+        <v>42760.81852510566</v>
       </c>
       <c r="D27">
-        <v>53290.10372228411</v>
+        <v>53396.82252510566</v>
       </c>
       <c r="E27">
-        <v>-8349.15</v>
+        <v>-7768.895999999999</v>
       </c>
       <c r="F27">
-        <v>14506.35</v>
+        <v>15086.604</v>
       </c>
       <c r="G27">
         <v>4450.6</v>
@@ -3507,28 +3507,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M27">
-        <v>1103.463148449355</v>
+        <v>1147.601674387329</v>
       </c>
       <c r="N27">
-        <v>4552.736851550644</v>
+        <v>4508.598325612669</v>
       </c>
       <c r="O27">
-        <v>1365.821055465193</v>
+        <v>1352.579497683801</v>
       </c>
       <c r="P27">
-        <v>3186.915796085451</v>
+        <v>3156.018827928869</v>
       </c>
       <c r="Q27">
-        <v>7478.015796085451</v>
+        <v>7447.118827928869</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1295660193431908</v>
+        <v>0.1304226477367662</v>
       </c>
       <c r="T27">
-        <v>1.153070786206093</v>
+        <v>1.164862598482853</v>
       </c>
       <c r="U27">
         <v>0.07606759442929167</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.125862162183115</v>
+        <v>4.928713617483764</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1103570615113381</v>
+        <v>0.110227779490157</v>
       </c>
       <c r="C28">
-        <v>42760.81852510566</v>
+        <v>42287.71161593078</v>
       </c>
       <c r="D28">
-        <v>53396.82252510566</v>
+        <v>53503.96961593079</v>
       </c>
       <c r="E28">
-        <v>-7768.895999999999</v>
+        <v>-7188.641999999998</v>
       </c>
       <c r="F28">
-        <v>15086.604</v>
+        <v>15666.858</v>
       </c>
       <c r="G28">
         <v>4450.6</v>
@@ -3589,28 +3589,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M28">
-        <v>1147.601674387329</v>
+        <v>1191.740200325304</v>
       </c>
       <c r="N28">
-        <v>4508.598325612669</v>
+        <v>4464.459799674695</v>
       </c>
       <c r="O28">
-        <v>1352.579497683801</v>
+        <v>1339.337939902409</v>
       </c>
       <c r="P28">
-        <v>3156.018827928869</v>
+        <v>3125.121859772286</v>
       </c>
       <c r="Q28">
-        <v>7447.118827928869</v>
+        <v>7416.221859772287</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1304226477367662</v>
+        <v>0.1313027454013984</v>
       </c>
       <c r="T28">
-        <v>1.164862598482853</v>
+        <v>1.176977474109662</v>
       </c>
       <c r="U28">
         <v>0.07606759442929167</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.928713617483764</v>
+        <v>4.746168668688068</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.110227779490157</v>
+        <v>0.1100984974689759</v>
       </c>
       <c r="C29">
-        <v>42287.71161593078</v>
+        <v>41815.0355781763</v>
       </c>
       <c r="D29">
-        <v>53503.96961593079</v>
+        <v>53611.5475781763</v>
       </c>
       <c r="E29">
-        <v>-7188.641999999998</v>
+        <v>-6608.387999999997</v>
       </c>
       <c r="F29">
-        <v>15666.858</v>
+        <v>16247.112</v>
       </c>
       <c r="G29">
         <v>4450.6</v>
@@ -3671,28 +3671,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M29">
-        <v>1191.740200325304</v>
+        <v>1235.878726263278</v>
       </c>
       <c r="N29">
-        <v>4464.459799674695</v>
+        <v>4420.321273736721</v>
       </c>
       <c r="O29">
-        <v>1339.337939902409</v>
+        <v>1326.096382121016</v>
       </c>
       <c r="P29">
-        <v>3125.121859772286</v>
+        <v>3094.224891615705</v>
       </c>
       <c r="Q29">
-        <v>7416.221859772287</v>
+        <v>7385.324891615705</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1313027454013984</v>
+        <v>0.1322072902233815</v>
       </c>
       <c r="T29">
-        <v>1.176977474109662</v>
+        <v>1.189428874059438</v>
       </c>
       <c r="U29">
         <v>0.07606759442929167</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.746168668688068</v>
+        <v>4.576662644806351</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1100984974689759</v>
+        <v>0.1099692154477948</v>
       </c>
       <c r="C30">
-        <v>41815.0355781763</v>
+        <v>41342.79301607819</v>
       </c>
       <c r="D30">
-        <v>53611.5475781763</v>
+        <v>53719.55901607819</v>
       </c>
       <c r="E30">
-        <v>-6608.387999999997</v>
+        <v>-6028.133999999998</v>
       </c>
       <c r="F30">
-        <v>16247.112</v>
+        <v>16827.366</v>
       </c>
       <c r="G30">
         <v>4450.6</v>
@@ -3753,28 +3753,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M30">
-        <v>1235.878726263278</v>
+        <v>1280.017252201252</v>
       </c>
       <c r="N30">
-        <v>4420.321273736721</v>
+        <v>4376.182747798746</v>
       </c>
       <c r="O30">
-        <v>1326.096382121016</v>
+        <v>1312.854824339624</v>
       </c>
       <c r="P30">
-        <v>3094.224891615705</v>
+        <v>3063.327923459123</v>
       </c>
       <c r="Q30">
-        <v>7385.324891615705</v>
+        <v>7354.427923459123</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1322072902233815</v>
+        <v>0.1331373151811952</v>
       </c>
       <c r="T30">
-        <v>1.189428874059438</v>
+        <v>1.202231017669771</v>
       </c>
       <c r="U30">
         <v>0.07606759442929167</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.576662644806351</v>
+        <v>4.418846691537167</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1099692154477948</v>
+        <v>0.1098399334266137</v>
       </c>
       <c r="C31">
-        <v>41342.7930160782</v>
+        <v>40870.986554902</v>
       </c>
       <c r="D31">
-        <v>53719.55901607819</v>
+        <v>53828.006554902</v>
       </c>
       <c r="E31">
-        <v>-6028.134000000002</v>
+        <v>-5447.880000000001</v>
       </c>
       <c r="F31">
-        <v>16827.366</v>
+        <v>17407.62</v>
       </c>
       <c r="G31">
         <v>4450.6</v>
@@ -3835,28 +3835,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M31">
-        <v>1280.017252201252</v>
+        <v>1324.155778139226</v>
       </c>
       <c r="N31">
-        <v>4376.182747798747</v>
+        <v>4332.044221860773</v>
       </c>
       <c r="O31">
-        <v>1312.854824339624</v>
+        <v>1299.613266558232</v>
       </c>
       <c r="P31">
-        <v>3063.327923459123</v>
+        <v>3032.430955302541</v>
       </c>
       <c r="Q31">
-        <v>7354.427923459123</v>
+        <v>7323.530955302542</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1331373151811952</v>
+        <v>0.1340939122806606</v>
       </c>
       <c r="T31">
-        <v>1.202231017669771</v>
+        <v>1.215398936811827</v>
       </c>
       <c r="U31">
         <v>0.07606759442929167</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.418846691537168</v>
+        <v>4.271551801819262</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1098399334266137</v>
+        <v>0.1099276514054326</v>
       </c>
       <c r="C32">
-        <v>40870.986554902</v>
+        <v>40217.10310122071</v>
       </c>
       <c r="D32">
-        <v>53828.006554902</v>
+        <v>53754.37710122071</v>
       </c>
       <c r="E32">
-        <v>-5447.880000000001</v>
+        <v>-4867.626</v>
       </c>
       <c r="F32">
-        <v>17407.62</v>
+        <v>17987.874</v>
       </c>
       <c r="G32">
         <v>4450.6</v>
@@ -3917,45 +3917,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M32">
-        <v>1324.155778139226</v>
+        <v>1386.282178077201</v>
       </c>
       <c r="N32">
-        <v>4332.044221860773</v>
+        <v>4269.917821922798</v>
       </c>
       <c r="O32">
-        <v>1299.613266558232</v>
+        <v>1280.975346576839</v>
       </c>
       <c r="P32">
-        <v>3032.430955302541</v>
+        <v>2988.942475345959</v>
       </c>
       <c r="Q32">
-        <v>7323.530955302542</v>
+        <v>7280.042475345959</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1340939122806606</v>
+        <v>0.1350782368322845</v>
       </c>
       <c r="T32">
-        <v>1.215398936811827</v>
+        <v>1.228948534769596</v>
       </c>
       <c r="U32">
-        <v>0.07606759442929167</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.05324731610050417</v>
+        <v>0.05394731610050417</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.271551801819262</v>
+        <v>4.080121702094774</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1099276514054326</v>
+        <v>0.1098053693842515</v>
       </c>
       <c r="C33">
-        <v>40217.10310122071</v>
+        <v>39739.54663960701</v>
       </c>
       <c r="D33">
-        <v>53754.37710122071</v>
+        <v>53857.07463960701</v>
       </c>
       <c r="E33">
-        <v>-4867.626</v>
+        <v>-4287.371999999999</v>
       </c>
       <c r="F33">
-        <v>17987.874</v>
+        <v>18568.128</v>
       </c>
       <c r="G33">
         <v>4450.6</v>
@@ -3999,28 +3999,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M33">
-        <v>1386.282178077201</v>
+        <v>1431.000958015175</v>
       </c>
       <c r="N33">
-        <v>4269.917821922798</v>
+        <v>4225.199041984824</v>
       </c>
       <c r="O33">
-        <v>1280.975346576839</v>
+        <v>1267.559712595447</v>
       </c>
       <c r="P33">
-        <v>2988.942475345959</v>
+        <v>2957.639329389377</v>
       </c>
       <c r="Q33">
-        <v>7280.042475345959</v>
+        <v>7248.739329389377</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1350782368322845</v>
+        <v>0.1360915121060149</v>
       </c>
       <c r="T33">
-        <v>1.228948534769596</v>
+        <v>1.242896650314357</v>
       </c>
       <c r="U33">
         <v>0.07706759442929167</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.080121702094774</v>
+        <v>3.952617898904313</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1098053693842515</v>
+        <v>0.1096830873630704</v>
       </c>
       <c r="C34">
-        <v>39739.54663960701</v>
+        <v>39262.38333565308</v>
       </c>
       <c r="D34">
-        <v>53857.07463960701</v>
+        <v>53960.16533565309</v>
       </c>
       <c r="E34">
-        <v>-4287.371999999999</v>
+        <v>-3707.117999999999</v>
       </c>
       <c r="F34">
-        <v>18568.128</v>
+        <v>19148.382</v>
       </c>
       <c r="G34">
         <v>4450.6</v>
@@ -4081,28 +4081,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M34">
-        <v>1431.000958015175</v>
+        <v>1475.719737953149</v>
       </c>
       <c r="N34">
-        <v>4225.199041984824</v>
+        <v>4180.48026204685</v>
       </c>
       <c r="O34">
-        <v>1267.559712595447</v>
+        <v>1254.144078614055</v>
       </c>
       <c r="P34">
-        <v>2957.639329389377</v>
+        <v>2926.336183432795</v>
       </c>
       <c r="Q34">
-        <v>7248.739329389377</v>
+        <v>7217.436183432796</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1360915121060149</v>
+        <v>0.1371350344028418</v>
       </c>
       <c r="T34">
-        <v>1.242896650314357</v>
+        <v>1.257261127517172</v>
       </c>
       <c r="U34">
         <v>0.07706759442929167</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.952617898904313</v>
+        <v>3.832841598937515</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1096830873630704</v>
+        <v>0.1095608053418893</v>
       </c>
       <c r="C35">
-        <v>39262.38333565308</v>
+        <v>38785.61545138092</v>
       </c>
       <c r="D35">
-        <v>53960.16533565309</v>
+        <v>54063.65145138092</v>
       </c>
       <c r="E35">
-        <v>-3707.117999999999</v>
+        <v>-3126.863999999998</v>
       </c>
       <c r="F35">
-        <v>19148.382</v>
+        <v>19728.636</v>
       </c>
       <c r="G35">
         <v>4450.6</v>
@@ -4163,28 +4163,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M35">
-        <v>1475.719737953149</v>
+        <v>1520.438517891123</v>
       </c>
       <c r="N35">
-        <v>4180.48026204685</v>
+        <v>4135.761482108875</v>
       </c>
       <c r="O35">
-        <v>1254.144078614055</v>
+        <v>1240.728444632663</v>
       </c>
       <c r="P35">
-        <v>2926.336183432795</v>
+        <v>2895.033037476213</v>
       </c>
       <c r="Q35">
-        <v>7217.436183432796</v>
+        <v>7186.133037476213</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1371350344028418</v>
+        <v>0.1382101785874513</v>
       </c>
       <c r="T35">
-        <v>1.257261127517172</v>
+        <v>1.27206089190795</v>
       </c>
       <c r="U35">
         <v>0.07706759442929167</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.832841598937515</v>
+        <v>3.720110963674647</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1095608053418893</v>
+        <v>0.1094385233207082</v>
       </c>
       <c r="C36">
-        <v>38785.61545138092</v>
+        <v>38309.24526619837</v>
       </c>
       <c r="D36">
-        <v>54063.65145138092</v>
+        <v>54167.53526619838</v>
       </c>
       <c r="E36">
-        <v>-3126.863999999998</v>
+        <v>-2546.609999999997</v>
       </c>
       <c r="F36">
-        <v>19728.636</v>
+        <v>20308.89</v>
       </c>
       <c r="G36">
         <v>4450.6</v>
@@ -4245,28 +4245,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M36">
-        <v>1520.438517891123</v>
+        <v>1565.157297829098</v>
       </c>
       <c r="N36">
-        <v>4135.761482108875</v>
+        <v>4091.042702170901</v>
       </c>
       <c r="O36">
-        <v>1240.728444632663</v>
+        <v>1227.31281065127</v>
       </c>
       <c r="P36">
-        <v>2895.033037476213</v>
+        <v>2863.729891519631</v>
       </c>
       <c r="Q36">
-        <v>7186.133037476213</v>
+        <v>7154.829891519631</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1382101785874513</v>
+        <v>0.1393184041315873</v>
       </c>
       <c r="T36">
-        <v>1.27206089190795</v>
+        <v>1.287316033664598</v>
       </c>
       <c r="U36">
         <v>0.07706759442929167</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.720110963674647</v>
+        <v>3.613822078998228</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1094385233207082</v>
+        <v>0.1093162412995271</v>
       </c>
       <c r="C37">
-        <v>38309.24526619837</v>
+        <v>37833.27507706675</v>
       </c>
       <c r="D37">
-        <v>54167.53526619838</v>
+        <v>54271.81907706675</v>
       </c>
       <c r="E37">
-        <v>-2546.609999999997</v>
+        <v>-1966.355999999996</v>
       </c>
       <c r="F37">
-        <v>20308.89</v>
+        <v>20889.144</v>
       </c>
       <c r="G37">
         <v>4450.6</v>
@@ -4327,28 +4327,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M37">
-        <v>1565.157297829098</v>
+        <v>1609.876077767072</v>
       </c>
       <c r="N37">
-        <v>4091.042702170901</v>
+        <v>4046.323922232927</v>
       </c>
       <c r="O37">
-        <v>1227.31281065127</v>
+        <v>1213.897176669878</v>
       </c>
       <c r="P37">
-        <v>2863.729891519631</v>
+        <v>2832.426745563049</v>
       </c>
       <c r="Q37">
-        <v>7154.829891519631</v>
+        <v>7123.526745563049</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1393184041315873</v>
+        <v>0.1404612617239775</v>
       </c>
       <c r="T37">
-        <v>1.287316033664598</v>
+        <v>1.303047898601142</v>
       </c>
       <c r="U37">
         <v>0.07706759442929167</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.613822078998228</v>
+        <v>3.513438132359389</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1093162412995271</v>
+        <v>0.109193959278346</v>
       </c>
       <c r="C38">
-        <v>37833.27507706673</v>
+        <v>37357.70719866991</v>
       </c>
       <c r="D38">
-        <v>54271.81907706674</v>
+        <v>54376.50519866991</v>
       </c>
       <c r="E38">
-        <v>-1966.356</v>
+        <v>-1386.101999999999</v>
       </c>
       <c r="F38">
-        <v>20889.144</v>
+        <v>21469.398</v>
       </c>
       <c r="G38">
         <v>4450.6</v>
@@ -4409,28 +4409,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M38">
-        <v>1609.876077767072</v>
+        <v>1654.594857705046</v>
       </c>
       <c r="N38">
-        <v>4046.323922232928</v>
+        <v>4001.605142294953</v>
       </c>
       <c r="O38">
-        <v>1213.897176669878</v>
+        <v>1200.481542688486</v>
       </c>
       <c r="P38">
-        <v>2832.426745563049</v>
+        <v>2801.123599606467</v>
       </c>
       <c r="Q38">
-        <v>7123.526745563049</v>
+        <v>7092.223599606467</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1404612617239775</v>
+        <v>0.1416404005097769</v>
       </c>
       <c r="T38">
-        <v>1.303047898601142</v>
+        <v>1.319279187821385</v>
       </c>
       <c r="U38">
         <v>0.07706759442929167</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.51343813235939</v>
+        <v>3.418480344998325</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.109193959278346</v>
+        <v>0.1090716772571649</v>
       </c>
       <c r="C39">
-        <v>37357.70719866991</v>
+        <v>36882.54396358565</v>
       </c>
       <c r="D39">
-        <v>54376.50519866991</v>
+        <v>54481.59596358566</v>
       </c>
       <c r="E39">
-        <v>-1386.101999999999</v>
+        <v>-805.8479999999981</v>
       </c>
       <c r="F39">
-        <v>21469.398</v>
+        <v>22049.652</v>
       </c>
       <c r="G39">
         <v>4450.6</v>
@@ -4491,28 +4491,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M39">
-        <v>1654.594857705046</v>
+        <v>1699.31363764302</v>
       </c>
       <c r="N39">
-        <v>4001.605142294953</v>
+        <v>3956.886362356979</v>
       </c>
       <c r="O39">
-        <v>1200.481542688486</v>
+        <v>1187.065908707094</v>
       </c>
       <c r="P39">
-        <v>2801.123599606467</v>
+        <v>2769.820453649885</v>
       </c>
       <c r="Q39">
-        <v>7092.223599606467</v>
+        <v>7060.920453649886</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1416404005097769</v>
+        <v>0.1428575760306021</v>
       </c>
       <c r="T39">
-        <v>1.319279187821385</v>
+        <v>1.336034067016475</v>
       </c>
       <c r="U39">
         <v>0.07706759442929167</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.418480344998325</v>
+        <v>3.328520335919421</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1090716772571649</v>
+        <v>0.1089493952359838</v>
       </c>
       <c r="C40">
-        <v>36882.54396358565</v>
+        <v>36407.78772245893</v>
       </c>
       <c r="D40">
-        <v>54481.59596358566</v>
+        <v>54587.09372245894</v>
       </c>
       <c r="E40">
-        <v>-805.8479999999981</v>
+        <v>-225.5939999999973</v>
       </c>
       <c r="F40">
-        <v>22049.652</v>
+        <v>22629.906</v>
       </c>
       <c r="G40">
         <v>4450.6</v>
@@ -4573,28 +4573,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M40">
-        <v>1699.31363764302</v>
+        <v>1744.032417580994</v>
       </c>
       <c r="N40">
-        <v>3956.886362356979</v>
+        <v>3912.167582419004</v>
       </c>
       <c r="O40">
-        <v>1187.065908707094</v>
+        <v>1173.650274725701</v>
       </c>
       <c r="P40">
-        <v>2769.820453649885</v>
+        <v>2738.517307693303</v>
       </c>
       <c r="Q40">
-        <v>7060.920453649886</v>
+        <v>7029.617307693304</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1428575760306021</v>
+        <v>0.1441146589455527</v>
       </c>
       <c r="T40">
-        <v>1.336034067016475</v>
+        <v>1.353338286513044</v>
       </c>
       <c r="U40">
         <v>0.07706759442929167</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.328520335919421</v>
+        <v>3.243173660639436</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1089493952359838</v>
+        <v>0.1088271132148027</v>
       </c>
       <c r="C41">
-        <v>36407.78772245893</v>
+        <v>35933.44084417709</v>
       </c>
       <c r="D41">
-        <v>54587.09372245894</v>
+        <v>54693.0008441771</v>
       </c>
       <c r="E41">
-        <v>-225.5939999999973</v>
+        <v>354.6600000000035</v>
       </c>
       <c r="F41">
-        <v>22629.906</v>
+        <v>23210.16</v>
       </c>
       <c r="G41">
         <v>4450.6</v>
@@ -4655,28 +4655,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M41">
-        <v>1744.032417580994</v>
+        <v>1788.751197518969</v>
       </c>
       <c r="N41">
-        <v>3912.167582419004</v>
+        <v>3867.44880248103</v>
       </c>
       <c r="O41">
-        <v>1173.650274725701</v>
+        <v>1160.234640744309</v>
       </c>
       <c r="P41">
-        <v>2738.517307693303</v>
+        <v>2707.214161736722</v>
       </c>
       <c r="Q41">
-        <v>7029.617307693304</v>
+        <v>6998.314161736722</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1441146589455527</v>
+        <v>0.145413644624335</v>
       </c>
       <c r="T41">
-        <v>1.353338286513044</v>
+        <v>1.371219313326164</v>
       </c>
       <c r="U41">
         <v>0.07706759442929167</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.243173660639436</v>
+        <v>3.16209431912345</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1088271132148027</v>
+        <v>0.1087048311936216</v>
       </c>
       <c r="C42">
-        <v>35933.44084417709</v>
+        <v>35459.50571604719</v>
       </c>
       <c r="D42">
-        <v>54693.0008441771</v>
+        <v>54799.3197160472</v>
       </c>
       <c r="E42">
-        <v>354.6600000000035</v>
+        <v>934.9140000000007</v>
       </c>
       <c r="F42">
-        <v>23210.16</v>
+        <v>23790.414</v>
       </c>
       <c r="G42">
         <v>4450.6</v>
@@ -4737,28 +4737,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M42">
-        <v>1788.751197518969</v>
+        <v>1833.469977456943</v>
       </c>
       <c r="N42">
-        <v>3867.44880248103</v>
+        <v>3822.730022543056</v>
       </c>
       <c r="O42">
-        <v>1160.234640744309</v>
+        <v>1146.819006762917</v>
       </c>
       <c r="P42">
-        <v>2707.214161736722</v>
+        <v>2675.91101578014</v>
       </c>
       <c r="Q42">
-        <v>6998.314161736722</v>
+        <v>6967.01101578014</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.145413644624335</v>
+        <v>0.1467566637159574</v>
       </c>
       <c r="T42">
-        <v>1.371219313326164</v>
+        <v>1.389706476641425</v>
       </c>
       <c r="U42">
         <v>0.07706759442929167</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.16209431912345</v>
+        <v>3.084970067437513</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1087048311936216</v>
+        <v>0.1085825491724405</v>
       </c>
       <c r="C43">
-        <v>35459.50571604719</v>
+        <v>34985.98474397541</v>
       </c>
       <c r="D43">
-        <v>54799.3197160472</v>
+        <v>54906.05274397542</v>
       </c>
       <c r="E43">
-        <v>934.9140000000007</v>
+        <v>1515.168000000001</v>
       </c>
       <c r="F43">
-        <v>23790.414</v>
+        <v>24370.668</v>
       </c>
       <c r="G43">
         <v>4450.6</v>
@@ -4819,28 +4819,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M43">
-        <v>1833.469977456943</v>
+        <v>1878.188757394917</v>
       </c>
       <c r="N43">
-        <v>3822.730022543056</v>
+        <v>3778.011242605082</v>
       </c>
       <c r="O43">
-        <v>1146.819006762917</v>
+        <v>1133.403372781524</v>
       </c>
       <c r="P43">
-        <v>2675.91101578014</v>
+        <v>2644.607869823557</v>
       </c>
       <c r="Q43">
-        <v>6967.01101578014</v>
+        <v>6935.707869823558</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1467566637159574</v>
+        <v>0.1481459938107392</v>
       </c>
       <c r="T43">
-        <v>1.389706476641425</v>
+        <v>1.408831128346866</v>
       </c>
       <c r="U43">
         <v>0.07706759442929167</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.084970067437513</v>
+        <v>3.01151839916519</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1085825491724405</v>
+        <v>0.1092127671512594</v>
       </c>
       <c r="C44">
-        <v>34985.98474397542</v>
+        <v>33860.05543063208</v>
       </c>
       <c r="D44">
-        <v>54906.05274397543</v>
+        <v>54360.37743063208</v>
       </c>
       <c r="E44">
-        <v>1515.168000000001</v>
+        <v>2095.421999999999</v>
       </c>
       <c r="F44">
-        <v>24370.668</v>
+        <v>24950.922</v>
       </c>
       <c r="G44">
         <v>4450.6</v>
@@ -4901,45 +4901,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M44">
-        <v>1878.188757394917</v>
+        <v>1985.284842332891</v>
       </c>
       <c r="N44">
-        <v>3778.011242605082</v>
+        <v>3670.915157667108</v>
       </c>
       <c r="O44">
-        <v>1133.403372781524</v>
+        <v>1101.274547300132</v>
       </c>
       <c r="P44">
-        <v>2644.607869823557</v>
+        <v>2569.640610366976</v>
       </c>
       <c r="Q44">
-        <v>6935.707869823558</v>
+        <v>6860.740610366976</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1481459938107392</v>
+        <v>0.1495840723298993</v>
       </c>
       <c r="T44">
-        <v>1.408831128346866</v>
+        <v>1.428626820463025</v>
       </c>
       <c r="U44">
-        <v>0.07706759442929167</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.05394731610050417</v>
+        <v>0.05569731610050417</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.01151839916519</v>
+        <v>2.849062199736259</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1092127671512594</v>
+        <v>0.1091079851300783</v>
       </c>
       <c r="C45">
-        <v>33860.05543063208</v>
+        <v>33369.77412850969</v>
       </c>
       <c r="D45">
-        <v>54360.37743063208</v>
+        <v>54450.35012850969</v>
       </c>
       <c r="E45">
-        <v>2095.421999999999</v>
+        <v>2675.675999999999</v>
       </c>
       <c r="F45">
-        <v>24950.922</v>
+        <v>25531.176</v>
       </c>
       <c r="G45">
         <v>4450.6</v>
@@ -4983,28 +4983,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M45">
-        <v>1985.284842332891</v>
+        <v>2031.454257270865</v>
       </c>
       <c r="N45">
-        <v>3670.915157667108</v>
+        <v>3624.745742729134</v>
       </c>
       <c r="O45">
-        <v>1101.274547300132</v>
+        <v>1087.42372281874</v>
       </c>
       <c r="P45">
-        <v>2569.640610366976</v>
+        <v>2537.322019910393</v>
       </c>
       <c r="Q45">
-        <v>6860.740610366976</v>
+        <v>6828.422019910394</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1495840723298993</v>
+        <v>0.1510735107961723</v>
       </c>
       <c r="T45">
-        <v>1.428626820463025</v>
+        <v>1.449129501583333</v>
       </c>
       <c r="U45">
         <v>0.07956759442929168</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.849062199736259</v>
+        <v>2.784310786105889</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1091079851300783</v>
+        <v>0.1090032031088972</v>
       </c>
       <c r="C46">
-        <v>33369.77412850969</v>
+        <v>32879.79115054401</v>
       </c>
       <c r="D46">
-        <v>54450.35012850969</v>
+        <v>54540.62115054402</v>
       </c>
       <c r="E46">
-        <v>2675.675999999999</v>
+        <v>3255.93</v>
       </c>
       <c r="F46">
-        <v>25531.176</v>
+        <v>26111.43</v>
       </c>
       <c r="G46">
         <v>4450.6</v>
@@ -5065,28 +5065,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M46">
-        <v>2031.454257270865</v>
+        <v>2077.62367220884</v>
       </c>
       <c r="N46">
-        <v>3624.745742729134</v>
+        <v>3578.576327791159</v>
       </c>
       <c r="O46">
-        <v>1087.42372281874</v>
+        <v>1073.572898337348</v>
       </c>
       <c r="P46">
-        <v>2537.322019910393</v>
+        <v>2505.003429453812</v>
       </c>
       <c r="Q46">
-        <v>6828.422019910394</v>
+        <v>6796.103429453812</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1510735107961723</v>
+        <v>0.1526171106612188</v>
       </c>
       <c r="T46">
-        <v>1.449129501583333</v>
+        <v>1.470377734744379</v>
       </c>
       <c r="U46">
         <v>0.07956759442929168</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.784310786105889</v>
+        <v>2.722437213081314</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1090032031088972</v>
+        <v>0.1088984210877161</v>
       </c>
       <c r="C47">
-        <v>32879.79115054401</v>
+        <v>32390.10798293746</v>
       </c>
       <c r="D47">
-        <v>54540.62115054402</v>
+        <v>54631.19198293746</v>
       </c>
       <c r="E47">
-        <v>3255.93</v>
+        <v>3836.184000000001</v>
       </c>
       <c r="F47">
-        <v>26111.43</v>
+        <v>26691.684</v>
       </c>
       <c r="G47">
         <v>4450.6</v>
@@ -5147,28 +5147,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M47">
-        <v>2077.62367220884</v>
+        <v>2123.793087146814</v>
       </c>
       <c r="N47">
-        <v>3578.576327791159</v>
+        <v>3532.406912853185</v>
       </c>
       <c r="O47">
-        <v>1073.572898337348</v>
+        <v>1059.722073855955</v>
       </c>
       <c r="P47">
-        <v>2505.003429453812</v>
+        <v>2472.68483899723</v>
       </c>
       <c r="Q47">
-        <v>6796.103429453812</v>
+        <v>6763.78483899723</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1526171106612188</v>
+        <v>0.1542178808916374</v>
       </c>
       <c r="T47">
-        <v>1.470377734744379</v>
+        <v>1.492412939503982</v>
       </c>
       <c r="U47">
         <v>0.07956759442929168</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.722437213081314</v>
+        <v>2.663253795405633</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1088984210877161</v>
+        <v>0.108793639066535</v>
       </c>
       <c r="C48">
-        <v>32390.10798293746</v>
+        <v>31900.72612178087</v>
       </c>
       <c r="D48">
-        <v>54631.19198293746</v>
+        <v>54722.06412178087</v>
       </c>
       <c r="E48">
-        <v>3836.184000000001</v>
+        <v>4416.438000000002</v>
       </c>
       <c r="F48">
-        <v>26691.684</v>
+        <v>27271.938</v>
       </c>
       <c r="G48">
         <v>4450.6</v>
@@ -5229,28 +5229,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M48">
-        <v>2123.793087146814</v>
+        <v>2169.962502084788</v>
       </c>
       <c r="N48">
-        <v>3532.406912853185</v>
+        <v>3486.237497915211</v>
       </c>
       <c r="O48">
-        <v>1059.722073855955</v>
+        <v>1045.871249374563</v>
       </c>
       <c r="P48">
-        <v>2472.68483899723</v>
+        <v>2440.366248540648</v>
       </c>
       <c r="Q48">
-        <v>6763.78483899723</v>
+        <v>6731.466248540648</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1542178808916374</v>
+        <v>0.1558790575458454</v>
       </c>
       <c r="T48">
-        <v>1.492412939503982</v>
+        <v>1.515279661424325</v>
       </c>
       <c r="U48">
         <v>0.07956759442929168</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.663253795405633</v>
+        <v>2.606588821035301</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.108793639066535</v>
+        <v>0.1086888570453539</v>
       </c>
       <c r="C49">
-        <v>31900.72612178087</v>
+        <v>31411.64707313586</v>
       </c>
       <c r="D49">
-        <v>54722.06412178087</v>
+        <v>54813.23907313587</v>
       </c>
       <c r="E49">
-        <v>4416.438000000002</v>
+        <v>4996.692000000003</v>
       </c>
       <c r="F49">
-        <v>27271.938</v>
+        <v>27852.192</v>
       </c>
       <c r="G49">
         <v>4450.6</v>
@@ -5311,28 +5311,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M49">
-        <v>2169.962502084788</v>
+        <v>2216.131917022763</v>
       </c>
       <c r="N49">
-        <v>3486.237497915211</v>
+        <v>3440.068082977236</v>
       </c>
       <c r="O49">
-        <v>1045.871249374563</v>
+        <v>1032.020424893171</v>
       </c>
       <c r="P49">
-        <v>2440.366248540648</v>
+        <v>2408.047658084065</v>
       </c>
       <c r="Q49">
-        <v>6731.466248540648</v>
+        <v>6699.147658084066</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1558790575458454</v>
+        <v>0.1576041256098306</v>
       </c>
       <c r="T49">
-        <v>1.515279661424325</v>
+        <v>1.539025872649296</v>
       </c>
       <c r="U49">
         <v>0.07956759442929168</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.606588821035301</v>
+        <v>2.552284887263732</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1086888570453539</v>
+        <v>0.1085840750241728</v>
       </c>
       <c r="C50">
-        <v>31411.64707313587</v>
+        <v>30922.87235311815</v>
       </c>
       <c r="D50">
-        <v>54813.23907313587</v>
+        <v>54904.71835311815</v>
       </c>
       <c r="E50">
-        <v>4996.691999999999</v>
+        <v>5576.946</v>
       </c>
       <c r="F50">
-        <v>27852.192</v>
+        <v>28432.446</v>
       </c>
       <c r="G50">
         <v>4450.6</v>
@@ -5393,28 +5393,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M50">
-        <v>2216.131917022762</v>
+        <v>2262.301331960736</v>
       </c>
       <c r="N50">
-        <v>3440.068082977237</v>
+        <v>3393.898668039263</v>
       </c>
       <c r="O50">
-        <v>1032.020424893171</v>
+        <v>1018.169600411779</v>
       </c>
       <c r="P50">
-        <v>2408.047658084066</v>
+        <v>2375.729067627484</v>
       </c>
       <c r="Q50">
-        <v>6699.147658084066</v>
+        <v>6666.829067627485</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1576041256098306</v>
+        <v>0.1593968434018152</v>
       </c>
       <c r="T50">
-        <v>1.539025872649296</v>
+        <v>1.563703307843874</v>
       </c>
       <c r="U50">
         <v>0.07956759442929168</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.552284887263732</v>
+        <v>2.500197440584881</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1085840750241728</v>
+        <v>0.1097042930029917</v>
       </c>
       <c r="C51">
-        <v>30922.87235311815</v>
+        <v>29380.15949893333</v>
       </c>
       <c r="D51">
-        <v>54904.71835311815</v>
+        <v>53942.25949893333</v>
       </c>
       <c r="E51">
-        <v>5576.946</v>
+        <v>6157.200000000001</v>
       </c>
       <c r="F51">
-        <v>28432.446</v>
+        <v>29012.7</v>
       </c>
       <c r="G51">
         <v>4450.6</v>
@@ -5475,45 +5475,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M51">
-        <v>2262.301331960736</v>
+        <v>2410.015196898711</v>
       </c>
       <c r="N51">
-        <v>3393.898668039263</v>
+        <v>3246.184803101288</v>
       </c>
       <c r="O51">
-        <v>1018.169600411779</v>
+        <v>973.8554409303864</v>
       </c>
       <c r="P51">
-        <v>2375.729067627484</v>
+        <v>2272.329362170902</v>
       </c>
       <c r="Q51">
-        <v>6666.829067627485</v>
+        <v>6563.429362170902</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1593968434018152</v>
+        <v>0.1612612699054793</v>
       </c>
       <c r="T51">
-        <v>1.563703307843874</v>
+        <v>1.589367840446236</v>
       </c>
       <c r="U51">
-        <v>0.07956759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.05569731610050417</v>
+        <v>0.05814731610050417</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.500197440584881</v>
+        <v>2.346956154997939</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1097042930029917</v>
+        <v>0.1096240109818106</v>
       </c>
       <c r="C52">
-        <v>29380.15949893333</v>
+        <v>28867.75760589168</v>
       </c>
       <c r="D52">
-        <v>53942.25949893333</v>
+        <v>54010.11160589168</v>
       </c>
       <c r="E52">
-        <v>6157.200000000001</v>
+        <v>6737.454000000002</v>
       </c>
       <c r="F52">
-        <v>29012.7</v>
+        <v>29592.954</v>
       </c>
       <c r="G52">
         <v>4450.6</v>
@@ -5557,28 +5557,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M52">
-        <v>2410.015196898711</v>
+        <v>2458.215500836685</v>
       </c>
       <c r="N52">
-        <v>3246.184803101288</v>
+        <v>3197.984499163314</v>
       </c>
       <c r="O52">
-        <v>973.8554409303864</v>
+        <v>959.3953497489941</v>
       </c>
       <c r="P52">
-        <v>2272.329362170902</v>
+        <v>2238.58914941432</v>
       </c>
       <c r="Q52">
-        <v>6563.429362170902</v>
+        <v>6529.68914941432</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1612612699054793</v>
+        <v>0.1632017954501092</v>
       </c>
       <c r="T52">
-        <v>1.589367840446236</v>
+        <v>1.616079904991551</v>
       </c>
       <c r="U52">
         <v>0.08306759442929168</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.346956154997939</v>
+        <v>2.300937406860724</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1096240109818106</v>
+        <v>0.1095437289606295</v>
       </c>
       <c r="C53">
-        <v>28867.75760589168</v>
+        <v>28355.5266254834</v>
       </c>
       <c r="D53">
-        <v>54010.11160589168</v>
+        <v>54078.13462548341</v>
       </c>
       <c r="E53">
-        <v>6737.454000000002</v>
+        <v>7317.708000000002</v>
       </c>
       <c r="F53">
-        <v>29592.954</v>
+        <v>30173.208</v>
       </c>
       <c r="G53">
         <v>4450.6</v>
@@ -5639,28 +5639,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M53">
-        <v>2458.215500836685</v>
+        <v>2506.415804774659</v>
       </c>
       <c r="N53">
-        <v>3197.984499163314</v>
+        <v>3149.78419522534</v>
       </c>
       <c r="O53">
-        <v>959.3953497489941</v>
+        <v>944.9352585676019</v>
       </c>
       <c r="P53">
-        <v>2238.58914941432</v>
+        <v>2204.848936657738</v>
       </c>
       <c r="Q53">
-        <v>6529.68914941432</v>
+        <v>6495.948936657738</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1632017954501092</v>
+        <v>0.1652231762257653</v>
       </c>
       <c r="T53">
-        <v>1.616079904991551</v>
+        <v>1.643904972226254</v>
       </c>
       <c r="U53">
         <v>0.08306759442929168</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.300937406860724</v>
+        <v>2.256688610574941</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1095437289606295</v>
+        <v>0.1105022469394484</v>
       </c>
       <c r="C54">
-        <v>28355.5266254834</v>
+        <v>26974.14334865899</v>
       </c>
       <c r="D54">
-        <v>54078.13462548341</v>
+        <v>53277.005348659</v>
       </c>
       <c r="E54">
-        <v>7317.708000000002</v>
+        <v>7897.962000000003</v>
       </c>
       <c r="F54">
-        <v>30173.208</v>
+        <v>30753.462</v>
       </c>
       <c r="G54">
         <v>4450.6</v>
@@ -5721,45 +5721,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M54">
-        <v>2506.415804774659</v>
+        <v>2640.725802312634</v>
       </c>
       <c r="N54">
-        <v>3149.78419522534</v>
+        <v>3015.474197687365</v>
       </c>
       <c r="O54">
-        <v>944.9352585676019</v>
+        <v>904.6422593062096</v>
       </c>
       <c r="P54">
-        <v>2204.848936657738</v>
+        <v>2110.831938381156</v>
       </c>
       <c r="Q54">
-        <v>6495.948936657738</v>
+        <v>6401.931938381156</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1652231762257653</v>
+        <v>0.1673305732046409</v>
       </c>
       <c r="T54">
-        <v>1.643904972226254</v>
+        <v>1.6729140848752</v>
       </c>
       <c r="U54">
-        <v>0.08306759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V54">
         <v>0.3</v>
       </c>
       <c r="W54">
-        <v>0.05814731610050417</v>
+        <v>0.06010731610050417</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.256688610574941</v>
+        <v>2.141911134827608</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1105022469394484</v>
+        <v>0.1104415649182673</v>
       </c>
       <c r="C55">
-        <v>26974.14334865899</v>
+        <v>26443.90293312467</v>
       </c>
       <c r="D55">
-        <v>53277.005348659</v>
+        <v>53327.01893312467</v>
       </c>
       <c r="E55">
-        <v>7897.962000000003</v>
+        <v>8478.216000000004</v>
       </c>
       <c r="F55">
-        <v>30753.462</v>
+        <v>31333.716</v>
       </c>
       <c r="G55">
         <v>4450.6</v>
@@ -5803,28 +5803,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M55">
-        <v>2640.725802312634</v>
+        <v>2690.550817450608</v>
       </c>
       <c r="N55">
-        <v>3015.474197687365</v>
+        <v>2965.649182549391</v>
       </c>
       <c r="O55">
-        <v>904.6422593062096</v>
+        <v>889.6947547648174</v>
       </c>
       <c r="P55">
-        <v>2110.831938381156</v>
+        <v>2075.954427784574</v>
       </c>
       <c r="Q55">
-        <v>6401.931938381156</v>
+        <v>6367.054427784575</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1673305732046409</v>
+        <v>0.1695295961391197</v>
       </c>
       <c r="T55">
-        <v>1.6729140848752</v>
+        <v>1.703184463291491</v>
       </c>
       <c r="U55">
         <v>0.08586759442929168</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.141911134827608</v>
+        <v>2.102246113812282</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1104415649182673</v>
+        <v>0.1103808828970862</v>
       </c>
       <c r="C56">
-        <v>26443.90293312467</v>
+        <v>25913.75650594278</v>
       </c>
       <c r="D56">
-        <v>53327.01893312467</v>
+        <v>53377.12650594279</v>
       </c>
       <c r="E56">
-        <v>8478.216000000004</v>
+        <v>9058.470000000005</v>
       </c>
       <c r="F56">
-        <v>31333.716</v>
+        <v>31913.97</v>
       </c>
       <c r="G56">
         <v>4450.6</v>
@@ -5885,28 +5885,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M56">
-        <v>2690.550817450608</v>
+        <v>2740.375832588582</v>
       </c>
       <c r="N56">
-        <v>2965.649182549391</v>
+        <v>2915.824167411417</v>
       </c>
       <c r="O56">
-        <v>889.6947547648174</v>
+        <v>874.7472502234251</v>
       </c>
       <c r="P56">
-        <v>2075.954427784574</v>
+        <v>2041.076917187992</v>
       </c>
       <c r="Q56">
-        <v>6367.054427784575</v>
+        <v>6332.176917187992</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1695295961391197</v>
+        <v>0.1718263534262421</v>
       </c>
       <c r="T56">
-        <v>1.703184463291491</v>
+        <v>1.734800191859617</v>
       </c>
       <c r="U56">
         <v>0.08586759442929168</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.102246113812282</v>
+        <v>2.064023457197513</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1103808828970862</v>
+        <v>0.1103202008759051</v>
       </c>
       <c r="C57">
-        <v>25913.75650594278</v>
+        <v>25383.70433230488</v>
       </c>
       <c r="D57">
-        <v>53377.12650594279</v>
+        <v>53427.32833230489</v>
       </c>
       <c r="E57">
-        <v>9058.470000000005</v>
+        <v>9638.724000000006</v>
       </c>
       <c r="F57">
-        <v>31913.97</v>
+        <v>32494.22400000001</v>
       </c>
       <c r="G57">
         <v>4450.6</v>
@@ -5967,28 +5967,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M57">
-        <v>2740.375832588582</v>
+        <v>2790.200847726556</v>
       </c>
       <c r="N57">
-        <v>2915.824167411417</v>
+        <v>2865.999152273443</v>
       </c>
       <c r="O57">
-        <v>874.7472502234251</v>
+        <v>859.7997456820327</v>
       </c>
       <c r="P57">
-        <v>2041.076917187992</v>
+        <v>2006.19940659141</v>
       </c>
       <c r="Q57">
-        <v>6332.176917187992</v>
+        <v>6297.29940659141</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1718263534262421</v>
+        <v>0.17422750877187</v>
       </c>
       <c r="T57">
-        <v>1.734800191859617</v>
+        <v>1.767852998999022</v>
       </c>
       <c r="U57">
         <v>0.08586759442929168</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.064023457197513</v>
+        <v>2.027165895461843</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1103202008759051</v>
+        <v>0.113371718854724</v>
       </c>
       <c r="C58">
-        <v>25383.70433230488</v>
+        <v>22390.68866618825</v>
       </c>
       <c r="D58">
-        <v>53427.32833230489</v>
+        <v>51014.56666618826</v>
       </c>
       <c r="E58">
-        <v>9638.724000000006</v>
+        <v>10218.978</v>
       </c>
       <c r="F58">
-        <v>32494.22400000001</v>
+        <v>33074.478</v>
       </c>
       <c r="G58">
         <v>4450.6</v>
@@ -6049,45 +6049,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M58">
-        <v>2790.200847726556</v>
+        <v>3098.00679126453</v>
       </c>
       <c r="N58">
-        <v>2865.999152273443</v>
+        <v>2558.193208735468</v>
       </c>
       <c r="O58">
-        <v>859.7997456820327</v>
+        <v>767.4579626206405</v>
       </c>
       <c r="P58">
-        <v>2006.19940659141</v>
+        <v>1790.735246114828</v>
       </c>
       <c r="Q58">
-        <v>6297.29940659141</v>
+        <v>6081.835246114828</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.17422750877187</v>
+        <v>0.1767403457614806</v>
       </c>
       <c r="T58">
-        <v>1.767852998999022</v>
+        <v>1.802443146005376</v>
       </c>
       <c r="U58">
-        <v>0.08586759442929168</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V58">
         <v>0.3</v>
       </c>
       <c r="W58">
-        <v>0.06010731610050417</v>
+        <v>0.06556731610050417</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.027165895461843</v>
+        <v>1.825754551587434</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.113371718854724</v>
+        <v>0.1133656368335429</v>
       </c>
       <c r="C59">
-        <v>22390.68866618825</v>
+        <v>21815.02681819847</v>
       </c>
       <c r="D59">
-        <v>51014.56666618826</v>
+        <v>51019.15881819848</v>
       </c>
       <c r="E59">
-        <v>10218.978</v>
+        <v>10799.232</v>
       </c>
       <c r="F59">
-        <v>33074.478</v>
+        <v>33654.732</v>
       </c>
       <c r="G59">
         <v>4450.6</v>
@@ -6131,28 +6131,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M59">
-        <v>3098.00679126453</v>
+        <v>3152.357787602505</v>
       </c>
       <c r="N59">
-        <v>2558.193208735468</v>
+        <v>2503.842212397494</v>
       </c>
       <c r="O59">
-        <v>767.4579626206405</v>
+        <v>751.1526637192483</v>
       </c>
       <c r="P59">
-        <v>1790.735246114828</v>
+        <v>1752.689548678246</v>
       </c>
       <c r="Q59">
-        <v>6081.835246114828</v>
+        <v>6043.789548678246</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1767403457614806</v>
+        <v>0.1793728416553584</v>
       </c>
       <c r="T59">
-        <v>1.802443146005376</v>
+        <v>1.838680442869175</v>
       </c>
       <c r="U59">
         <v>0.09366759442929168</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.825754551587434</v>
+        <v>1.794276024835927</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1133656368335429</v>
+        <v>0.1133595548123618</v>
       </c>
       <c r="C60">
-        <v>21815.02681819849</v>
+        <v>21239.36579702193</v>
       </c>
       <c r="D60">
-        <v>51019.15881819849</v>
+        <v>51023.75179702193</v>
       </c>
       <c r="E60">
-        <v>10799.232</v>
+        <v>11379.486</v>
       </c>
       <c r="F60">
-        <v>33654.732</v>
+        <v>34234.986</v>
       </c>
       <c r="G60">
         <v>4450.6</v>
@@ -6213,28 +6213,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M60">
-        <v>3152.357787602504</v>
+        <v>3206.708783940478</v>
       </c>
       <c r="N60">
-        <v>2503.842212397495</v>
+        <v>2449.49121605952</v>
       </c>
       <c r="O60">
-        <v>751.1526637192484</v>
+        <v>734.8473648178561</v>
       </c>
       <c r="P60">
-        <v>1752.689548678246</v>
+        <v>1714.643851241664</v>
       </c>
       <c r="Q60">
-        <v>6043.789548678247</v>
+        <v>6005.743851241665</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1793728416553584</v>
+        <v>0.1821337519830838</v>
       </c>
       <c r="T60">
-        <v>1.838680442869175</v>
+        <v>1.87668541275072</v>
       </c>
       <c r="U60">
         <v>0.09366759442929168</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.794276024835927</v>
+        <v>1.763864566787861</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1133595548123618</v>
+        <v>0.1149914727911807</v>
       </c>
       <c r="C61">
-        <v>21239.36579702193</v>
+        <v>19455.68925743166</v>
       </c>
       <c r="D61">
-        <v>51023.75179702193</v>
+        <v>49820.32925743166</v>
       </c>
       <c r="E61">
-        <v>11379.486</v>
+        <v>11959.74</v>
       </c>
       <c r="F61">
-        <v>34234.986</v>
+        <v>34815.24</v>
       </c>
       <c r="G61">
         <v>4450.6</v>
@@ -6295,45 +6295,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M61">
-        <v>3206.708783940478</v>
+        <v>3396.839216278453</v>
       </c>
       <c r="N61">
-        <v>2449.49121605952</v>
+        <v>2259.360783721546</v>
       </c>
       <c r="O61">
-        <v>734.8473648178561</v>
+        <v>677.8082351164638</v>
       </c>
       <c r="P61">
-        <v>1714.643851241664</v>
+        <v>1581.552548605082</v>
       </c>
       <c r="Q61">
-        <v>6005.743851241665</v>
+        <v>5872.652548605083</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1821337519830838</v>
+        <v>0.1850327078271956</v>
       </c>
       <c r="T61">
-        <v>1.87668541275072</v>
+        <v>1.916590631126343</v>
       </c>
       <c r="U61">
-        <v>0.09366759442929168</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.06556731610050417</v>
+        <v>0.06829731610050417</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.763864566787861</v>
+        <v>1.665136216307842</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1149914727911807</v>
+        <v>0.1150126907699996</v>
       </c>
       <c r="C62">
-        <v>19455.68925743166</v>
+        <v>18860.1622391575</v>
       </c>
       <c r="D62">
-        <v>49820.32925743166</v>
+        <v>49805.0562391575</v>
       </c>
       <c r="E62">
-        <v>11959.74</v>
+        <v>12539.994</v>
       </c>
       <c r="F62">
-        <v>34815.24</v>
+        <v>35395.494</v>
       </c>
       <c r="G62">
         <v>4450.6</v>
@@ -6377,28 +6377,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M62">
-        <v>3396.839216278453</v>
+        <v>3453.453203216427</v>
       </c>
       <c r="N62">
-        <v>2259.360783721546</v>
+        <v>2202.746796783572</v>
       </c>
       <c r="O62">
-        <v>677.8082351164638</v>
+        <v>660.8240390350716</v>
       </c>
       <c r="P62">
-        <v>1581.552548605082</v>
+        <v>1541.9227577485</v>
       </c>
       <c r="Q62">
-        <v>5872.652548605083</v>
+        <v>5833.0227577485</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1850327078271956</v>
+        <v>0.1880803280735694</v>
       </c>
       <c r="T62">
-        <v>1.916590631126343</v>
+        <v>1.958542270957126</v>
       </c>
       <c r="U62">
         <v>0.09756759442929168</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.665136216307842</v>
+        <v>1.637838901286402</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1150126907699996</v>
+        <v>0.1150339087488185</v>
       </c>
       <c r="C63">
-        <v>18860.1622391575</v>
+        <v>18264.64458226661</v>
       </c>
       <c r="D63">
-        <v>49805.0562391575</v>
+        <v>49789.79258226661</v>
       </c>
       <c r="E63">
-        <v>12539.994</v>
+        <v>13120.248</v>
       </c>
       <c r="F63">
-        <v>35395.494</v>
+        <v>35975.748</v>
       </c>
       <c r="G63">
         <v>4450.6</v>
@@ -6459,28 +6459,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M63">
-        <v>3453.453203216427</v>
+        <v>3510.067190154401</v>
       </c>
       <c r="N63">
-        <v>2202.746796783572</v>
+        <v>2146.132809845598</v>
       </c>
       <c r="O63">
-        <v>660.8240390350716</v>
+        <v>643.8398429536793</v>
       </c>
       <c r="P63">
-        <v>1541.9227577485</v>
+        <v>1502.292966891919</v>
       </c>
       <c r="Q63">
-        <v>5833.0227577485</v>
+        <v>5793.392966891919</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1880803280735694</v>
+        <v>0.191288349385542</v>
       </c>
       <c r="T63">
-        <v>1.958542270957126</v>
+        <v>2.002701891831634</v>
       </c>
       <c r="U63">
         <v>0.09756759442929168</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.637838901286402</v>
+        <v>1.611422144814041</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1150339087488185</v>
+        <v>0.1150551267276374</v>
       </c>
       <c r="C64">
-        <v>18264.64458226661</v>
+        <v>17669.13627815477</v>
       </c>
       <c r="D64">
-        <v>49789.79258226661</v>
+        <v>49774.53827815477</v>
       </c>
       <c r="E64">
-        <v>13120.248</v>
+        <v>13700.502</v>
       </c>
       <c r="F64">
-        <v>35975.748</v>
+        <v>36556.002</v>
       </c>
       <c r="G64">
         <v>4450.6</v>
@@ -6541,28 +6541,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M64">
-        <v>3510.067190154401</v>
+        <v>3566.681177092375</v>
       </c>
       <c r="N64">
-        <v>2146.132809845598</v>
+        <v>2089.518822907623</v>
       </c>
       <c r="O64">
-        <v>643.8398429536793</v>
+        <v>626.855646872287</v>
       </c>
       <c r="P64">
-        <v>1502.292966891919</v>
+        <v>1462.663176035336</v>
       </c>
       <c r="Q64">
-        <v>5793.392966891919</v>
+        <v>5753.763176035337</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.191288349385542</v>
+        <v>0.1946697772549184</v>
       </c>
       <c r="T64">
-        <v>2.002701891831634</v>
+        <v>2.0492485192399</v>
       </c>
       <c r="U64">
         <v>0.09756759442929168</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.611422144814041</v>
+        <v>1.585844015531278</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1150551267276374</v>
+        <v>0.1150763447064563</v>
       </c>
       <c r="C65">
-        <v>17669.13627815477</v>
+        <v>17073.63731822823</v>
       </c>
       <c r="D65">
-        <v>49774.53827815477</v>
+        <v>49759.29331822824</v>
       </c>
       <c r="E65">
-        <v>13700.502</v>
+        <v>14280.756</v>
       </c>
       <c r="F65">
-        <v>36556.002</v>
+        <v>37136.256</v>
       </c>
       <c r="G65">
         <v>4450.6</v>
@@ -6623,28 +6623,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M65">
-        <v>3566.681177092375</v>
+        <v>3623.29516403035</v>
       </c>
       <c r="N65">
-        <v>2089.518822907623</v>
+        <v>2032.904835969649</v>
       </c>
       <c r="O65">
-        <v>626.855646872287</v>
+        <v>609.8714507908946</v>
       </c>
       <c r="P65">
-        <v>1462.663176035336</v>
+        <v>1423.033385178754</v>
       </c>
       <c r="Q65">
-        <v>5753.763176035337</v>
+        <v>5714.133385178755</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1946697772549184</v>
+        <v>0.1982390622281491</v>
       </c>
       <c r="T65">
-        <v>2.0492485192399</v>
+        <v>2.098381070393069</v>
       </c>
       <c r="U65">
         <v>0.09756759442929168</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.585844015531278</v>
+        <v>1.561065202788602</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1150763447064563</v>
+        <v>0.1150975626852753</v>
       </c>
       <c r="C66">
-        <v>17073.63731822823</v>
+        <v>16478.14769390381</v>
       </c>
       <c r="D66">
-        <v>49759.29331822824</v>
+        <v>49744.05769390381</v>
       </c>
       <c r="E66">
-        <v>14280.756</v>
+        <v>14861.01</v>
       </c>
       <c r="F66">
-        <v>37136.256</v>
+        <v>37716.51</v>
       </c>
       <c r="G66">
         <v>4450.6</v>
@@ -6705,28 +6705,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M66">
-        <v>3623.29516403035</v>
+        <v>3679.909150968324</v>
       </c>
       <c r="N66">
-        <v>2032.904835969649</v>
+        <v>1976.290849031675</v>
       </c>
       <c r="O66">
-        <v>609.8714507908946</v>
+        <v>592.8872547095025</v>
       </c>
       <c r="P66">
-        <v>1423.033385178754</v>
+        <v>1383.403594322172</v>
       </c>
       <c r="Q66">
-        <v>5714.133385178755</v>
+        <v>5674.503594322173</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1982390622281491</v>
+        <v>0.2020123063427073</v>
       </c>
       <c r="T66">
-        <v>2.098381070393069</v>
+        <v>2.150321195897849</v>
       </c>
       <c r="U66">
         <v>0.09756759442929168</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.561065202788602</v>
+        <v>1.537048815053393</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1150975626852753</v>
+        <v>0.1151187806640941</v>
       </c>
       <c r="C67">
-        <v>16478.14769390381</v>
+        <v>15882.66739660886</v>
       </c>
       <c r="D67">
-        <v>49744.05769390381</v>
+        <v>49728.83139660887</v>
       </c>
       <c r="E67">
-        <v>14861.01</v>
+        <v>15441.264</v>
       </c>
       <c r="F67">
-        <v>37716.51</v>
+        <v>38296.764</v>
       </c>
       <c r="G67">
         <v>4450.6</v>
@@ -6787,28 +6787,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M67">
-        <v>3679.909150968324</v>
+        <v>3736.523137906298</v>
       </c>
       <c r="N67">
-        <v>1976.290849031675</v>
+        <v>1919.6768620937</v>
       </c>
       <c r="O67">
-        <v>592.8872547095025</v>
+        <v>575.9030586281101</v>
       </c>
       <c r="P67">
-        <v>1383.403594322172</v>
+        <v>1343.77380346559</v>
       </c>
       <c r="Q67">
-        <v>5674.503594322173</v>
+        <v>5634.873803465591</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2020123063427073</v>
+        <v>0.2060075059934159</v>
       </c>
       <c r="T67">
-        <v>2.150321195897849</v>
+        <v>2.205316622902909</v>
       </c>
       <c r="U67">
         <v>0.09756759442929168</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.537048815053393</v>
+        <v>1.513760196643493</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1151187806640941</v>
+        <v>0.121799798642913</v>
       </c>
       <c r="C68">
-        <v>15882.66739660886</v>
+        <v>10930.83317456864</v>
       </c>
       <c r="D68">
-        <v>49728.83139660887</v>
+        <v>45357.25117456865</v>
       </c>
       <c r="E68">
-        <v>15441.264</v>
+        <v>16021.518</v>
       </c>
       <c r="F68">
-        <v>38296.764</v>
+        <v>38877.018</v>
       </c>
       <c r="G68">
         <v>4450.6</v>
@@ -6869,45 +6869,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M68">
-        <v>3736.523137906298</v>
+        <v>4345.190780444273</v>
       </c>
       <c r="N68">
-        <v>1919.6768620937</v>
+        <v>1311.009219555726</v>
       </c>
       <c r="O68">
-        <v>575.9030586281101</v>
+        <v>393.3027658667179</v>
       </c>
       <c r="P68">
-        <v>1343.77380346559</v>
+        <v>917.7064536890084</v>
       </c>
       <c r="Q68">
-        <v>5634.873803465591</v>
+        <v>5208.806453689009</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2060075059934159</v>
+        <v>0.2102448389562886</v>
       </c>
       <c r="T68">
-        <v>2.205316622902909</v>
+        <v>2.263645106090094</v>
       </c>
       <c r="U68">
-        <v>0.09756759442929168</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V68">
         <v>0.3</v>
       </c>
       <c r="W68">
-        <v>0.06829731610050417</v>
+        <v>0.07823731610050418</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.513760196643493</v>
+        <v>1.301714996141477</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.121799798642913</v>
+        <v>0.121920416621732</v>
       </c>
       <c r="C69">
-        <v>10930.83317456864</v>
+        <v>10278.70752430371</v>
       </c>
       <c r="D69">
-        <v>45357.25117456865</v>
+        <v>45285.37952430372</v>
       </c>
       <c r="E69">
-        <v>16021.518</v>
+        <v>16601.772</v>
       </c>
       <c r="F69">
-        <v>38877.018</v>
+        <v>39457.272</v>
       </c>
       <c r="G69">
         <v>4450.6</v>
@@ -6951,28 +6951,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M69">
-        <v>4345.190780444273</v>
+        <v>4410.044374182247</v>
       </c>
       <c r="N69">
-        <v>1311.009219555726</v>
+        <v>1246.155625817752</v>
       </c>
       <c r="O69">
-        <v>393.3027658667179</v>
+        <v>373.8466877453255</v>
       </c>
       <c r="P69">
-        <v>917.7064536890084</v>
+        <v>872.3089380724261</v>
       </c>
       <c r="Q69">
-        <v>5208.806453689009</v>
+        <v>5163.408938072426</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2102448389562886</v>
+        <v>0.214747005229341</v>
       </c>
       <c r="T69">
-        <v>2.263645106090094</v>
+        <v>2.325619119476478</v>
       </c>
       <c r="U69">
         <v>0.1117675944292917</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.301714996141477</v>
+        <v>1.282572128551161</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.121920416621732</v>
+        <v>0.1220410346005509</v>
       </c>
       <c r="C70">
-        <v>10278.70752430371</v>
+        <v>9626.809284730014</v>
       </c>
       <c r="D70">
-        <v>45285.37952430372</v>
+        <v>45213.73528473002</v>
       </c>
       <c r="E70">
-        <v>16601.772</v>
+        <v>17182.02600000001</v>
       </c>
       <c r="F70">
-        <v>39457.272</v>
+        <v>40037.52600000001</v>
       </c>
       <c r="G70">
         <v>4450.6</v>
@@ -7033,28 +7033,28 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M70">
-        <v>4410.044374182247</v>
+        <v>4474.897967920221</v>
       </c>
       <c r="N70">
-        <v>1246.155625817752</v>
+        <v>1181.302032079778</v>
       </c>
       <c r="O70">
-        <v>373.8466877453255</v>
+        <v>354.3906096239333</v>
       </c>
       <c r="P70">
-        <v>872.3089380724261</v>
+        <v>826.9114224558444</v>
       </c>
       <c r="Q70">
-        <v>5163.408938072426</v>
+        <v>5118.011422455845</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.214747005229341</v>
+        <v>0.2195396338425903</v>
       </c>
       <c r="T70">
-        <v>2.325619119476478</v>
+        <v>2.391591456307145</v>
       </c>
       <c r="U70">
         <v>0.1117675944292917</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.282572128551161</v>
+        <v>1.263984126688101</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1220410346005509</v>
+        <v>0.1365225711411666</v>
       </c>
       <c r="C71">
-        <v>9626.809284730014</v>
+        <v>1829.339641175182</v>
       </c>
       <c r="D71">
-        <v>45213.73528473002</v>
+        <v>37996.51964117519</v>
       </c>
       <c r="E71">
-        <v>17182.02600000001</v>
+        <v>17762.28000000001</v>
       </c>
       <c r="F71">
-        <v>40037.52600000001</v>
+        <v>40617.78000000001</v>
       </c>
       <c r="G71">
         <v>4450.6</v>
@@ -7115,45 +7115,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M71">
-        <v>4474.897967920221</v>
+        <v>5701.420069658197</v>
       </c>
       <c r="N71">
-        <v>1181.302032079778</v>
+        <v>-45.22006965819764</v>
       </c>
       <c r="O71">
-        <v>354.3906096239333</v>
+        <v>-13.56602089745929</v>
       </c>
       <c r="P71">
-        <v>826.9114224558444</v>
+        <v>-31.65404876073835</v>
       </c>
       <c r="Q71">
-        <v>5118.011422455845</v>
+        <v>4259.445951239262</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2195396338425903</v>
+        <v>0.2250288511488905</v>
       </c>
       <c r="T71">
-        <v>2.391591456307145</v>
+        <v>2.467152598697113</v>
       </c>
       <c r="U71">
-        <v>0.1117675944292917</v>
+        <v>0.1403675944292917</v>
       </c>
       <c r="V71">
-        <v>0.3</v>
+        <v>0.2976205891283726</v>
       </c>
       <c r="W71">
-        <v>0.07823731610050418</v>
+        <v>0.09859130828071344</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.263984126688101</v>
+        <v>0.9920686304279087</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1365225711411666</v>
+        <v>0.1374682470854595</v>
       </c>
       <c r="C72">
-        <v>1829.339641175182</v>
+        <v>857.1026401474301</v>
       </c>
       <c r="D72">
-        <v>37996.51964117519</v>
+        <v>37604.53664014744</v>
       </c>
       <c r="E72">
-        <v>17762.28000000001</v>
+        <v>18342.53400000001</v>
       </c>
       <c r="F72">
-        <v>40617.78000000001</v>
+        <v>41198.03400000001</v>
       </c>
       <c r="G72">
         <v>4450.6</v>
@@ -7197,37 +7197,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M72">
-        <v>5701.420069658197</v>
+        <v>5782.868927796171</v>
       </c>
       <c r="N72">
-        <v>-45.22006965819764</v>
+        <v>-126.6689277961723</v>
       </c>
       <c r="O72">
-        <v>-13.56602089745929</v>
+        <v>-38.00067833885169</v>
       </c>
       <c r="P72">
-        <v>-31.65404876073835</v>
+        <v>-88.6682494573206</v>
       </c>
       <c r="Q72">
-        <v>4259.445951239262</v>
+        <v>4202.43175054268</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2250288511488905</v>
+        <v>0.2312091563609212</v>
       </c>
       <c r="T72">
-        <v>2.467152598697113</v>
+        <v>2.552226826238392</v>
       </c>
       <c r="U72">
         <v>0.1403675944292917</v>
       </c>
       <c r="V72">
-        <v>0.2976205891283726</v>
+        <v>0.2934287498448744</v>
       </c>
       <c r="W72">
-        <v>0.09859130828071344</v>
+        <v>0.09917970667717227</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9920686304279087</v>
+        <v>0.9780958328162479</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1374682470854594</v>
+        <v>0.1384139230297524</v>
       </c>
       <c r="C73">
-        <v>857.1026401474373</v>
+        <v>-107.1293248659276</v>
       </c>
       <c r="D73">
-        <v>37604.53664014744</v>
+        <v>37220.55867513407</v>
       </c>
       <c r="E73">
-        <v>18342.534</v>
+        <v>18922.788</v>
       </c>
       <c r="F73">
-        <v>41198.034</v>
+        <v>41778.288</v>
       </c>
       <c r="G73">
         <v>4450.6</v>
@@ -7279,37 +7279,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M73">
-        <v>5782.86892779617</v>
+        <v>5864.317785934144</v>
       </c>
       <c r="N73">
-        <v>-126.6689277961714</v>
+        <v>-208.1177859341451</v>
       </c>
       <c r="O73">
-        <v>-38.00067833885141</v>
+        <v>-62.43533578024353</v>
       </c>
       <c r="P73">
-        <v>-88.66824945731997</v>
+        <v>-145.6824501539016</v>
       </c>
       <c r="Q73">
-        <v>4202.431750542681</v>
+        <v>4145.417549846099</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2312091563609211</v>
+        <v>0.2378309119452397</v>
       </c>
       <c r="T73">
-        <v>2.552226826238392</v>
+        <v>2.643377784318334</v>
       </c>
       <c r="U73">
         <v>0.1403675944292917</v>
       </c>
       <c r="V73">
-        <v>0.2934287498448744</v>
+        <v>0.2893533505414734</v>
       </c>
       <c r="W73">
-        <v>0.09917970667717227</v>
+        <v>0.0997517606737295</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9780958328162481</v>
+        <v>0.964511168471578</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1384139230297524</v>
+        <v>0.1393595989740453</v>
       </c>
       <c r="C74">
-        <v>-107.1293248659276</v>
+        <v>-1063.598992292864</v>
       </c>
       <c r="D74">
-        <v>37220.55867513407</v>
+        <v>36844.34300770714</v>
       </c>
       <c r="E74">
-        <v>18922.788</v>
+        <v>19503.042</v>
       </c>
       <c r="F74">
-        <v>41778.288</v>
+        <v>42358.542</v>
       </c>
       <c r="G74">
         <v>4450.6</v>
@@ -7361,37 +7361,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M74">
-        <v>5864.317785934144</v>
+        <v>5945.766644072119</v>
       </c>
       <c r="N74">
-        <v>-208.1177859341451</v>
+        <v>-289.5666440721197</v>
       </c>
       <c r="O74">
-        <v>-62.43533578024353</v>
+        <v>-86.86999322163592</v>
       </c>
       <c r="P74">
-        <v>-145.6824501539016</v>
+        <v>-202.6966508504838</v>
       </c>
       <c r="Q74">
-        <v>4145.417549846099</v>
+        <v>4088.403349149517</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2378309119452397</v>
+        <v>0.2449431679432116</v>
       </c>
       <c r="T74">
-        <v>2.643377784318334</v>
+        <v>2.741280665219013</v>
       </c>
       <c r="U74">
         <v>0.1403675944292917</v>
       </c>
       <c r="V74">
-        <v>0.2893533505414734</v>
+        <v>0.285389606013508</v>
       </c>
       <c r="W74">
-        <v>0.0997517606737295</v>
+        <v>0.1003081419580523</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.964511168471578</v>
+        <v>0.9512986867116934</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1393595989740453</v>
+        <v>0.1403052749183382</v>
       </c>
       <c r="C75">
-        <v>-1063.598992292864</v>
+        <v>-2012.539384621487</v>
       </c>
       <c r="D75">
-        <v>36844.34300770714</v>
+        <v>36475.65661537852</v>
       </c>
       <c r="E75">
-        <v>19503.042</v>
+        <v>20083.296</v>
       </c>
       <c r="F75">
-        <v>42358.542</v>
+        <v>42938.796</v>
       </c>
       <c r="G75">
         <v>4450.6</v>
@@ -7443,37 +7443,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M75">
-        <v>5945.766644072119</v>
+        <v>6027.215502210093</v>
       </c>
       <c r="N75">
-        <v>-289.5666440721197</v>
+        <v>-371.0155022100944</v>
       </c>
       <c r="O75">
-        <v>-86.86999322163592</v>
+        <v>-111.3046506630283</v>
       </c>
       <c r="P75">
-        <v>-202.6966508504838</v>
+        <v>-259.7108515470661</v>
       </c>
       <c r="Q75">
-        <v>4088.403349149517</v>
+        <v>4031.389148452934</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2449431679432116</v>
+        <v>0.252602520556412</v>
       </c>
       <c r="T75">
-        <v>2.741280665219013</v>
+        <v>2.846714536958206</v>
       </c>
       <c r="U75">
         <v>0.1403675944292917</v>
       </c>
       <c r="V75">
-        <v>0.285389606013508</v>
+        <v>0.2815329897160281</v>
       </c>
       <c r="W75">
-        <v>0.1003081419580523</v>
+        <v>0.1008494859103663</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9512986867116934</v>
+        <v>0.9384432990534272</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1403052749183382</v>
+        <v>0.1412509508626311</v>
       </c>
       <c r="C76">
-        <v>-2012.539384621487</v>
+        <v>-2954.174289701135</v>
       </c>
       <c r="D76">
-        <v>36475.65661537852</v>
+        <v>36114.27571029887</v>
       </c>
       <c r="E76">
-        <v>20083.296</v>
+        <v>20663.55</v>
       </c>
       <c r="F76">
-        <v>42938.796</v>
+        <v>43519.05</v>
       </c>
       <c r="G76">
         <v>4450.6</v>
@@ -7525,37 +7525,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M76">
-        <v>6027.215502210093</v>
+        <v>6108.664360348067</v>
       </c>
       <c r="N76">
-        <v>-371.0155022100944</v>
+        <v>-452.4643603480681</v>
       </c>
       <c r="O76">
-        <v>-111.3046506630283</v>
+        <v>-135.7393081044204</v>
       </c>
       <c r="P76">
-        <v>-259.7108515470661</v>
+        <v>-316.7250522436477</v>
       </c>
       <c r="Q76">
-        <v>4031.389148452934</v>
+        <v>3974.374947756352</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.252602520556412</v>
+        <v>0.2608746213786685</v>
       </c>
       <c r="T76">
-        <v>2.846714536958206</v>
+        <v>2.960583118436534</v>
       </c>
       <c r="U76">
         <v>0.1403675944292917</v>
       </c>
       <c r="V76">
-        <v>0.2815329897160281</v>
+        <v>0.2777792165198145</v>
       </c>
       <c r="W76">
-        <v>0.1008494859103663</v>
+        <v>0.101376394023952</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9384432990534272</v>
+        <v>0.9259307217327148</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1412509508626311</v>
+        <v>0.142196626806924</v>
       </c>
       <c r="C77">
-        <v>-2954.174289701135</v>
+        <v>-3888.718713713562</v>
       </c>
       <c r="D77">
-        <v>36114.27571029887</v>
+        <v>35759.98528628644</v>
       </c>
       <c r="E77">
-        <v>20663.55</v>
+        <v>21243.804</v>
       </c>
       <c r="F77">
-        <v>43519.05</v>
+        <v>44099.304</v>
       </c>
       <c r="G77">
         <v>4450.6</v>
@@ -7607,37 +7607,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M77">
-        <v>6108.664360348067</v>
+        <v>6190.113218486042</v>
       </c>
       <c r="N77">
-        <v>-452.4643603480681</v>
+        <v>-533.9132184860428</v>
       </c>
       <c r="O77">
-        <v>-135.7393081044204</v>
+        <v>-160.1739655458128</v>
       </c>
       <c r="P77">
-        <v>-316.7250522436477</v>
+        <v>-373.7392529402299</v>
       </c>
       <c r="Q77">
-        <v>3974.374947756352</v>
+        <v>3917.36074705977</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2608746213786685</v>
+        <v>0.269836063936113</v>
       </c>
       <c r="T77">
-        <v>2.960583118436534</v>
+        <v>3.083940748371391</v>
       </c>
       <c r="U77">
         <v>0.1403675944292917</v>
       </c>
       <c r="V77">
-        <v>0.2777792165198145</v>
+        <v>0.2741242268287643</v>
       </c>
       <c r="W77">
-        <v>0.101376394023952</v>
+        <v>0.1018894361345486</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9259307217327148</v>
+        <v>0.9137474227625475</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.142196626806924</v>
+        <v>0.1431423027512169</v>
       </c>
       <c r="C78">
-        <v>-3888.718713713562</v>
+        <v>-4816.379307740201</v>
       </c>
       <c r="D78">
-        <v>35759.98528628644</v>
+        <v>35412.57869225981</v>
       </c>
       <c r="E78">
-        <v>21243.804</v>
+        <v>21824.058</v>
       </c>
       <c r="F78">
-        <v>44099.304</v>
+        <v>44679.558</v>
       </c>
       <c r="G78">
         <v>4450.6</v>
@@ -7689,37 +7689,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M78">
-        <v>6190.113218486042</v>
+        <v>6271.562076624016</v>
       </c>
       <c r="N78">
-        <v>-533.9132184860428</v>
+        <v>-615.3620766240174</v>
       </c>
       <c r="O78">
-        <v>-160.1739655458128</v>
+        <v>-184.6086229872052</v>
       </c>
       <c r="P78">
-        <v>-373.7392529402299</v>
+        <v>-430.7534536368122</v>
       </c>
       <c r="Q78">
-        <v>3917.36074705977</v>
+        <v>3860.346546363188</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.269836063936113</v>
+        <v>0.279576762368118</v>
       </c>
       <c r="T78">
-        <v>3.083940748371391</v>
+        <v>3.218025128735364</v>
       </c>
       <c r="U78">
         <v>0.1403675944292917</v>
       </c>
       <c r="V78">
-        <v>0.2741242268287643</v>
+        <v>0.2705641719348842</v>
       </c>
       <c r="W78">
-        <v>0.1018894361345486</v>
+        <v>0.1023891524760387</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9137474227625475</v>
+        <v>0.9018805731162807</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1431423027512169</v>
+        <v>0.1440879786955099</v>
       </c>
       <c r="C79">
-        <v>-4816.379307740201</v>
+        <v>-5737.354769704507</v>
       </c>
       <c r="D79">
-        <v>35412.57869225981</v>
+        <v>35071.8572302955</v>
       </c>
       <c r="E79">
-        <v>21824.058</v>
+        <v>22404.31200000001</v>
       </c>
       <c r="F79">
-        <v>44679.558</v>
+        <v>45259.81200000001</v>
       </c>
       <c r="G79">
         <v>4450.6</v>
@@ -7771,37 +7771,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M79">
-        <v>6271.562076624016</v>
+        <v>6353.01093476199</v>
       </c>
       <c r="N79">
-        <v>-615.3620766240174</v>
+        <v>-696.8109347619911</v>
       </c>
       <c r="O79">
-        <v>-184.6086229872052</v>
+        <v>-209.0432804285973</v>
       </c>
       <c r="P79">
-        <v>-430.7534536368122</v>
+        <v>-487.7676543333938</v>
       </c>
       <c r="Q79">
-        <v>3860.346546363188</v>
+        <v>3803.332345666607</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.279576762368118</v>
+        <v>0.2902029788393961</v>
       </c>
       <c r="T79">
-        <v>3.218025128735364</v>
+        <v>3.364298998223335</v>
       </c>
       <c r="U79">
         <v>0.1403675944292917</v>
       </c>
       <c r="V79">
-        <v>0.2705641719348842</v>
+        <v>0.2670954004998216</v>
       </c>
       <c r="W79">
-        <v>0.1023891524760387</v>
+        <v>0.1028760555780035</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9018805731162807</v>
+        <v>0.890318001666072</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1440879786955099</v>
+        <v>0.1450336546398028</v>
       </c>
       <c r="C80">
-        <v>-5737.354769704507</v>
+        <v>-6651.836223331542</v>
       </c>
       <c r="D80">
-        <v>35071.8572302955</v>
+        <v>34737.62977666847</v>
       </c>
       <c r="E80">
-        <v>22404.31200000001</v>
+        <v>22984.56600000001</v>
       </c>
       <c r="F80">
-        <v>45259.81200000001</v>
+        <v>45840.06600000001</v>
       </c>
       <c r="G80">
         <v>4450.6</v>
@@ -7853,37 +7853,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M80">
-        <v>6353.01093476199</v>
+        <v>6434.459792899965</v>
       </c>
       <c r="N80">
-        <v>-696.8109347619911</v>
+        <v>-778.2597928999658</v>
       </c>
       <c r="O80">
-        <v>-209.0432804285973</v>
+        <v>-233.4779378699897</v>
       </c>
       <c r="P80">
-        <v>-487.7676543333938</v>
+        <v>-544.781855029976</v>
       </c>
       <c r="Q80">
-        <v>3803.332345666607</v>
+        <v>3746.318144970024</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2902029788393961</v>
+        <v>0.3018412159269864</v>
       </c>
       <c r="T80">
-        <v>3.364298998223335</v>
+        <v>3.524503712424447</v>
       </c>
       <c r="U80">
         <v>0.1403675944292917</v>
       </c>
       <c r="V80">
-        <v>0.2670954004998216</v>
+        <v>0.2637144460631149</v>
       </c>
       <c r="W80">
-        <v>0.1028760555780035</v>
+        <v>0.1033506320191591</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.890318001666072</v>
+        <v>0.8790481535437166</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1450336546398028</v>
+        <v>0.1459793305840957</v>
       </c>
       <c r="C81">
-        <v>-6651.836223331542</v>
+        <v>-7560.00757564378</v>
       </c>
       <c r="D81">
-        <v>34737.62977666847</v>
+        <v>34409.71242435623</v>
       </c>
       <c r="E81">
-        <v>22984.56600000001</v>
+        <v>23564.82000000001</v>
       </c>
       <c r="F81">
-        <v>45840.06600000001</v>
+        <v>46420.32000000001</v>
       </c>
       <c r="G81">
         <v>4450.6</v>
@@ -7935,37 +7935,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M81">
-        <v>6434.459792899965</v>
+        <v>6515.908651037939</v>
       </c>
       <c r="N81">
-        <v>-778.2597928999658</v>
+        <v>-859.7086510379404</v>
       </c>
       <c r="O81">
-        <v>-233.4779378699897</v>
+        <v>-257.9125953113821</v>
       </c>
       <c r="P81">
-        <v>-544.781855029976</v>
+        <v>-601.7960557265583</v>
       </c>
       <c r="Q81">
-        <v>3746.318144970024</v>
+        <v>3689.303944273442</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3018412159269864</v>
+        <v>0.3146432767233357</v>
       </c>
       <c r="T81">
-        <v>3.524503712424447</v>
+        <v>3.700728898045669</v>
       </c>
       <c r="U81">
         <v>0.1403675944292917</v>
       </c>
       <c r="V81">
-        <v>0.2637144460631149</v>
+        <v>0.260418015487326</v>
       </c>
       <c r="W81">
-        <v>0.1033506320191591</v>
+        <v>0.1038133440492857</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8790481535437166</v>
+        <v>0.8680600516244201</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1459793305840957</v>
+        <v>0.1469250065283886</v>
       </c>
       <c r="C82">
-        <v>-7560.00757564378</v>
+        <v>-8462.045854397962</v>
       </c>
       <c r="D82">
-        <v>34409.71242435623</v>
+        <v>34087.92814560205</v>
       </c>
       <c r="E82">
-        <v>23564.82000000001</v>
+        <v>24145.07400000001</v>
       </c>
       <c r="F82">
-        <v>46420.32000000001</v>
+        <v>47000.57400000001</v>
       </c>
       <c r="G82">
         <v>4450.6</v>
@@ -8017,37 +8017,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M82">
-        <v>6515.908651037939</v>
+        <v>6597.357509175913</v>
       </c>
       <c r="N82">
-        <v>-859.7086510379404</v>
+        <v>-941.1575091759141</v>
       </c>
       <c r="O82">
-        <v>-257.9125953113821</v>
+        <v>-282.3472527527742</v>
       </c>
       <c r="P82">
-        <v>-601.7960557265583</v>
+        <v>-658.8102564231399</v>
       </c>
       <c r="Q82">
-        <v>3689.303944273442</v>
+        <v>3632.28974357686</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3146432767233357</v>
+        <v>0.3287929228666691</v>
       </c>
       <c r="T82">
-        <v>3.700728898045669</v>
+        <v>3.895504103205967</v>
       </c>
       <c r="U82">
         <v>0.1403675944292917</v>
       </c>
       <c r="V82">
-        <v>0.260418015487326</v>
+        <v>0.2572029782590874</v>
       </c>
       <c r="W82">
-        <v>0.1038133440492857</v>
+        <v>0.1042646310910142</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8680600516244201</v>
+        <v>0.8573432608636249</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1469250065283886</v>
+        <v>0.1478706824726815</v>
       </c>
       <c r="C83">
-        <v>-8462.045854397962</v>
+        <v>-9358.12152676416</v>
       </c>
       <c r="D83">
-        <v>34087.92814560205</v>
+        <v>33772.10647323584</v>
       </c>
       <c r="E83">
-        <v>24145.07400000001</v>
+        <v>24725.328</v>
       </c>
       <c r="F83">
-        <v>47000.57400000001</v>
+        <v>47580.828</v>
       </c>
       <c r="G83">
         <v>4450.6</v>
@@ -8099,37 +8099,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M83">
-        <v>6597.357509175913</v>
+        <v>6678.806367313887</v>
       </c>
       <c r="N83">
-        <v>-941.1575091759141</v>
+        <v>-1022.606367313888</v>
       </c>
       <c r="O83">
-        <v>-282.3472527527742</v>
+        <v>-306.7819101941664</v>
       </c>
       <c r="P83">
-        <v>-658.8102564231399</v>
+        <v>-715.8244571197215</v>
       </c>
       <c r="Q83">
-        <v>3632.28974357686</v>
+        <v>3575.275542880279</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3287929228666691</v>
+        <v>0.3445147519148175</v>
       </c>
       <c r="T83">
-        <v>3.895504103205967</v>
+        <v>4.111920997828522</v>
       </c>
       <c r="U83">
         <v>0.1403675944292917</v>
       </c>
       <c r="V83">
-        <v>0.2572029782590874</v>
+        <v>0.254066356573001</v>
       </c>
       <c r="W83">
-        <v>0.1042646310910142</v>
+        <v>0.1047049111317249</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8573432608636249</v>
+        <v>0.8468878552433368</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1478706824726815</v>
+        <v>0.1488163584169744</v>
       </c>
       <c r="C84">
-        <v>-9358.12152676416</v>
+        <v>-10248.39880045207</v>
       </c>
       <c r="D84">
-        <v>33772.10647323584</v>
+        <v>33462.08319954793</v>
       </c>
       <c r="E84">
-        <v>24725.328</v>
+        <v>25305.582</v>
       </c>
       <c r="F84">
-        <v>47580.828</v>
+        <v>48161.082</v>
       </c>
       <c r="G84">
         <v>4450.6</v>
@@ -8181,37 +8181,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M84">
-        <v>6678.806367313887</v>
+        <v>6760.255225451861</v>
       </c>
       <c r="N84">
-        <v>-1022.606367313888</v>
+        <v>-1104.055225451862</v>
       </c>
       <c r="O84">
-        <v>-306.7819101941664</v>
+        <v>-331.2165676355588</v>
       </c>
       <c r="P84">
-        <v>-715.8244571197215</v>
+        <v>-772.8386578163038</v>
       </c>
       <c r="Q84">
-        <v>3575.275542880279</v>
+        <v>3518.261342183697</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3445147519148175</v>
+        <v>0.3620862079098067</v>
       </c>
       <c r="T84">
-        <v>4.111920997828522</v>
+        <v>4.35379870358314</v>
       </c>
       <c r="U84">
         <v>0.1403675944292917</v>
       </c>
       <c r="V84">
-        <v>0.254066356573001</v>
+        <v>0.2510053161323624</v>
       </c>
       <c r="W84">
-        <v>0.1047049111317249</v>
+        <v>0.1051345820148281</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8468878552433368</v>
+        <v>0.8366843871078748</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1488163584169744</v>
+        <v>0.1497620343612674</v>
       </c>
       <c r="C85">
-        <v>-10248.39880045207</v>
+        <v>-11133.0359084026</v>
       </c>
       <c r="D85">
-        <v>33462.08319954793</v>
+        <v>33157.70009159741</v>
       </c>
       <c r="E85">
-        <v>25305.582</v>
+        <v>25885.836</v>
       </c>
       <c r="F85">
-        <v>48161.082</v>
+        <v>48741.336</v>
       </c>
       <c r="G85">
         <v>4450.6</v>
@@ -8263,37 +8263,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M85">
-        <v>6760.255225451861</v>
+        <v>6841.704083589835</v>
       </c>
       <c r="N85">
-        <v>-1104.055225451862</v>
+        <v>-1185.504083589836</v>
       </c>
       <c r="O85">
-        <v>-331.2165676355588</v>
+        <v>-355.6512250769509</v>
       </c>
       <c r="P85">
-        <v>-772.8386578163038</v>
+        <v>-829.8528585128854</v>
       </c>
       <c r="Q85">
-        <v>3518.261342183697</v>
+        <v>3461.247141487115</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3620862079098067</v>
+        <v>0.3818540959041697</v>
       </c>
       <c r="T85">
-        <v>4.35379870358314</v>
+        <v>4.625911122557088</v>
       </c>
       <c r="U85">
         <v>0.1403675944292917</v>
       </c>
       <c r="V85">
-        <v>0.2510053161323624</v>
+        <v>0.2480171576069772</v>
       </c>
       <c r="W85">
-        <v>0.1051345820148281</v>
+        <v>0.1055540226388098</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8366843871078748</v>
+        <v>0.826723858689924</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1497620343612674</v>
+        <v>0.1507077103055603</v>
       </c>
       <c r="C86">
-        <v>-11133.03590840259</v>
+        <v>-12012.18537808134</v>
       </c>
       <c r="D86">
-        <v>33157.70009159741</v>
+        <v>32858.80462191866</v>
       </c>
       <c r="E86">
-        <v>25885.836</v>
+        <v>26466.09</v>
       </c>
       <c r="F86">
-        <v>48741.336</v>
+        <v>49321.59</v>
       </c>
       <c r="G86">
         <v>4450.6</v>
@@ -8345,37 +8345,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M86">
-        <v>6841.704083589835</v>
+        <v>6923.152941727809</v>
       </c>
       <c r="N86">
-        <v>-1185.504083589836</v>
+        <v>-1266.95294172781</v>
       </c>
       <c r="O86">
-        <v>-355.6512250769509</v>
+        <v>-380.085882518343</v>
       </c>
       <c r="P86">
-        <v>-829.8528585128854</v>
+        <v>-886.867059209467</v>
       </c>
       <c r="Q86">
-        <v>3461.247141487115</v>
+        <v>3404.232940790534</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3818540959041695</v>
+        <v>0.4042577022977808</v>
       </c>
       <c r="T86">
-        <v>4.625911122557085</v>
+        <v>4.934305197394224</v>
       </c>
       <c r="U86">
         <v>0.1403675944292917</v>
       </c>
       <c r="V86">
-        <v>0.2480171576069772</v>
+        <v>0.2450993086939539</v>
       </c>
       <c r="W86">
-        <v>0.1055540226388098</v>
+        <v>0.105963594071639</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.826723858689924</v>
+        <v>0.8169976956465133</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1507077103055603</v>
+        <v>0.1516533862498532</v>
       </c>
       <c r="C87">
-        <v>-12012.18537808134</v>
+        <v>-12885.99428633739</v>
       </c>
       <c r="D87">
-        <v>32858.80462191866</v>
+        <v>32565.2497136626</v>
       </c>
       <c r="E87">
-        <v>26466.09</v>
+        <v>27046.344</v>
       </c>
       <c r="F87">
-        <v>49321.59</v>
+        <v>49901.844</v>
       </c>
       <c r="G87">
         <v>4450.6</v>
@@ -8427,37 +8427,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M87">
-        <v>6923.152941727809</v>
+        <v>7004.601799865783</v>
       </c>
       <c r="N87">
-        <v>-1266.95294172781</v>
+        <v>-1348.401799865784</v>
       </c>
       <c r="O87">
-        <v>-380.085882518343</v>
+        <v>-404.5205399597351</v>
       </c>
       <c r="P87">
-        <v>-886.867059209467</v>
+        <v>-943.8812599060486</v>
       </c>
       <c r="Q87">
-        <v>3404.232940790534</v>
+        <v>3347.218740093952</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4042577022977808</v>
+        <v>0.4298618238904794</v>
       </c>
       <c r="T87">
-        <v>4.934305197394224</v>
+        <v>5.286755568636669</v>
       </c>
       <c r="U87">
         <v>0.1403675944292917</v>
       </c>
       <c r="V87">
-        <v>0.2450993086939539</v>
+        <v>0.2422493167323964</v>
       </c>
       <c r="W87">
-        <v>0.105963594071639</v>
+        <v>0.1063636405874257</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8169976956465133</v>
+        <v>0.8074977224413212</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1516533862498532</v>
+        <v>0.1795001994436337</v>
       </c>
       <c r="C88">
-        <v>-12885.99428633739</v>
+        <v>-20248.8741100744</v>
       </c>
       <c r="D88">
-        <v>32565.2497136626</v>
+        <v>25782.6238899256</v>
       </c>
       <c r="E88">
-        <v>27046.344</v>
+        <v>27626.598</v>
       </c>
       <c r="F88">
-        <v>49901.844</v>
+        <v>50482.098</v>
       </c>
       <c r="G88">
         <v>4450.6</v>
@@ -8509,45 +8509,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M88">
-        <v>7004.601799865783</v>
+        <v>8509.645821603757</v>
       </c>
       <c r="N88">
-        <v>-1348.401799865784</v>
+        <v>-2853.445821603758</v>
       </c>
       <c r="O88">
-        <v>-404.5205399597351</v>
+        <v>-856.0337464811274</v>
       </c>
       <c r="P88">
-        <v>-943.8812599060486</v>
+        <v>-1997.412075122631</v>
       </c>
       <c r="Q88">
-        <v>3347.218740093952</v>
+        <v>2293.687924877369</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4298618238904794</v>
+        <v>0.4776137891858058</v>
       </c>
       <c r="T88">
-        <v>5.286755568636669</v>
+        <v>5.944079345004512</v>
       </c>
       <c r="U88">
-        <v>0.1403675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V88">
-        <v>0.2422493167323964</v>
+        <v>0.1994043037246177</v>
       </c>
       <c r="W88">
-        <v>0.1063636405874257</v>
+        <v>0.134954490631585</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8074977224413212</v>
+        <v>0.6646810124153923</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1795001994436337</v>
+        <v>0.1807278753879267</v>
       </c>
       <c r="C89">
-        <v>-20248.8741100744</v>
+        <v>-21063.71793845057</v>
       </c>
       <c r="D89">
-        <v>25782.6238899256</v>
+        <v>25548.03406154944</v>
       </c>
       <c r="E89">
-        <v>27626.598</v>
+        <v>28206.852</v>
       </c>
       <c r="F89">
-        <v>50482.098</v>
+        <v>51062.352</v>
       </c>
       <c r="G89">
         <v>4450.6</v>
@@ -8591,37 +8591,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M89">
-        <v>8509.645821603757</v>
+        <v>8607.457842541731</v>
       </c>
       <c r="N89">
-        <v>-2853.445821603758</v>
+        <v>-2951.257842541732</v>
       </c>
       <c r="O89">
-        <v>-856.0337464811274</v>
+        <v>-885.3773527625196</v>
       </c>
       <c r="P89">
-        <v>-1997.412075122631</v>
+        <v>-2065.880489779212</v>
       </c>
       <c r="Q89">
-        <v>2293.687924877369</v>
+        <v>2225.219510220788</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4776137891858058</v>
+        <v>0.5135982716179565</v>
       </c>
       <c r="T89">
-        <v>5.944079345004512</v>
+        <v>6.439419290421557</v>
       </c>
       <c r="U89">
         <v>0.1685675944292917</v>
       </c>
       <c r="V89">
-        <v>0.1994043037246177</v>
+        <v>0.197138345727747</v>
       </c>
       <c r="W89">
-        <v>0.134954490631585</v>
+        <v>0.1353364577201953</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.6646810124153923</v>
+        <v>0.6571278190924903</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1807278753879267</v>
+        <v>0.2328742805236711</v>
       </c>
       <c r="C90">
-        <v>-21063.71793845057</v>
+        <v>-28765.41124515838</v>
       </c>
       <c r="D90">
-        <v>25548.03406154944</v>
+        <v>18426.59475484162</v>
       </c>
       <c r="E90">
-        <v>28206.852</v>
+        <v>28787.106</v>
       </c>
       <c r="F90">
-        <v>51062.352</v>
+        <v>51642.606</v>
       </c>
       <c r="G90">
         <v>4450.6</v>
@@ -8673,45 +8673,45 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M90">
-        <v>8607.457842541731</v>
+        <v>11493.97058747971</v>
       </c>
       <c r="N90">
-        <v>-2951.257842541732</v>
+        <v>-5837.770587479707</v>
       </c>
       <c r="O90">
-        <v>-885.3773527625196</v>
+        <v>-1751.331176243912</v>
       </c>
       <c r="P90">
-        <v>-2065.880489779212</v>
+        <v>-4086.439411235795</v>
       </c>
       <c r="Q90">
-        <v>2225.219510220788</v>
+        <v>204.6605887642054</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5135982716179565</v>
+        <v>0.5821138344146026</v>
       </c>
       <c r="T90">
-        <v>6.439419290421557</v>
+        <v>7.382561801916629</v>
       </c>
       <c r="U90">
-        <v>0.1685675944292917</v>
+        <v>0.2225675944292917</v>
       </c>
       <c r="V90">
-        <v>0.197138345727747</v>
+        <v>0.1476304456397667</v>
       </c>
       <c r="W90">
-        <v>0.1353364577201953</v>
+        <v>0.1897098412787245</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.6571278190924903</v>
+        <v>0.4921014854658889</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2328742805236711</v>
+        <v>0.234641956467964</v>
       </c>
       <c r="C91">
-        <v>-28765.41124515838</v>
+        <v>-29518.14941600995</v>
       </c>
       <c r="D91">
-        <v>18426.59475484162</v>
+        <v>18254.11058399004</v>
       </c>
       <c r="E91">
-        <v>28787.106</v>
+        <v>29367.36</v>
       </c>
       <c r="F91">
-        <v>51642.606</v>
+        <v>52222.86</v>
       </c>
       <c r="G91">
         <v>4450.6</v>
@@ -8755,37 +8755,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M91">
-        <v>11493.97058747971</v>
+        <v>11623.11632441768</v>
       </c>
       <c r="N91">
-        <v>-5837.770587479707</v>
+        <v>-5966.916324417682</v>
       </c>
       <c r="O91">
-        <v>-1751.331176243912</v>
+        <v>-1790.074897325304</v>
       </c>
       <c r="P91">
-        <v>-4086.439411235795</v>
+        <v>-4176.841427092377</v>
       </c>
       <c r="Q91">
-        <v>204.6605887642054</v>
+        <v>114.2585729076236</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5821138344146026</v>
+        <v>0.635745217856063</v>
       </c>
       <c r="T91">
-        <v>7.382561801916629</v>
+        <v>8.120817982108292</v>
       </c>
       <c r="U91">
         <v>0.2225675944292917</v>
       </c>
       <c r="V91">
-        <v>0.1476304456397667</v>
+        <v>0.1459901073548804</v>
       </c>
       <c r="W91">
-        <v>0.1897098412787245</v>
+        <v>0.1900749274248419</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4921014854658889</v>
+        <v>0.4866336911829345</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.234641956467964</v>
+        <v>0.236409632412257</v>
       </c>
       <c r="C92">
-        <v>-29518.14941600995</v>
+        <v>-30267.68841884756</v>
       </c>
       <c r="D92">
-        <v>18254.11058399004</v>
+        <v>18084.82558115244</v>
       </c>
       <c r="E92">
-        <v>29367.36</v>
+        <v>29947.614</v>
       </c>
       <c r="F92">
-        <v>52222.86</v>
+        <v>52803.114</v>
       </c>
       <c r="G92">
         <v>4450.6</v>
@@ -8837,37 +8837,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M92">
-        <v>11623.11632441768</v>
+        <v>11752.26206135565</v>
       </c>
       <c r="N92">
-        <v>-5966.916324417682</v>
+        <v>-6096.062061355655</v>
       </c>
       <c r="O92">
-        <v>-1790.074897325304</v>
+        <v>-1828.818618406696</v>
       </c>
       <c r="P92">
-        <v>-4176.841427092377</v>
+        <v>-4267.243442948959</v>
       </c>
       <c r="Q92">
-        <v>114.2585729076236</v>
+        <v>23.85655705104182</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.635745217856063</v>
+        <v>0.7012946865067368</v>
       </c>
       <c r="T92">
-        <v>8.120817982108292</v>
+        <v>9.023131091231438</v>
       </c>
       <c r="U92">
         <v>0.2225675944292917</v>
       </c>
       <c r="V92">
-        <v>0.1459901073548804</v>
+        <v>0.1443858204608707</v>
       </c>
       <c r="W92">
-        <v>0.1900749274248419</v>
+        <v>0.1904319896996161</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4866336911829345</v>
+        <v>0.4812860682029023</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.236409632412257</v>
+        <v>0.2381773083565499</v>
       </c>
       <c r="C93">
-        <v>-30267.68841884756</v>
+        <v>-31014.11644118749</v>
       </c>
       <c r="D93">
-        <v>18084.82558115244</v>
+        <v>17918.65155881251</v>
       </c>
       <c r="E93">
-        <v>29947.614</v>
+        <v>30527.868</v>
       </c>
       <c r="F93">
-        <v>52803.114</v>
+        <v>53383.368</v>
       </c>
       <c r="G93">
         <v>4450.6</v>
@@ -8919,37 +8919,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M93">
-        <v>11752.26206135565</v>
+        <v>11881.40779829363</v>
       </c>
       <c r="N93">
-        <v>-6096.062061355655</v>
+        <v>-6225.20779829363</v>
       </c>
       <c r="O93">
-        <v>-1828.818618406696</v>
+        <v>-1867.562339488089</v>
       </c>
       <c r="P93">
-        <v>-4267.243442948959</v>
+        <v>-4357.645458805541</v>
       </c>
       <c r="Q93">
-        <v>23.85655705104182</v>
+        <v>-66.54545880554087</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7012946865067368</v>
+        <v>0.7832315223200791</v>
       </c>
       <c r="T93">
-        <v>9.023131091231438</v>
+        <v>10.15102247763537</v>
       </c>
       <c r="U93">
         <v>0.2225675944292917</v>
       </c>
       <c r="V93">
-        <v>0.1443858204608707</v>
+        <v>0.1428164093689047</v>
       </c>
       <c r="W93">
-        <v>0.1904319896996161</v>
+        <v>0.1907812897510256</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4812860682029023</v>
+        <v>0.476054697896349</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2381773083565499</v>
+        <v>0.2399449843008428</v>
       </c>
       <c r="C94">
-        <v>-31014.11644118749</v>
+        <v>-31757.5184587824</v>
       </c>
       <c r="D94">
-        <v>17918.65155881251</v>
+        <v>17755.5035412176</v>
       </c>
       <c r="E94">
-        <v>30527.868</v>
+        <v>31108.122</v>
       </c>
       <c r="F94">
-        <v>53383.368</v>
+        <v>53963.622</v>
       </c>
       <c r="G94">
         <v>4450.6</v>
@@ -9001,37 +9001,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M94">
-        <v>11881.40779829363</v>
+        <v>12010.5535352316</v>
       </c>
       <c r="N94">
-        <v>-6225.20779829363</v>
+        <v>-6354.353535231605</v>
       </c>
       <c r="O94">
-        <v>-1867.562339488089</v>
+        <v>-1906.306060569481</v>
       </c>
       <c r="P94">
-        <v>-4357.645458805541</v>
+        <v>-4448.047474662124</v>
       </c>
       <c r="Q94">
-        <v>-66.54545880554087</v>
+        <v>-156.9474746621236</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7832315223200791</v>
+        <v>0.888578882651519</v>
       </c>
       <c r="T94">
-        <v>10.15102247763537</v>
+        <v>11.601168545869</v>
       </c>
       <c r="U94">
         <v>0.2225675944292917</v>
       </c>
       <c r="V94">
-        <v>0.1428164093689047</v>
+        <v>0.14128074905311</v>
       </c>
       <c r="W94">
-        <v>0.1907812897510256</v>
+        <v>0.1911230779733726</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.476054697896349</v>
+        <v>0.4709358301770334</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2399449843008428</v>
+        <v>0.2417126602451357</v>
       </c>
       <c r="C95">
-        <v>-31757.5184587824</v>
+        <v>-32497.97638051644</v>
       </c>
       <c r="D95">
-        <v>17755.5035412176</v>
+        <v>17595.29961948356</v>
       </c>
       <c r="E95">
-        <v>31108.122</v>
+        <v>31688.376</v>
       </c>
       <c r="F95">
-        <v>53963.622</v>
+        <v>54543.876</v>
       </c>
       <c r="G95">
         <v>4450.6</v>
@@ -9083,37 +9083,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M95">
-        <v>12010.5535352316</v>
+        <v>12139.69927216958</v>
       </c>
       <c r="N95">
-        <v>-6354.353535231605</v>
+        <v>-6483.499272169578</v>
       </c>
       <c r="O95">
-        <v>-1906.306060569481</v>
+        <v>-1945.049781650873</v>
       </c>
       <c r="P95">
-        <v>-4448.047474662124</v>
+        <v>-4538.449490518705</v>
       </c>
       <c r="Q95">
-        <v>-156.9474746621236</v>
+        <v>-247.3494905187044</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.888578882651519</v>
+        <v>1.029042029760106</v>
       </c>
       <c r="T95">
-        <v>11.601168545869</v>
+        <v>13.53469663684717</v>
       </c>
       <c r="U95">
         <v>0.2225675944292917</v>
       </c>
       <c r="V95">
-        <v>0.14128074905311</v>
+        <v>0.1397777623610557</v>
       </c>
       <c r="W95">
-        <v>0.1911230779733726</v>
+        <v>0.1914575941058823</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4709358301770334</v>
+        <v>0.4659258745368523</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2417126602451357</v>
+        <v>0.2434803361894286</v>
       </c>
       <c r="C96">
-        <v>-32497.97638051644</v>
+        <v>-33235.56918552628</v>
       </c>
       <c r="D96">
-        <v>17595.29961948356</v>
+        <v>17437.96081447372</v>
       </c>
       <c r="E96">
-        <v>31688.376</v>
+        <v>32268.63</v>
       </c>
       <c r="F96">
-        <v>54543.876</v>
+        <v>55124.13</v>
       </c>
       <c r="G96">
         <v>4450.6</v>
@@ -9165,37 +9165,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M96">
-        <v>12139.69927216958</v>
+        <v>12268.84500910755</v>
       </c>
       <c r="N96">
-        <v>-6483.499272169578</v>
+        <v>-6612.645009107553</v>
       </c>
       <c r="O96">
-        <v>-1945.049781650873</v>
+        <v>-1983.793502732266</v>
       </c>
       <c r="P96">
-        <v>-4538.449490518705</v>
+        <v>-4628.851506375287</v>
       </c>
       <c r="Q96">
-        <v>-247.3494905187044</v>
+        <v>-337.7515063752871</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.029042029760106</v>
+        <v>1.225690435712128</v>
       </c>
       <c r="T96">
-        <v>13.53469663684717</v>
+        <v>16.24163596421661</v>
       </c>
       <c r="U96">
         <v>0.2225675944292917</v>
       </c>
       <c r="V96">
-        <v>0.1397777623610557</v>
+        <v>0.1383064174940972</v>
       </c>
       <c r="W96">
-        <v>0.1914575941058823</v>
+        <v>0.1917850677934972</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4659258745368523</v>
+        <v>0.4610213916469906</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2434803361894286</v>
+        <v>0.2452480121337215</v>
       </c>
       <c r="C97">
-        <v>-33235.56918552628</v>
+        <v>-33970.37305303061</v>
       </c>
       <c r="D97">
-        <v>17437.96081447372</v>
+        <v>17283.4109469694</v>
       </c>
       <c r="E97">
-        <v>32268.63</v>
+        <v>32848.88400000001</v>
       </c>
       <c r="F97">
-        <v>55124.13</v>
+        <v>55704.38400000001</v>
       </c>
       <c r="G97">
         <v>4450.6</v>
@@ -9247,37 +9247,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M97">
-        <v>12268.84500910755</v>
+        <v>12397.99074604553</v>
       </c>
       <c r="N97">
-        <v>-6612.645009107553</v>
+        <v>-6741.790746045528</v>
       </c>
       <c r="O97">
-        <v>-1983.793502732266</v>
+        <v>-2022.537223813658</v>
       </c>
       <c r="P97">
-        <v>-4628.851506375287</v>
+        <v>-4719.253522231869</v>
       </c>
       <c r="Q97">
-        <v>-337.7515063752871</v>
+        <v>-428.1535222318689</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.225690435712128</v>
+        <v>1.52066304464016</v>
       </c>
       <c r="T97">
-        <v>16.24163596421661</v>
+        <v>20.30204495527077</v>
       </c>
       <c r="U97">
         <v>0.2225675944292917</v>
       </c>
       <c r="V97">
-        <v>0.1383064174940972</v>
+        <v>0.1368657256452003</v>
       </c>
       <c r="W97">
-        <v>0.1917850677934972</v>
+        <v>0.19210571911262</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4610213916469906</v>
+        <v>0.4562190854840011</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2452480121337215</v>
+        <v>0.2470156880780144</v>
       </c>
       <c r="C98">
-        <v>-33970.3730530306</v>
+        <v>-34702.46148531623</v>
       </c>
       <c r="D98">
-        <v>17283.4109469694</v>
+        <v>17131.57651468377</v>
       </c>
       <c r="E98">
-        <v>32848.884</v>
+        <v>33429.138</v>
       </c>
       <c r="F98">
-        <v>55704.384</v>
+        <v>56284.638</v>
       </c>
       <c r="G98">
         <v>4450.6</v>
@@ -9329,37 +9329,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M98">
-        <v>12397.99074604553</v>
+        <v>12527.1364829835</v>
       </c>
       <c r="N98">
-        <v>-6741.790746045526</v>
+        <v>-6870.936482983501</v>
       </c>
       <c r="O98">
-        <v>-2022.537223813658</v>
+        <v>-2061.28094489505</v>
       </c>
       <c r="P98">
-        <v>-4719.253522231868</v>
+        <v>-4809.655538088451</v>
       </c>
       <c r="Q98">
-        <v>-428.153522231868</v>
+        <v>-518.5555380884507</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.520663044640156</v>
+        <v>2.012284059520208</v>
       </c>
       <c r="T98">
-        <v>20.30204495527071</v>
+        <v>27.06939327369428</v>
       </c>
       <c r="U98">
         <v>0.2225675944292917</v>
       </c>
       <c r="V98">
-        <v>0.1368657256452004</v>
+        <v>0.1354547387828787</v>
       </c>
       <c r="W98">
-        <v>0.19210571911262</v>
+        <v>0.1924197590643383</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4562190854840011</v>
+        <v>0.451515795942929</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2470156880780144</v>
+        <v>0.2487833640223074</v>
       </c>
       <c r="C99">
-        <v>-34702.46148531623</v>
+        <v>-35431.90542429809</v>
       </c>
       <c r="D99">
-        <v>17131.57651468377</v>
+        <v>16982.38657570192</v>
       </c>
       <c r="E99">
-        <v>33429.138</v>
+        <v>34009.392</v>
       </c>
       <c r="F99">
-        <v>56284.638</v>
+        <v>56864.892</v>
       </c>
       <c r="G99">
         <v>4450.6</v>
@@ -9411,37 +9411,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M99">
-        <v>12527.1364829835</v>
+        <v>12656.28221992147</v>
       </c>
       <c r="N99">
-        <v>-6870.936482983501</v>
+        <v>-7000.082219921474</v>
       </c>
       <c r="O99">
-        <v>-2061.28094489505</v>
+        <v>-2100.024665976442</v>
       </c>
       <c r="P99">
-        <v>-4809.655538088451</v>
+        <v>-4900.057553945033</v>
       </c>
       <c r="Q99">
-        <v>-518.5555380884507</v>
+        <v>-608.9575539450325</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.012284059520208</v>
+        <v>2.995526089280312</v>
       </c>
       <c r="T99">
-        <v>27.06939327369428</v>
+        <v>40.60408991054143</v>
       </c>
       <c r="U99">
         <v>0.2225675944292917</v>
       </c>
       <c r="V99">
-        <v>0.1354547387828787</v>
+        <v>0.1340725475708085</v>
       </c>
       <c r="W99">
-        <v>0.1924197590643383</v>
+        <v>0.1927273900374501</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.451515795942929</v>
+        <v>0.446908491902695</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2487833640223074</v>
+        <v>0.2505510399666003</v>
       </c>
       <c r="C100">
-        <v>-35431.90542429809</v>
+        <v>-36158.77336204144</v>
       </c>
       <c r="D100">
-        <v>16982.38657570192</v>
+        <v>16835.77263795856</v>
       </c>
       <c r="E100">
-        <v>34009.392</v>
+        <v>34589.646</v>
       </c>
       <c r="F100">
-        <v>56864.892</v>
+        <v>57445.146</v>
       </c>
       <c r="G100">
         <v>4450.6</v>
@@ -9493,37 +9493,37 @@
         <v>5656.199999999999</v>
       </c>
       <c r="M100">
-        <v>12656.28221992147</v>
+        <v>12785.42795685945</v>
       </c>
       <c r="N100">
-        <v>-7000.082219921474</v>
+        <v>-7129.227956859449</v>
       </c>
       <c r="O100">
-        <v>-2100.024665976442</v>
+        <v>-2138.768387057835</v>
       </c>
       <c r="P100">
-        <v>-4900.057553945033</v>
+        <v>-4990.459569801615</v>
       </c>
       <c r="Q100">
-        <v>-608.9575539450325</v>
+        <v>-699.3595698016143</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.995526089280312</v>
+        <v>5.945252178560624</v>
       </c>
       <c r="T100">
-        <v>40.60408991054143</v>
+        <v>81.20817982108285</v>
       </c>
       <c r="U100">
         <v>0.2225675944292917</v>
       </c>
       <c r="V100">
-        <v>0.1340725475708085</v>
+        <v>0.1327182794135276</v>
       </c>
       <c r="W100">
-        <v>0.1927273900374501</v>
+        <v>0.1930288062434283</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.446908491902695</v>
+        <v>0.4423942647117587</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2505510399666003</v>
-      </c>
-      <c r="C101">
-        <v>-36158.77336204144</v>
-      </c>
-      <c r="D101">
-        <v>16835.77263795856</v>
-      </c>
-      <c r="E101">
-        <v>34589.646</v>
-      </c>
-      <c r="F101">
-        <v>57445.146</v>
-      </c>
-      <c r="G101">
-        <v>4450.6</v>
-      </c>
-      <c r="H101">
-        <v>35169.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9947.299999999999</v>
-      </c>
-      <c r="K101">
-        <v>4291.1</v>
-      </c>
-      <c r="L101">
-        <v>5656.199999999999</v>
-      </c>
-      <c r="M101">
-        <v>12785.42795685945</v>
-      </c>
-      <c r="N101">
-        <v>-7129.227956859449</v>
-      </c>
-      <c r="O101">
-        <v>-2138.768387057835</v>
-      </c>
-      <c r="P101">
-        <v>-4990.459569801615</v>
-      </c>
-      <c r="Q101">
-        <v>-699.3595698016143</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.945252178560624</v>
-      </c>
-      <c r="T101">
-        <v>81.20817982108285</v>
-      </c>
-      <c r="U101">
-        <v>0.2225675944292917</v>
-      </c>
-      <c r="V101">
-        <v>0.1327182794135276</v>
-      </c>
-      <c r="W101">
-        <v>0.1930288062434283</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4423942647117587</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
